--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011216</v>
       </c>
       <c r="B34" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>411316</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129011229</v>
       </c>
       <c r="B35" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>412001</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,19 +4105,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011216</v>
+        <v>129032187</v>
       </c>
       <c r="B36" t="n">
         <v>79034</v>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411316</v>
+        <v>411321</v>
       </c>
       <c r="R36" t="n">
-        <v>6781674</v>
+        <v>6781689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4185,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011229</v>
+        <v>129032764</v>
       </c>
       <c r="B37" t="n">
         <v>79034</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>412001</v>
+        <v>410852</v>
       </c>
       <c r="R37" t="n">
-        <v>6781693</v>
+        <v>6781859</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,19 +4282,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4309,19 +4299,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032187</v>
+        <v>129032774</v>
       </c>
       <c r="B38" t="n">
         <v>79034</v>
@@ -4356,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411321</v>
+        <v>411548</v>
       </c>
       <c r="R38" t="n">
-        <v>6781689</v>
+        <v>6781798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,22 +4396,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032764</v>
+        <v>129011197</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4429,21 +4419,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4453,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410852</v>
+        <v>411531</v>
       </c>
       <c r="R39" t="n">
-        <v>6781859</v>
+        <v>6781805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,9 +4476,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032774</v>
+        <v>129032739</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411548</v>
+        <v>410877</v>
       </c>
       <c r="R40" t="n">
-        <v>6781798</v>
+        <v>6781741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>129032786</v>
       </c>
       <c r="B12" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032201</v>
+        <v>129032779</v>
       </c>
       <c r="B32" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411198</v>
+        <v>411808</v>
       </c>
       <c r="R32" t="n">
-        <v>6781834</v>
+        <v>6781920</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,22 +3794,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032779</v>
+        <v>129032201</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411808</v>
+        <v>411198</v>
       </c>
       <c r="R33" t="n">
-        <v>6781920</v>
+        <v>6781834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011216</v>
+        <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411316</v>
+        <v>411531</v>
       </c>
       <c r="R34" t="n">
-        <v>6781674</v>
+        <v>6781805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011229</v>
+        <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>412001</v>
+        <v>410877</v>
       </c>
       <c r="R35" t="n">
-        <v>6781693</v>
+        <v>6781741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,19 +4078,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,19 +4095,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032187</v>
+        <v>129011216</v>
       </c>
       <c r="B36" t="n">
         <v>79034</v>
@@ -4152,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411321</v>
+        <v>411316</v>
       </c>
       <c r="R36" t="n">
-        <v>6781689</v>
+        <v>6781674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4185,9 +4175,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032764</v>
+        <v>129011229</v>
       </c>
       <c r="B37" t="n">
         <v>79034</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410852</v>
+        <v>412001</v>
       </c>
       <c r="R37" t="n">
-        <v>6781859</v>
+        <v>6781693</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,9 +4282,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,19 +4309,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032774</v>
+        <v>129032187</v>
       </c>
       <c r="B38" t="n">
         <v>79034</v>
@@ -4346,10 +4356,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411548</v>
+        <v>411321</v>
       </c>
       <c r="R38" t="n">
-        <v>6781798</v>
+        <v>6781689</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,22 +4406,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011197</v>
+        <v>129032764</v>
       </c>
       <c r="B39" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,21 +4429,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411531</v>
+        <v>410852</v>
       </c>
       <c r="R39" t="n">
-        <v>6781805</v>
+        <v>6781859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,19 +4486,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032739</v>
+        <v>129032774</v>
       </c>
       <c r="B40" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410877</v>
+        <v>411548</v>
       </c>
       <c r="R40" t="n">
-        <v>6781741</v>
+        <v>6781798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032765</v>
+        <v>129032740</v>
       </c>
       <c r="B63" t="n">
-        <v>79034</v>
+        <v>79066</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>410893</v>
+        <v>411020</v>
       </c>
       <c r="R63" t="n">
-        <v>6781859</v>
+        <v>6781851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032740</v>
+        <v>129011220</v>
       </c>
       <c r="B64" t="n">
-        <v>79066</v>
+        <v>79034</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411020</v>
+        <v>411312</v>
       </c>
       <c r="R64" t="n">
-        <v>6781851</v>
+        <v>6781706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,9 +7011,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7028,19 +7038,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B65" t="n">
         <v>79034</v>
@@ -7075,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R65" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7108,19 +7118,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7135,44 +7135,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032200</v>
+        <v>129032772</v>
       </c>
       <c r="B66" t="n">
-        <v>92811</v>
+        <v>79034</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411326</v>
+        <v>411565</v>
       </c>
       <c r="R66" t="n">
-        <v>6781874</v>
+        <v>6781780</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,19 +7232,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032772</v>
+        <v>129032746</v>
       </c>
       <c r="B67" t="n">
         <v>79034</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411565</v>
+        <v>410697</v>
       </c>
       <c r="R67" t="n">
-        <v>6781780</v>
+        <v>6781752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032746</v>
+        <v>129032189</v>
       </c>
       <c r="B68" t="n">
         <v>79034</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410697</v>
+        <v>411250</v>
       </c>
       <c r="R68" t="n">
-        <v>6781752</v>
+        <v>6781886</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,19 +7426,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032189</v>
+        <v>129032760</v>
       </c>
       <c r="B69" t="n">
         <v>79034</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411250</v>
+        <v>410875</v>
       </c>
       <c r="R69" t="n">
-        <v>6781886</v>
+        <v>6781746</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,44 +7523,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032760</v>
+        <v>129032200</v>
       </c>
       <c r="B70" t="n">
-        <v>79034</v>
+        <v>92816</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410875</v>
+        <v>411326</v>
       </c>
       <c r="R70" t="n">
-        <v>6781746</v>
+        <v>6781874</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,12 +7620,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032181</v>
+        <v>129032767</v>
       </c>
       <c r="B75" t="n">
-        <v>79653</v>
+        <v>79034</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R75" t="n">
-        <v>6781806</v>
+        <v>6781848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032767</v>
+        <v>129032768</v>
       </c>
       <c r="B76" t="n">
         <v>79034</v>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781848</v>
+        <v>6781857</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032768</v>
+        <v>129011230</v>
       </c>
       <c r="B77" t="n">
         <v>79034</v>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R77" t="n">
-        <v>6781857</v>
+        <v>6781667</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,9 +8290,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8307,22 +8317,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011230</v>
+        <v>129032181</v>
       </c>
       <c r="B78" t="n">
-        <v>79034</v>
+        <v>79653</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,21 +8340,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8354,10 +8364,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412017</v>
+        <v>411425</v>
       </c>
       <c r="R78" t="n">
-        <v>6781667</v>
+        <v>6781806</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8387,19 +8397,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129032775</v>
       </c>
       <c r="B2" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129011223</v>
       </c>
       <c r="B3" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129032199</v>
       </c>
       <c r="B4" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032188</v>
+        <v>129032756</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411295</v>
+        <v>410745</v>
       </c>
       <c r="R5" t="n">
-        <v>6781724</v>
+        <v>6781852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032756</v>
+        <v>129032188</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410745</v>
+        <v>411295</v>
       </c>
       <c r="R6" t="n">
-        <v>6781852</v>
+        <v>6781724</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,12 +1158,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1173,7 +1173,7 @@
         <v>129032745</v>
       </c>
       <c r="B7" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129032781</v>
       </c>
       <c r="B8" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129011228</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032766</v>
+        <v>129011217</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410949</v>
+        <v>411318</v>
       </c>
       <c r="R10" t="n">
-        <v>6781860</v>
+        <v>6781689</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,9 +1539,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011217</v>
+        <v>129032766</v>
       </c>
       <c r="B11" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411318</v>
+        <v>410949</v>
       </c>
       <c r="R11" t="n">
-        <v>6781689</v>
+        <v>6781860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1636,19 +1646,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,68 +1663,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032786</v>
+        <v>129011211</v>
       </c>
       <c r="B12" t="n">
-        <v>92816</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410970</v>
+        <v>411303</v>
       </c>
       <c r="R12" t="n">
-        <v>6781684</v>
+        <v>6781649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,40 +1743,49 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011211</v>
+        <v>129011209</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1819,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411303</v>
+        <v>411237</v>
       </c>
       <c r="R13" t="n">
-        <v>6781649</v>
+        <v>6781635</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,7 +1852,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1864,7 +1862,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,10 +1889,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011208</v>
+        <v>129011212</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411221</v>
+        <v>411313</v>
       </c>
       <c r="R14" t="n">
-        <v>6781624</v>
+        <v>6781661</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,7 +1959,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1971,7 +1969,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,10 +1996,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011209</v>
+        <v>129011208</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411237</v>
+        <v>411221</v>
       </c>
       <c r="R15" t="n">
-        <v>6781635</v>
+        <v>6781624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2066,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2078,7 +2076,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2105,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011212</v>
+        <v>129032749</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2140,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411313</v>
+        <v>410719</v>
       </c>
       <c r="R16" t="n">
-        <v>6781661</v>
+        <v>6781851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,19 +2171,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,57 +2188,68 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032749</v>
+        <v>129032786</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>92819</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410719</v>
+        <v>410970</v>
       </c>
       <c r="R17" t="n">
-        <v>6781851</v>
+        <v>6781684</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,6 +2290,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2309,10 +2309,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032758</v>
+        <v>129011219</v>
       </c>
       <c r="B18" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410842</v>
+        <v>411315</v>
       </c>
       <c r="R18" t="n">
-        <v>6781713</v>
+        <v>6781704</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,9 +2377,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,22 +2404,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011219</v>
+        <v>129011207</v>
       </c>
       <c r="B19" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411315</v>
+        <v>411175</v>
       </c>
       <c r="R19" t="n">
-        <v>6781704</v>
+        <v>6781624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,7 +2486,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2486,7 +2496,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2516,7 +2526,7 @@
         <v>129032751</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2623,7 @@
         <v>129032780</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2707,10 +2717,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011207</v>
+        <v>129032758</v>
       </c>
       <c r="B22" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411175</v>
+        <v>410842</v>
       </c>
       <c r="R22" t="n">
-        <v>6781624</v>
+        <v>6781713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,19 +2785,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,68 +2802,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032787</v>
+        <v>129032754</v>
       </c>
       <c r="B23" t="n">
-        <v>92816</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410912</v>
+        <v>410774</v>
       </c>
       <c r="R23" t="n">
-        <v>6781662</v>
+        <v>6781776</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,7 +2893,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,10 +2911,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032754</v>
+        <v>129011222</v>
       </c>
       <c r="B24" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,10 +2946,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410774</v>
+        <v>411303</v>
       </c>
       <c r="R24" t="n">
-        <v>6781776</v>
+        <v>6781896</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2991,9 +2979,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3008,22 +3006,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011222</v>
+        <v>129032755</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3055,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411303</v>
+        <v>410678</v>
       </c>
       <c r="R25" t="n">
-        <v>6781896</v>
+        <v>6781823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,19 +3086,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,22 +3103,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B26" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3162,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R26" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,45 +3212,56 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032759</v>
+        <v>129032787</v>
       </c>
       <c r="B27" t="n">
-        <v>79034</v>
+        <v>92819</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410870</v>
+        <v>410912</v>
       </c>
       <c r="R27" t="n">
-        <v>6781738</v>
+        <v>6781662</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3303,6 +3302,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3324,7 +3324,7 @@
         <v>129032761</v>
       </c>
       <c r="B28" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032762</v>
+        <v>129032771</v>
       </c>
       <c r="B29" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410890</v>
+        <v>411508</v>
       </c>
       <c r="R29" t="n">
-        <v>6781771</v>
+        <v>6781794</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032771</v>
+        <v>129032762</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411508</v>
+        <v>410890</v>
       </c>
       <c r="R30" t="n">
-        <v>6781794</v>
+        <v>6781771</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,7 +3615,7 @@
         <v>129032180</v>
       </c>
       <c r="B31" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3709,10 +3709,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032779</v>
+        <v>129032201</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3720,21 +3720,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411808</v>
+        <v>411198</v>
       </c>
       <c r="R32" t="n">
-        <v>6781920</v>
+        <v>6781834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3794,22 +3794,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032201</v>
+        <v>129032779</v>
       </c>
       <c r="B33" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411198</v>
+        <v>411808</v>
       </c>
       <c r="R33" t="n">
-        <v>6781834</v>
+        <v>6781920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3906,7 +3906,7 @@
         <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>129011216</v>
       </c>
       <c r="B36" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>129011229</v>
       </c>
       <c r="B37" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>129032187</v>
       </c>
       <c r="B38" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>129032764</v>
       </c>
       <c r="B39" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>129032774</v>
       </c>
       <c r="B40" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128978125</v>
+        <v>129011215</v>
       </c>
       <c r="B41" t="n">
-        <v>79066</v>
+        <v>79035</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411776</v>
+        <v>411330</v>
       </c>
       <c r="R41" t="n">
-        <v>6781941</v>
+        <v>6781666</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011215</v>
+        <v>129011202</v>
       </c>
       <c r="B42" t="n">
-        <v>79034</v>
+        <v>78792</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411330</v>
+        <v>411246</v>
       </c>
       <c r="R42" t="n">
-        <v>6781666</v>
+        <v>6781879</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011221</v>
+        <v>129032183</v>
       </c>
       <c r="B43" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411310</v>
+        <v>412070</v>
       </c>
       <c r="R43" t="n">
-        <v>6781709</v>
+        <v>6781682</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,19 +4894,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4921,22 +4911,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011202</v>
+        <v>128978125</v>
       </c>
       <c r="B44" t="n">
-        <v>78791</v>
+        <v>79067</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,21 +4934,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>185</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4958,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>411246</v>
+        <v>411776</v>
       </c>
       <c r="R44" t="n">
-        <v>6781879</v>
+        <v>6781941</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5003,7 +4993,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5013,7 +5003,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5040,10 +5030,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032183</v>
+        <v>129011221</v>
       </c>
       <c r="B45" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412070</v>
+        <v>411310</v>
       </c>
       <c r="R45" t="n">
-        <v>6781682</v>
+        <v>6781709</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,9 +5098,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5140,7 +5140,7 @@
         <v>129032748</v>
       </c>
       <c r="B46" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>129032752</v>
       </c>
       <c r="B47" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>129011224</v>
       </c>
       <c r="B48" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5441,7 +5441,7 @@
         <v>129032184</v>
       </c>
       <c r="B49" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5538,7 +5538,7 @@
         <v>129011206</v>
       </c>
       <c r="B50" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5645,7 +5645,7 @@
         <v>129032191</v>
       </c>
       <c r="B51" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
         <v>129032769</v>
       </c>
       <c r="B52" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129032196</v>
       </c>
       <c r="B53" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>129011225</v>
       </c>
       <c r="B54" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011227</v>
+        <v>129032750</v>
       </c>
       <c r="B55" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411730</v>
+        <v>410717</v>
       </c>
       <c r="R55" t="n">
-        <v>6781958</v>
+        <v>6781843</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,19 +6108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6135,22 +6125,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011213</v>
+        <v>129011227</v>
       </c>
       <c r="B56" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6182,10 +6172,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411327</v>
+        <v>411730</v>
       </c>
       <c r="R56" t="n">
-        <v>6781657</v>
+        <v>6781958</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,7 +6207,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6227,7 +6217,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6254,10 +6244,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032192</v>
+        <v>129011213</v>
       </c>
       <c r="B57" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6289,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411504</v>
+        <v>411327</v>
       </c>
       <c r="R57" t="n">
-        <v>6781807</v>
+        <v>6781657</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6322,9 +6312,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,22 +6339,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032750</v>
+        <v>129032192</v>
       </c>
       <c r="B58" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410717</v>
+        <v>411504</v>
       </c>
       <c r="R58" t="n">
-        <v>6781843</v>
+        <v>6781807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
         <v>129032185</v>
       </c>
       <c r="B59" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>129032778</v>
       </c>
       <c r="B60" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>129011218</v>
       </c>
       <c r="B61" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>129032770</v>
       </c>
       <c r="B62" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>129032740</v>
       </c>
       <c r="B63" t="n">
-        <v>79066</v>
+        <v>79067</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B64" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R64" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,19 +7011,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,22 +7028,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032765</v>
+        <v>129011220</v>
       </c>
       <c r="B65" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7085,10 +7075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410893</v>
+        <v>411312</v>
       </c>
       <c r="R65" t="n">
-        <v>6781859</v>
+        <v>6781706</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,9 +7108,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7135,44 +7135,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032772</v>
+        <v>129032200</v>
       </c>
       <c r="B66" t="n">
-        <v>79034</v>
+        <v>92819</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411565</v>
+        <v>411326</v>
       </c>
       <c r="R66" t="n">
-        <v>6781780</v>
+        <v>6781874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,22 +7232,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032746</v>
+        <v>129032772</v>
       </c>
       <c r="B67" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410697</v>
+        <v>411565</v>
       </c>
       <c r="R67" t="n">
-        <v>6781752</v>
+        <v>6781780</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032189</v>
+        <v>129032746</v>
       </c>
       <c r="B68" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411250</v>
+        <v>410697</v>
       </c>
       <c r="R68" t="n">
-        <v>6781886</v>
+        <v>6781752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,22 +7426,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032760</v>
+        <v>129032189</v>
       </c>
       <c r="B69" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410875</v>
+        <v>411250</v>
       </c>
       <c r="R69" t="n">
-        <v>6781746</v>
+        <v>6781886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,44 +7523,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032200</v>
+        <v>129032760</v>
       </c>
       <c r="B70" t="n">
-        <v>92816</v>
+        <v>79035</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411326</v>
+        <v>410875</v>
       </c>
       <c r="R70" t="n">
-        <v>6781874</v>
+        <v>6781746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,22 +7620,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032783</v>
+        <v>129032757</v>
       </c>
       <c r="B71" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411996</v>
+        <v>410790</v>
       </c>
       <c r="R71" t="n">
-        <v>6781690</v>
+        <v>6781786</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7729,10 +7729,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032757</v>
+        <v>129032186</v>
       </c>
       <c r="B72" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410790</v>
+        <v>411332</v>
       </c>
       <c r="R72" t="n">
-        <v>6781786</v>
+        <v>6781694</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7814,22 +7814,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032186</v>
+        <v>129032783</v>
       </c>
       <c r="B73" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411332</v>
+        <v>411996</v>
       </c>
       <c r="R73" t="n">
-        <v>6781694</v>
+        <v>6781690</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,12 +7911,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032767</v>
+        <v>129032181</v>
       </c>
       <c r="B75" t="n">
-        <v>79034</v>
+        <v>79654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R75" t="n">
-        <v>6781848</v>
+        <v>6781806</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,22 +8113,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032768</v>
+        <v>129032767</v>
       </c>
       <c r="B76" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781857</v>
+        <v>6781848</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129011230</v>
+        <v>129032768</v>
       </c>
       <c r="B77" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>412017</v>
+        <v>410959</v>
       </c>
       <c r="R77" t="n">
-        <v>6781667</v>
+        <v>6781857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,19 +8290,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8317,22 +8307,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032181</v>
+        <v>129011230</v>
       </c>
       <c r="B78" t="n">
-        <v>79653</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8340,21 +8330,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8364,10 +8354,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411425</v>
+        <v>412017</v>
       </c>
       <c r="R78" t="n">
-        <v>6781806</v>
+        <v>6781667</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,9 +8387,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032756</v>
+        <v>129032188</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410745</v>
+        <v>411295</v>
       </c>
       <c r="R5" t="n">
-        <v>6781852</v>
+        <v>6781724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,19 +1061,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032188</v>
+        <v>129032756</v>
       </c>
       <c r="B6" t="n">
         <v>79035</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411295</v>
+        <v>410745</v>
       </c>
       <c r="R6" t="n">
-        <v>6781724</v>
+        <v>6781852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1158,12 +1158,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011217</v>
+        <v>129032766</v>
       </c>
       <c r="B10" t="n">
         <v>79035</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411318</v>
+        <v>410949</v>
       </c>
       <c r="R10" t="n">
-        <v>6781689</v>
+        <v>6781860</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,19 +1539,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,19 +1556,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032766</v>
+        <v>129011217</v>
       </c>
       <c r="B11" t="n">
         <v>79035</v>
@@ -1613,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410949</v>
+        <v>411318</v>
       </c>
       <c r="R11" t="n">
-        <v>6781860</v>
+        <v>6781689</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1636,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,57 +1663,68 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011211</v>
+        <v>129032786</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>411303</v>
+        <v>410970</v>
       </c>
       <c r="R12" t="n">
-        <v>6781649</v>
+        <v>6781684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,46 +1754,37 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011209</v>
+        <v>129011211</v>
       </c>
       <c r="B13" t="n">
         <v>79035</v>
@@ -1817,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411237</v>
+        <v>411303</v>
       </c>
       <c r="R13" t="n">
-        <v>6781635</v>
+        <v>6781649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1854,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1862,7 +1864,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,7 +1891,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011212</v>
+        <v>129011208</v>
       </c>
       <c r="B14" t="n">
         <v>79035</v>
@@ -1924,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411313</v>
+        <v>411221</v>
       </c>
       <c r="R14" t="n">
-        <v>6781661</v>
+        <v>6781624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1961,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1969,7 +1971,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1998,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011208</v>
+        <v>129011209</v>
       </c>
       <c r="B15" t="n">
         <v>79035</v>
@@ -2031,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411221</v>
+        <v>411237</v>
       </c>
       <c r="R15" t="n">
-        <v>6781624</v>
+        <v>6781635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2068,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2076,7 +2078,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2105,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032749</v>
+        <v>129011212</v>
       </c>
       <c r="B16" t="n">
         <v>79035</v>
@@ -2138,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410719</v>
+        <v>411313</v>
       </c>
       <c r="R16" t="n">
-        <v>6781851</v>
+        <v>6781661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2171,9 +2173,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,68 +2200,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032786</v>
+        <v>129032749</v>
       </c>
       <c r="B17" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410970</v>
+        <v>410719</v>
       </c>
       <c r="R17" t="n">
-        <v>6781684</v>
+        <v>6781851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,7 +2291,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011219</v>
+        <v>129032758</v>
       </c>
       <c r="B18" t="n">
         <v>79035</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411315</v>
+        <v>410842</v>
       </c>
       <c r="R18" t="n">
-        <v>6781704</v>
+        <v>6781713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,19 +2377,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,19 +2394,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011207</v>
+        <v>129011219</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -2451,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411175</v>
+        <v>411315</v>
       </c>
       <c r="R19" t="n">
-        <v>6781624</v>
+        <v>6781704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2486,7 +2476,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2496,7 +2486,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2717,7 +2707,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032758</v>
+        <v>129011207</v>
       </c>
       <c r="B22" t="n">
         <v>79035</v>
@@ -2752,10 +2742,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410842</v>
+        <v>411175</v>
       </c>
       <c r="R22" t="n">
-        <v>6781713</v>
+        <v>6781624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,9 +2775,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,57 +2802,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032754</v>
+        <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410774</v>
+        <v>410912</v>
       </c>
       <c r="R23" t="n">
-        <v>6781776</v>
+        <v>6781662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2904,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2911,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011222</v>
+        <v>129032754</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -2946,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411303</v>
+        <v>410774</v>
       </c>
       <c r="R24" t="n">
-        <v>6781896</v>
+        <v>6781776</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,19 +2991,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3006,19 +3008,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032755</v>
+        <v>129011222</v>
       </c>
       <c r="B25" t="n">
         <v>79035</v>
@@ -3053,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410678</v>
+        <v>411303</v>
       </c>
       <c r="R25" t="n">
-        <v>6781823</v>
+        <v>6781896</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,9 +3088,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,19 +3115,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032759</v>
+        <v>129032755</v>
       </c>
       <c r="B26" t="n">
         <v>79035</v>
@@ -3150,10 +3162,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410870</v>
+        <v>410678</v>
       </c>
       <c r="R26" t="n">
-        <v>6781738</v>
+        <v>6781823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,56 +3224,45 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032787</v>
+        <v>129032759</v>
       </c>
       <c r="B27" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410912</v>
+        <v>410870</v>
       </c>
       <c r="R27" t="n">
-        <v>6781662</v>
+        <v>6781738</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3302,7 +3303,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032771</v>
+        <v>129032762</v>
       </c>
       <c r="B29" t="n">
         <v>79035</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411508</v>
+        <v>410890</v>
       </c>
       <c r="R29" t="n">
-        <v>6781794</v>
+        <v>6781771</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032762</v>
+        <v>129032771</v>
       </c>
       <c r="B30" t="n">
         <v>79035</v>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410890</v>
+        <v>411508</v>
       </c>
       <c r="R30" t="n">
-        <v>6781771</v>
+        <v>6781794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011215</v>
+        <v>128978125</v>
       </c>
       <c r="B41" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411330</v>
+        <v>411776</v>
       </c>
       <c r="R41" t="n">
-        <v>6781666</v>
+        <v>6781941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011202</v>
+        <v>129011215</v>
       </c>
       <c r="B42" t="n">
-        <v>78792</v>
+        <v>79035</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411246</v>
+        <v>411330</v>
       </c>
       <c r="R42" t="n">
-        <v>6781879</v>
+        <v>6781666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032183</v>
+        <v>129011221</v>
       </c>
       <c r="B43" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>412070</v>
+        <v>411310</v>
       </c>
       <c r="R43" t="n">
-        <v>6781682</v>
+        <v>6781709</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,9 +4894,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4911,22 +4921,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128978125</v>
+        <v>129011202</v>
       </c>
       <c r="B44" t="n">
-        <v>79067</v>
+        <v>78792</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4934,21 +4944,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4958,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>411776</v>
+        <v>411246</v>
       </c>
       <c r="R44" t="n">
-        <v>6781941</v>
+        <v>6781879</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,7 +5003,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5003,7 +5013,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5030,10 +5040,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011221</v>
+        <v>129032183</v>
       </c>
       <c r="B45" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5041,21 +5051,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411310</v>
+        <v>412070</v>
       </c>
       <c r="R45" t="n">
-        <v>6781709</v>
+        <v>6781682</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,19 +5108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129032750</v>
+        <v>129011227</v>
       </c>
       <c r="B55" t="n">
         <v>79035</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410717</v>
+        <v>411730</v>
       </c>
       <c r="R55" t="n">
-        <v>6781843</v>
+        <v>6781958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,9 +6108,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6125,19 +6135,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011227</v>
+        <v>129011213</v>
       </c>
       <c r="B56" t="n">
         <v>79035</v>
@@ -6172,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411730</v>
+        <v>411327</v>
       </c>
       <c r="R56" t="n">
-        <v>6781958</v>
+        <v>6781657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6207,7 +6217,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6217,7 +6227,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6244,7 +6254,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011213</v>
+        <v>129032192</v>
       </c>
       <c r="B57" t="n">
         <v>79035</v>
@@ -6279,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411327</v>
+        <v>411504</v>
       </c>
       <c r="R57" t="n">
-        <v>6781657</v>
+        <v>6781807</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6312,19 +6322,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032192</v>
+        <v>129032750</v>
       </c>
       <c r="B58" t="n">
         <v>79035</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411504</v>
+        <v>410717</v>
       </c>
       <c r="R58" t="n">
-        <v>6781807</v>
+        <v>6781843</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032765</v>
+        <v>129011220</v>
       </c>
       <c r="B64" t="n">
         <v>79035</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410893</v>
+        <v>411312</v>
       </c>
       <c r="R64" t="n">
-        <v>6781859</v>
+        <v>6781706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,9 +7011,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7028,19 +7038,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B65" t="n">
         <v>79035</v>
@@ -7075,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R65" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7108,19 +7118,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7135,12 +7135,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7632,7 +7632,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032757</v>
+        <v>129032783</v>
       </c>
       <c r="B71" t="n">
         <v>79035</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410790</v>
+        <v>411996</v>
       </c>
       <c r="R71" t="n">
-        <v>6781786</v>
+        <v>6781690</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7729,7 +7729,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032186</v>
+        <v>129032757</v>
       </c>
       <c r="B72" t="n">
         <v>79035</v>
@@ -7764,10 +7764,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>411332</v>
+        <v>410790</v>
       </c>
       <c r="R72" t="n">
-        <v>6781694</v>
+        <v>6781786</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7814,19 +7814,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032783</v>
+        <v>129032186</v>
       </c>
       <c r="B73" t="n">
         <v>79035</v>
@@ -7861,10 +7861,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411996</v>
+        <v>411332</v>
       </c>
       <c r="R73" t="n">
-        <v>6781690</v>
+        <v>6781694</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,12 +7911,12 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032181</v>
+        <v>129032767</v>
       </c>
       <c r="B75" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R75" t="n">
-        <v>6781806</v>
+        <v>6781848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032767</v>
+        <v>129032768</v>
       </c>
       <c r="B76" t="n">
         <v>79035</v>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781848</v>
+        <v>6781857</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032768</v>
+        <v>129011230</v>
       </c>
       <c r="B77" t="n">
         <v>79035</v>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R77" t="n">
-        <v>6781857</v>
+        <v>6781667</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,9 +8290,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8307,22 +8317,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011230</v>
+        <v>129032181</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,21 +8340,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8354,10 +8364,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412017</v>
+        <v>411425</v>
       </c>
       <c r="R78" t="n">
-        <v>6781667</v>
+        <v>6781806</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8387,19 +8397,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -2814,56 +2814,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032787</v>
+        <v>129032754</v>
       </c>
       <c r="B23" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410912</v>
+        <v>410774</v>
       </c>
       <c r="R23" t="n">
-        <v>6781662</v>
+        <v>6781776</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,7 +2893,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2911,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032754</v>
+        <v>129011222</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -2958,10 +2946,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410774</v>
+        <v>411303</v>
       </c>
       <c r="R24" t="n">
-        <v>6781776</v>
+        <v>6781896</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2991,9 +2979,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3008,19 +3006,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011222</v>
+        <v>129032755</v>
       </c>
       <c r="B25" t="n">
         <v>79035</v>
@@ -3055,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411303</v>
+        <v>410678</v>
       </c>
       <c r="R25" t="n">
-        <v>6781896</v>
+        <v>6781823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,19 +3086,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,19 +3103,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B26" t="n">
         <v>79035</v>
@@ -3162,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R26" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,7 +3212,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032759</v>
+        <v>129032761</v>
       </c>
       <c r="B27" t="n">
         <v>79035</v>
@@ -3259,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410870</v>
+        <v>410889</v>
       </c>
       <c r="R27" t="n">
-        <v>6781738</v>
+        <v>6781774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,45 +3309,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032761</v>
+        <v>129032787</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410889</v>
+        <v>410912</v>
       </c>
       <c r="R28" t="n">
-        <v>6781774</v>
+        <v>6781662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3400,6 +3399,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032180</v>
+        <v>129032779</v>
       </c>
       <c r="B31" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411312</v>
+        <v>411808</v>
       </c>
       <c r="R31" t="n">
-        <v>6781871</v>
+        <v>6781920</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,19 +3697,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032201</v>
+        <v>129032180</v>
       </c>
       <c r="B32" t="n">
         <v>79654</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411198</v>
+        <v>411312</v>
       </c>
       <c r="R32" t="n">
-        <v>6781834</v>
+        <v>6781871</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032779</v>
+        <v>129032201</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411808</v>
+        <v>411198</v>
       </c>
       <c r="R33" t="n">
-        <v>6781920</v>
+        <v>6781834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032775</v>
+        <v>129011223</v>
       </c>
       <c r="B2" t="n">
         <v>79035</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411542</v>
+        <v>411437</v>
       </c>
       <c r="R2" t="n">
-        <v>6781824</v>
+        <v>6781809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,19 +770,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011223</v>
+        <v>129032199</v>
       </c>
       <c r="B3" t="n">
         <v>79035</v>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411437</v>
+        <v>412062</v>
       </c>
       <c r="R3" t="n">
-        <v>6781809</v>
+        <v>6781678</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +850,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +867,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032199</v>
+        <v>129032775</v>
       </c>
       <c r="B4" t="n">
         <v>79035</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412062</v>
+        <v>411542</v>
       </c>
       <c r="R4" t="n">
-        <v>6781678</v>
+        <v>6781824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,19 +964,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032188</v>
+        <v>129032756</v>
       </c>
       <c r="B5" t="n">
         <v>79035</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411295</v>
+        <v>410745</v>
       </c>
       <c r="R5" t="n">
-        <v>6781724</v>
+        <v>6781852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,19 +1061,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032756</v>
+        <v>129032745</v>
       </c>
       <c r="B6" t="n">
         <v>79035</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410745</v>
+        <v>411010</v>
       </c>
       <c r="R6" t="n">
-        <v>6781852</v>
+        <v>6781686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032745</v>
+        <v>129032781</v>
       </c>
       <c r="B7" t="n">
         <v>79035</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411010</v>
+        <v>411940</v>
       </c>
       <c r="R7" t="n">
-        <v>6781686</v>
+        <v>6781749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032781</v>
+        <v>129032188</v>
       </c>
       <c r="B8" t="n">
         <v>79035</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411940</v>
+        <v>411295</v>
       </c>
       <c r="R8" t="n">
-        <v>6781749</v>
+        <v>6781724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011219</v>
+        <v>129032780</v>
       </c>
       <c r="B19" t="n">
         <v>79035</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411315</v>
+        <v>411808</v>
       </c>
       <c r="R19" t="n">
-        <v>6781704</v>
+        <v>6781897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,19 +2474,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,19 +2491,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032751</v>
+        <v>129011207</v>
       </c>
       <c r="B20" t="n">
         <v>79035</v>
@@ -2548,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410727</v>
+        <v>411175</v>
       </c>
       <c r="R20" t="n">
-        <v>6781837</v>
+        <v>6781624</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,9 +2571,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,19 +2598,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032780</v>
+        <v>129011219</v>
       </c>
       <c r="B21" t="n">
         <v>79035</v>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>411808</v>
+        <v>411315</v>
       </c>
       <c r="R21" t="n">
-        <v>6781897</v>
+        <v>6781704</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,9 +2678,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,19 +2705,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011207</v>
+        <v>129032751</v>
       </c>
       <c r="B22" t="n">
         <v>79035</v>
@@ -2742,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411175</v>
+        <v>410727</v>
       </c>
       <c r="R22" t="n">
-        <v>6781624</v>
+        <v>6781837</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,19 +2785,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,57 +2802,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032754</v>
+        <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>79035</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410774</v>
+        <v>410912</v>
       </c>
       <c r="R23" t="n">
-        <v>6781776</v>
+        <v>6781662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2904,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2911,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011222</v>
+        <v>129032755</v>
       </c>
       <c r="B24" t="n">
         <v>79035</v>
@@ -2946,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411303</v>
+        <v>410678</v>
       </c>
       <c r="R24" t="n">
-        <v>6781896</v>
+        <v>6781823</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,19 +2991,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3006,19 +3008,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032755</v>
+        <v>129011222</v>
       </c>
       <c r="B25" t="n">
         <v>79035</v>
@@ -3053,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410678</v>
+        <v>411303</v>
       </c>
       <c r="R25" t="n">
-        <v>6781823</v>
+        <v>6781896</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,9 +3088,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,19 +3115,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032759</v>
+        <v>129032754</v>
       </c>
       <c r="B26" t="n">
         <v>79035</v>
@@ -3150,10 +3162,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410870</v>
+        <v>410774</v>
       </c>
       <c r="R26" t="n">
-        <v>6781738</v>
+        <v>6781776</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3224,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032761</v>
+        <v>129032759</v>
       </c>
       <c r="B27" t="n">
         <v>79035</v>
@@ -3247,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410889</v>
+        <v>410870</v>
       </c>
       <c r="R27" t="n">
-        <v>6781774</v>
+        <v>6781738</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,56 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032787</v>
+        <v>129032761</v>
       </c>
       <c r="B28" t="n">
-        <v>92819</v>
+        <v>79035</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410912</v>
+        <v>410889</v>
       </c>
       <c r="R28" t="n">
-        <v>6781662</v>
+        <v>6781774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,7 +3400,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032779</v>
+        <v>129032180</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411808</v>
+        <v>411312</v>
       </c>
       <c r="R31" t="n">
-        <v>6781920</v>
+        <v>6781871</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,19 +3697,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032180</v>
+        <v>129032201</v>
       </c>
       <c r="B32" t="n">
         <v>79654</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411312</v>
+        <v>411198</v>
       </c>
       <c r="R32" t="n">
-        <v>6781871</v>
+        <v>6781834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032201</v>
+        <v>129032779</v>
       </c>
       <c r="B33" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411198</v>
+        <v>411808</v>
       </c>
       <c r="R33" t="n">
-        <v>6781834</v>
+        <v>6781920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011216</v>
       </c>
       <c r="B34" t="n">
-        <v>79067</v>
+        <v>79035</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>411316</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,7 +4010,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129011197</v>
       </c>
       <c r="B35" t="n">
         <v>79067</v>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>411531</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781805</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,22 +4105,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011216</v>
+        <v>129032739</v>
       </c>
       <c r="B36" t="n">
-        <v>79035</v>
+        <v>79067</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4118,21 +4128,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411316</v>
+        <v>410877</v>
       </c>
       <c r="R36" t="n">
-        <v>6781674</v>
+        <v>6781741</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4185,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,12 +4202,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -5438,7 +5438,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032184</v>
+        <v>129032769</v>
       </c>
       <c r="B49" t="n">
         <v>79035</v>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411414</v>
+        <v>411017</v>
       </c>
       <c r="R49" t="n">
-        <v>6781817</v>
+        <v>6781839</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5523,19 +5523,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011206</v>
+        <v>129032184</v>
       </c>
       <c r="B50" t="n">
         <v>79035</v>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411166</v>
+        <v>411414</v>
       </c>
       <c r="R50" t="n">
-        <v>6781615</v>
+        <v>6781817</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5603,19 +5603,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5630,12 +5620,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5739,7 +5729,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032769</v>
+        <v>129011206</v>
       </c>
       <c r="B52" t="n">
         <v>79035</v>
@@ -5774,10 +5764,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411017</v>
+        <v>411166</v>
       </c>
       <c r="R52" t="n">
-        <v>6781839</v>
+        <v>6781615</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5807,9 +5797,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011225</v>
+        <v>129011227</v>
       </c>
       <c r="B54" t="n">
         <v>79035</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411536</v>
+        <v>411730</v>
       </c>
       <c r="R54" t="n">
-        <v>6781806</v>
+        <v>6781958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6040,7 +6040,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011227</v>
+        <v>129032750</v>
       </c>
       <c r="B55" t="n">
         <v>79035</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411730</v>
+        <v>410717</v>
       </c>
       <c r="R55" t="n">
-        <v>6781958</v>
+        <v>6781843</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,19 +6108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6135,19 +6125,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011213</v>
+        <v>129032192</v>
       </c>
       <c r="B56" t="n">
         <v>79035</v>
@@ -6182,10 +6172,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411327</v>
+        <v>411504</v>
       </c>
       <c r="R56" t="n">
-        <v>6781657</v>
+        <v>6781807</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6215,19 +6205,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6242,19 +6222,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032192</v>
+        <v>129011225</v>
       </c>
       <c r="B57" t="n">
         <v>79035</v>
@@ -6289,10 +6269,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411504</v>
+        <v>411536</v>
       </c>
       <c r="R57" t="n">
-        <v>6781807</v>
+        <v>6781806</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6322,9 +6302,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,19 +6329,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032750</v>
+        <v>129011213</v>
       </c>
       <c r="B58" t="n">
         <v>79035</v>
@@ -6386,10 +6376,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410717</v>
+        <v>411327</v>
       </c>
       <c r="R58" t="n">
-        <v>6781843</v>
+        <v>6781657</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6419,9 +6409,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B61" t="n">
         <v>79035</v>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R61" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,19 +6710,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,19 +6727,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032770</v>
+        <v>129011218</v>
       </c>
       <c r="B62" t="n">
         <v>79035</v>
@@ -6784,10 +6774,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411070</v>
+        <v>411322</v>
       </c>
       <c r="R62" t="n">
-        <v>6781879</v>
+        <v>6781695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6817,9 +6807,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,12 +6834,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032189</v>
+        <v>129032760</v>
       </c>
       <c r="B69" t="n">
         <v>79035</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411250</v>
+        <v>410875</v>
       </c>
       <c r="R69" t="n">
-        <v>6781886</v>
+        <v>6781746</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,19 +7523,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032760</v>
+        <v>129032189</v>
       </c>
       <c r="B70" t="n">
         <v>79035</v>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410875</v>
+        <v>411250</v>
       </c>
       <c r="R70" t="n">
-        <v>6781746</v>
+        <v>6781886</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,12 +7620,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7826,10 +7826,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032186</v>
+        <v>129032741</v>
       </c>
       <c r="B73" t="n">
-        <v>79035</v>
+        <v>57720</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7837,34 +7837,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411332</v>
+        <v>410958</v>
       </c>
       <c r="R73" t="n">
-        <v>6781694</v>
+        <v>6781689</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,22 +7919,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032741</v>
+        <v>129032186</v>
       </c>
       <c r="B74" t="n">
-        <v>57720</v>
+        <v>79035</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7934,42 +7942,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410958</v>
+        <v>411332</v>
       </c>
       <c r="R74" t="n">
-        <v>6781689</v>
+        <v>6781694</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,12 +8016,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129011230</v>
+        <v>129032181</v>
       </c>
       <c r="B77" t="n">
-        <v>79035</v>
+        <v>79654</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8233,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>412017</v>
+        <v>411425</v>
       </c>
       <c r="R77" t="n">
-        <v>6781667</v>
+        <v>6781806</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,19 +8290,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8317,22 +8307,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032181</v>
+        <v>129011230</v>
       </c>
       <c r="B78" t="n">
-        <v>79654</v>
+        <v>79035</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8340,21 +8330,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8364,10 +8354,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411425</v>
+        <v>412017</v>
       </c>
       <c r="R78" t="n">
-        <v>6781806</v>
+        <v>6781667</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,9 +8387,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129011223</v>
+        <v>129032775</v>
       </c>
       <c r="B2" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411437</v>
+        <v>411542</v>
       </c>
       <c r="R2" t="n">
-        <v>6781809</v>
+        <v>6781824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,22 +760,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129032199</v>
+        <v>129011223</v>
       </c>
       <c r="B3" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>412062</v>
+        <v>411437</v>
       </c>
       <c r="R3" t="n">
-        <v>6781678</v>
+        <v>6781809</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,22 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032775</v>
+        <v>129032199</v>
       </c>
       <c r="B4" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411542</v>
+        <v>412062</v>
       </c>
       <c r="R4" t="n">
-        <v>6781824</v>
+        <v>6781678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,22 +964,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032756</v>
+        <v>129032188</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410745</v>
+        <v>411295</v>
       </c>
       <c r="R5" t="n">
-        <v>6781852</v>
+        <v>6781724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032745</v>
+        <v>129032756</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411010</v>
+        <v>410745</v>
       </c>
       <c r="R6" t="n">
-        <v>6781686</v>
+        <v>6781852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032781</v>
+        <v>129032745</v>
       </c>
       <c r="B7" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411940</v>
+        <v>411010</v>
       </c>
       <c r="R7" t="n">
-        <v>6781749</v>
+        <v>6781686</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032188</v>
+        <v>129032781</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411295</v>
+        <v>411940</v>
       </c>
       <c r="R8" t="n">
-        <v>6781724</v>
+        <v>6781749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1367,7 +1367,7 @@
         <v>129011228</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129032766</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129011217</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129032786</v>
       </c>
       <c r="B12" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>129011211</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1894,7 +1894,7 @@
         <v>129011208</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,7 +2001,7 @@
         <v>129011209</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2108,7 +2108,7 @@
         <v>129011212</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         <v>129032749</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>129032758</v>
       </c>
       <c r="B18" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2406,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032780</v>
+        <v>129011219</v>
       </c>
       <c r="B19" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411808</v>
+        <v>411315</v>
       </c>
       <c r="R19" t="n">
-        <v>6781897</v>
+        <v>6781704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,9 +2474,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,22 +2501,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011207</v>
+        <v>129032751</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2538,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>411175</v>
+        <v>410727</v>
       </c>
       <c r="R20" t="n">
-        <v>6781624</v>
+        <v>6781837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2571,19 +2581,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,22 +2598,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011219</v>
+        <v>129032780</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>411315</v>
+        <v>411808</v>
       </c>
       <c r="R21" t="n">
-        <v>6781704</v>
+        <v>6781897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,19 +2678,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,22 +2695,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032751</v>
+        <v>129011207</v>
       </c>
       <c r="B22" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,10 +2742,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410727</v>
+        <v>411175</v>
       </c>
       <c r="R22" t="n">
-        <v>6781837</v>
+        <v>6781624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,9 +2775,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,12 +2802,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2817,7 +2817,7 @@
         <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,10 +2923,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032755</v>
+        <v>129032754</v>
       </c>
       <c r="B24" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410678</v>
+        <v>410774</v>
       </c>
       <c r="R24" t="n">
-        <v>6781823</v>
+        <v>6781776</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3023,7 +3023,7 @@
         <v>129011222</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3127,10 +3127,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032754</v>
+        <v>129032755</v>
       </c>
       <c r="B26" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410774</v>
+        <v>410678</v>
       </c>
       <c r="R26" t="n">
-        <v>6781776</v>
+        <v>6781823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3227,7 +3227,7 @@
         <v>129032759</v>
       </c>
       <c r="B27" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>129032761</v>
       </c>
       <c r="B28" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
         <v>129032762</v>
       </c>
       <c r="B29" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>129032771</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         <v>129032180</v>
       </c>
       <c r="B31" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>129032201</v>
       </c>
       <c r="B32" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>129032779</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011216</v>
+        <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79035</v>
+        <v>79071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411316</v>
+        <v>411531</v>
       </c>
       <c r="R34" t="n">
-        <v>6781674</v>
+        <v>6781805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011197</v>
+        <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411531</v>
+        <v>410877</v>
       </c>
       <c r="R35" t="n">
-        <v>6781805</v>
+        <v>6781741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,19 +4078,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,22 +4095,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032739</v>
+        <v>129011216</v>
       </c>
       <c r="B36" t="n">
-        <v>79067</v>
+        <v>79039</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4128,21 +4118,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4152,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410877</v>
+        <v>411316</v>
       </c>
       <c r="R36" t="n">
-        <v>6781741</v>
+        <v>6781674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4185,9 +4175,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,12 +4202,12 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4217,7 +4217,7 @@
         <v>129011229</v>
       </c>
       <c r="B37" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>129032187</v>
       </c>
       <c r="B38" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4421,7 +4421,7 @@
         <v>129032764</v>
       </c>
       <c r="B39" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4518,7 +4518,7 @@
         <v>129032774</v>
       </c>
       <c r="B40" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128978125</v>
+        <v>129011215</v>
       </c>
       <c r="B41" t="n">
-        <v>79067</v>
+        <v>79039</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411776</v>
+        <v>411330</v>
       </c>
       <c r="R41" t="n">
-        <v>6781941</v>
+        <v>6781666</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011215</v>
+        <v>129011221</v>
       </c>
       <c r="B42" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411330</v>
+        <v>411310</v>
       </c>
       <c r="R42" t="n">
-        <v>6781666</v>
+        <v>6781709</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011221</v>
+        <v>129011202</v>
       </c>
       <c r="B43" t="n">
-        <v>79035</v>
+        <v>78796</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411310</v>
+        <v>411246</v>
       </c>
       <c r="R43" t="n">
-        <v>6781709</v>
+        <v>6781879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4933,10 +4933,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011202</v>
+        <v>129032183</v>
       </c>
       <c r="B44" t="n">
-        <v>78792</v>
+        <v>79658</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>411246</v>
+        <v>412070</v>
       </c>
       <c r="R44" t="n">
-        <v>6781879</v>
+        <v>6781682</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5001,19 +5001,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5028,22 +5018,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032183</v>
+        <v>128978125</v>
       </c>
       <c r="B45" t="n">
-        <v>79654</v>
+        <v>79071</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412070</v>
+        <v>411776</v>
       </c>
       <c r="R45" t="n">
-        <v>6781682</v>
+        <v>6781941</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,9 +5098,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5140,7 +5140,7 @@
         <v>129032748</v>
       </c>
       <c r="B46" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>129032752</v>
       </c>
       <c r="B47" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5334,7 +5334,7 @@
         <v>129011224</v>
       </c>
       <c r="B48" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5438,10 +5438,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032769</v>
+        <v>129032184</v>
       </c>
       <c r="B49" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5473,10 +5473,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411017</v>
+        <v>411414</v>
       </c>
       <c r="R49" t="n">
-        <v>6781839</v>
+        <v>6781817</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5523,22 +5523,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032184</v>
+        <v>129011206</v>
       </c>
       <c r="B50" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411414</v>
+        <v>411166</v>
       </c>
       <c r="R50" t="n">
-        <v>6781817</v>
+        <v>6781615</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5603,9 +5603,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5620,12 +5630,12 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -5635,7 +5645,7 @@
         <v>129032191</v>
       </c>
       <c r="B51" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5729,10 +5739,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011206</v>
+        <v>129032769</v>
       </c>
       <c r="B52" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5764,10 +5774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411166</v>
+        <v>411017</v>
       </c>
       <c r="R52" t="n">
-        <v>6781615</v>
+        <v>6781839</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5797,19 +5807,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5839,7 +5839,7 @@
         <v>129032196</v>
       </c>
       <c r="B53" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011227</v>
+        <v>129011225</v>
       </c>
       <c r="B54" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411730</v>
+        <v>411536</v>
       </c>
       <c r="R54" t="n">
-        <v>6781958</v>
+        <v>6781806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6040,10 +6040,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129032750</v>
+        <v>129011227</v>
       </c>
       <c r="B55" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410717</v>
+        <v>411730</v>
       </c>
       <c r="R55" t="n">
-        <v>6781843</v>
+        <v>6781958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,9 +6108,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6125,22 +6135,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032192</v>
+        <v>129011213</v>
       </c>
       <c r="B56" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6172,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411504</v>
+        <v>411327</v>
       </c>
       <c r="R56" t="n">
-        <v>6781807</v>
+        <v>6781657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6205,9 +6215,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6222,22 +6242,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011225</v>
+        <v>129032192</v>
       </c>
       <c r="B57" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6269,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411536</v>
+        <v>411504</v>
       </c>
       <c r="R57" t="n">
-        <v>6781806</v>
+        <v>6781807</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6302,19 +6322,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6329,22 +6339,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011213</v>
+        <v>129032750</v>
       </c>
       <c r="B58" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6376,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411327</v>
+        <v>410717</v>
       </c>
       <c r="R58" t="n">
-        <v>6781657</v>
+        <v>6781843</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6409,19 +6419,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
         <v>129032185</v>
       </c>
       <c r="B59" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>129032778</v>
       </c>
       <c r="B60" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6642,10 +6642,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032770</v>
+        <v>129011218</v>
       </c>
       <c r="B61" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411070</v>
+        <v>411322</v>
       </c>
       <c r="R61" t="n">
-        <v>6781879</v>
+        <v>6781695</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,9 +6710,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6727,22 +6737,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B62" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6774,10 +6784,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R62" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,19 +6817,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,12 +6834,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6849,7 +6849,7 @@
         <v>129032740</v>
       </c>
       <c r="B63" t="n">
-        <v>79067</v>
+        <v>79071</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>129011220</v>
       </c>
       <c r="B64" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7053,7 +7053,7 @@
         <v>129032765</v>
       </c>
       <c r="B65" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7147,32 +7147,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032200</v>
+        <v>129032772</v>
       </c>
       <c r="B66" t="n">
-        <v>92819</v>
+        <v>79039</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411326</v>
+        <v>411565</v>
       </c>
       <c r="R66" t="n">
-        <v>6781874</v>
+        <v>6781780</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,22 +7232,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032772</v>
+        <v>129032746</v>
       </c>
       <c r="B67" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411565</v>
+        <v>410697</v>
       </c>
       <c r="R67" t="n">
-        <v>6781780</v>
+        <v>6781752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032746</v>
+        <v>129032189</v>
       </c>
       <c r="B68" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410697</v>
+        <v>411250</v>
       </c>
       <c r="R68" t="n">
-        <v>6781752</v>
+        <v>6781886</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,12 +7426,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7441,7 +7441,7 @@
         <v>129032760</v>
       </c>
       <c r="B69" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7535,32 +7535,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032189</v>
+        <v>129032200</v>
       </c>
       <c r="B70" t="n">
-        <v>79035</v>
+        <v>92826</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411250</v>
+        <v>411326</v>
       </c>
       <c r="R70" t="n">
-        <v>6781886</v>
+        <v>6781874</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7635,7 +7635,7 @@
         <v>129032783</v>
       </c>
       <c r="B71" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7732,7 +7732,7 @@
         <v>129032757</v>
       </c>
       <c r="B72" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7826,10 +7826,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032741</v>
+        <v>129032186</v>
       </c>
       <c r="B73" t="n">
-        <v>57720</v>
+        <v>79039</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7837,42 +7837,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>410958</v>
+        <v>411332</v>
       </c>
       <c r="R73" t="n">
-        <v>6781689</v>
+        <v>6781694</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7919,22 +7911,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032186</v>
+        <v>129032741</v>
       </c>
       <c r="B74" t="n">
-        <v>79035</v>
+        <v>57722</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7942,34 +7934,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>411332</v>
+        <v>410958</v>
       </c>
       <c r="R74" t="n">
-        <v>6781694</v>
+        <v>6781689</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032767</v>
+        <v>129032181</v>
       </c>
       <c r="B75" t="n">
-        <v>79035</v>
+        <v>79658</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R75" t="n">
-        <v>6781848</v>
+        <v>6781806</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,22 +8113,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032768</v>
+        <v>129032767</v>
       </c>
       <c r="B76" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781857</v>
+        <v>6781848</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032181</v>
+        <v>129032768</v>
       </c>
       <c r="B77" t="n">
-        <v>79654</v>
+        <v>79039</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8233,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R77" t="n">
-        <v>6781806</v>
+        <v>6781857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8307,12 +8307,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8322,7 +8322,7 @@
         <v>129011230</v>
       </c>
       <c r="B78" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011216</v>
       </c>
       <c r="B34" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>411316</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129011229</v>
       </c>
       <c r="B35" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>412001</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,19 +4105,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011216</v>
+        <v>129032187</v>
       </c>
       <c r="B36" t="n">
         <v>79039</v>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411316</v>
+        <v>411321</v>
       </c>
       <c r="R36" t="n">
-        <v>6781674</v>
+        <v>6781689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4185,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011229</v>
+        <v>129032764</v>
       </c>
       <c r="B37" t="n">
         <v>79039</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>412001</v>
+        <v>410852</v>
       </c>
       <c r="R37" t="n">
-        <v>6781693</v>
+        <v>6781859</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,19 +4282,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4309,19 +4299,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032187</v>
+        <v>129032774</v>
       </c>
       <c r="B38" t="n">
         <v>79039</v>
@@ -4356,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411321</v>
+        <v>411548</v>
       </c>
       <c r="R38" t="n">
-        <v>6781689</v>
+        <v>6781798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,22 +4396,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032764</v>
+        <v>129011197</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4429,21 +4419,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4453,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410852</v>
+        <v>411531</v>
       </c>
       <c r="R39" t="n">
-        <v>6781859</v>
+        <v>6781805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,9 +4476,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032774</v>
+        <v>129032739</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411548</v>
+        <v>410877</v>
       </c>
       <c r="R40" t="n">
-        <v>6781798</v>
+        <v>6781741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -7147,32 +7147,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032772</v>
+        <v>129032200</v>
       </c>
       <c r="B66" t="n">
-        <v>79039</v>
+        <v>92826</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411565</v>
+        <v>411326</v>
       </c>
       <c r="R66" t="n">
-        <v>6781780</v>
+        <v>6781874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,19 +7232,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032746</v>
+        <v>129032772</v>
       </c>
       <c r="B67" t="n">
         <v>79039</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410697</v>
+        <v>411565</v>
       </c>
       <c r="R67" t="n">
-        <v>6781752</v>
+        <v>6781780</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032189</v>
+        <v>129032746</v>
       </c>
       <c r="B68" t="n">
         <v>79039</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411250</v>
+        <v>410697</v>
       </c>
       <c r="R68" t="n">
-        <v>6781886</v>
+        <v>6781752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,19 +7426,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032760</v>
+        <v>129032189</v>
       </c>
       <c r="B69" t="n">
         <v>79039</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410875</v>
+        <v>411250</v>
       </c>
       <c r="R69" t="n">
-        <v>6781746</v>
+        <v>6781886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,44 +7523,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032200</v>
+        <v>129032760</v>
       </c>
       <c r="B70" t="n">
-        <v>92826</v>
+        <v>79039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411326</v>
+        <v>410875</v>
       </c>
       <c r="R70" t="n">
-        <v>6781874</v>
+        <v>6781746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,12 +7620,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032775</v>
+        <v>129032199</v>
       </c>
       <c r="B2" t="n">
         <v>79039</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411542</v>
+        <v>412062</v>
       </c>
       <c r="R2" t="n">
-        <v>6781824</v>
+        <v>6781678</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032199</v>
+        <v>129032775</v>
       </c>
       <c r="B4" t="n">
         <v>79039</v>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412062</v>
+        <v>411542</v>
       </c>
       <c r="R4" t="n">
-        <v>6781678</v>
+        <v>6781824</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,12 +964,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1675,56 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032786</v>
+        <v>129011211</v>
       </c>
       <c r="B12" t="n">
-        <v>92826</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410970</v>
+        <v>411303</v>
       </c>
       <c r="R12" t="n">
-        <v>6781684</v>
+        <v>6781649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,37 +1743,46 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011211</v>
+        <v>129011208</v>
       </c>
       <c r="B13" t="n">
         <v>79039</v>
@@ -1819,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411303</v>
+        <v>411221</v>
       </c>
       <c r="R13" t="n">
-        <v>6781649</v>
+        <v>6781624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,7 +1852,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1864,7 +1862,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011208</v>
+        <v>129011209</v>
       </c>
       <c r="B14" t="n">
         <v>79039</v>
@@ -1926,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411221</v>
+        <v>411237</v>
       </c>
       <c r="R14" t="n">
-        <v>6781624</v>
+        <v>6781635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,7 +1959,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1971,7 +1969,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,7 +1996,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011209</v>
+        <v>129011212</v>
       </c>
       <c r="B15" t="n">
         <v>79039</v>
@@ -2033,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411237</v>
+        <v>411313</v>
       </c>
       <c r="R15" t="n">
-        <v>6781635</v>
+        <v>6781661</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2066,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2078,7 +2076,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2105,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011212</v>
+        <v>129032749</v>
       </c>
       <c r="B16" t="n">
         <v>79039</v>
@@ -2140,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411313</v>
+        <v>410719</v>
       </c>
       <c r="R16" t="n">
-        <v>6781661</v>
+        <v>6781851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,19 +2171,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,57 +2188,68 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032749</v>
+        <v>129032786</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>92833</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410719</v>
+        <v>410970</v>
       </c>
       <c r="R17" t="n">
-        <v>6781851</v>
+        <v>6781684</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,6 +2290,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032758</v>
+        <v>129011207</v>
       </c>
       <c r="B18" t="n">
         <v>79039</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410842</v>
+        <v>411175</v>
       </c>
       <c r="R18" t="n">
-        <v>6781713</v>
+        <v>6781624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,9 +2377,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,12 +2404,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2513,7 +2523,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032751</v>
+        <v>129032758</v>
       </c>
       <c r="B20" t="n">
         <v>79039</v>
@@ -2548,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410727</v>
+        <v>410842</v>
       </c>
       <c r="R20" t="n">
-        <v>6781837</v>
+        <v>6781713</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2610,7 +2620,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032780</v>
+        <v>129032751</v>
       </c>
       <c r="B21" t="n">
         <v>79039</v>
@@ -2645,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>411808</v>
+        <v>410727</v>
       </c>
       <c r="R21" t="n">
-        <v>6781897</v>
+        <v>6781837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2707,7 +2717,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011207</v>
+        <v>129032780</v>
       </c>
       <c r="B22" t="n">
         <v>79039</v>
@@ -2742,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411175</v>
+        <v>411808</v>
       </c>
       <c r="R22" t="n">
-        <v>6781624</v>
+        <v>6781897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,19 +2785,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,68 +2802,57 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032787</v>
+        <v>129011222</v>
       </c>
       <c r="B23" t="n">
-        <v>92826</v>
+        <v>79039</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410912</v>
+        <v>411303</v>
       </c>
       <c r="R23" t="n">
-        <v>6781662</v>
+        <v>6781896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,75 +2882,95 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032754</v>
+        <v>129032787</v>
       </c>
       <c r="B24" t="n">
-        <v>79039</v>
+        <v>92833</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410774</v>
+        <v>410912</v>
       </c>
       <c r="R24" t="n">
-        <v>6781776</v>
+        <v>6781662</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,6 +3011,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3020,7 +3030,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011222</v>
+        <v>129032754</v>
       </c>
       <c r="B25" t="n">
         <v>79039</v>
@@ -3055,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411303</v>
+        <v>410774</v>
       </c>
       <c r="R25" t="n">
-        <v>6781896</v>
+        <v>6781776</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,19 +3098,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,12 +3115,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032180</v>
+        <v>129032779</v>
       </c>
       <c r="B31" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411312</v>
+        <v>411808</v>
       </c>
       <c r="R31" t="n">
-        <v>6781871</v>
+        <v>6781920</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,12 +3697,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032779</v>
+        <v>129032180</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411808</v>
+        <v>411312</v>
       </c>
       <c r="R33" t="n">
-        <v>6781920</v>
+        <v>6781871</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011216</v>
+        <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411316</v>
+        <v>411531</v>
       </c>
       <c r="R34" t="n">
-        <v>6781674</v>
+        <v>6781805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011229</v>
+        <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>412001</v>
+        <v>410877</v>
       </c>
       <c r="R35" t="n">
-        <v>6781693</v>
+        <v>6781741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,19 +4078,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,19 +4095,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032187</v>
+        <v>129011216</v>
       </c>
       <c r="B36" t="n">
         <v>79039</v>
@@ -4152,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411321</v>
+        <v>411316</v>
       </c>
       <c r="R36" t="n">
-        <v>6781689</v>
+        <v>6781674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4185,9 +4175,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032764</v>
+        <v>129011229</v>
       </c>
       <c r="B37" t="n">
         <v>79039</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410852</v>
+        <v>412001</v>
       </c>
       <c r="R37" t="n">
-        <v>6781859</v>
+        <v>6781693</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,9 +4282,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,19 +4309,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032774</v>
+        <v>129032187</v>
       </c>
       <c r="B38" t="n">
         <v>79039</v>
@@ -4346,10 +4356,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411548</v>
+        <v>411321</v>
       </c>
       <c r="R38" t="n">
-        <v>6781798</v>
+        <v>6781689</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,22 +4406,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011197</v>
+        <v>129032774</v>
       </c>
       <c r="B39" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,21 +4429,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411531</v>
+        <v>411548</v>
       </c>
       <c r="R39" t="n">
-        <v>6781805</v>
+        <v>6781798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,19 +4486,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032739</v>
+        <v>129032764</v>
       </c>
       <c r="B40" t="n">
-        <v>79071</v>
+        <v>79039</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410877</v>
+        <v>410852</v>
       </c>
       <c r="R40" t="n">
-        <v>6781741</v>
+        <v>6781859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011215</v>
+        <v>128978125</v>
       </c>
       <c r="B41" t="n">
-        <v>79039</v>
+        <v>79071</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411330</v>
+        <v>411776</v>
       </c>
       <c r="R41" t="n">
-        <v>6781666</v>
+        <v>6781941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,7 +4719,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011221</v>
+        <v>129011215</v>
       </c>
       <c r="B42" t="n">
         <v>79039</v>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411310</v>
+        <v>411330</v>
       </c>
       <c r="R42" t="n">
-        <v>6781709</v>
+        <v>6781666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011202</v>
+        <v>129011221</v>
       </c>
       <c r="B43" t="n">
-        <v>78796</v>
+        <v>79039</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411246</v>
+        <v>411310</v>
       </c>
       <c r="R43" t="n">
-        <v>6781879</v>
+        <v>6781709</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5030,10 +5030,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128978125</v>
+        <v>129011202</v>
       </c>
       <c r="B45" t="n">
-        <v>79071</v>
+        <v>78796</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5041,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411776</v>
+        <v>411246</v>
       </c>
       <c r="R45" t="n">
-        <v>6781941</v>
+        <v>6781879</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5331,7 +5331,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011224</v>
+        <v>129032184</v>
       </c>
       <c r="B48" t="n">
         <v>79039</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411539</v>
+        <v>411414</v>
       </c>
       <c r="R48" t="n">
-        <v>6781802</v>
+        <v>6781817</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,19 +5399,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5426,19 +5416,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032184</v>
+        <v>129032191</v>
       </c>
       <c r="B49" t="n">
         <v>79039</v>
@@ -5473,10 +5463,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411414</v>
+        <v>411495</v>
       </c>
       <c r="R49" t="n">
-        <v>6781817</v>
+        <v>6781803</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5535,7 +5525,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011206</v>
+        <v>129011224</v>
       </c>
       <c r="B50" t="n">
         <v>79039</v>
@@ -5570,10 +5560,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411166</v>
+        <v>411539</v>
       </c>
       <c r="R50" t="n">
-        <v>6781615</v>
+        <v>6781802</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5605,7 +5595,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5615,7 +5605,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5642,7 +5632,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032191</v>
+        <v>129011206</v>
       </c>
       <c r="B51" t="n">
         <v>79039</v>
@@ -5677,10 +5667,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411495</v>
+        <v>411166</v>
       </c>
       <c r="R51" t="n">
-        <v>6781803</v>
+        <v>6781615</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5710,9 +5700,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5727,12 +5727,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6254,7 +6254,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032192</v>
+        <v>129032750</v>
       </c>
       <c r="B57" t="n">
         <v>79039</v>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411504</v>
+        <v>410717</v>
       </c>
       <c r="R57" t="n">
-        <v>6781807</v>
+        <v>6781843</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6339,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032750</v>
+        <v>129032192</v>
       </c>
       <c r="B58" t="n">
         <v>79039</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410717</v>
+        <v>411504</v>
       </c>
       <c r="R58" t="n">
-        <v>6781843</v>
+        <v>6781807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7150,7 +7150,7 @@
         <v>129032200</v>
       </c>
       <c r="B66" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7632,10 +7632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032783</v>
+        <v>129032741</v>
       </c>
       <c r="B71" t="n">
-        <v>79039</v>
+        <v>57722</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,34 +7643,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411996</v>
+        <v>410958</v>
       </c>
       <c r="R71" t="n">
-        <v>6781690</v>
+        <v>6781689</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7729,7 +7737,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032757</v>
+        <v>129032783</v>
       </c>
       <c r="B72" t="n">
         <v>79039</v>
@@ -7764,10 +7772,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410790</v>
+        <v>411996</v>
       </c>
       <c r="R72" t="n">
-        <v>6781786</v>
+        <v>6781690</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7826,7 +7834,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032186</v>
+        <v>129032757</v>
       </c>
       <c r="B73" t="n">
         <v>79039</v>
@@ -7861,10 +7869,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411332</v>
+        <v>410790</v>
       </c>
       <c r="R73" t="n">
-        <v>6781694</v>
+        <v>6781786</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,22 +7919,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032741</v>
+        <v>129032186</v>
       </c>
       <c r="B74" t="n">
-        <v>57722</v>
+        <v>79039</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7934,42 +7942,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410958</v>
+        <v>411332</v>
       </c>
       <c r="R74" t="n">
-        <v>6781689</v>
+        <v>6781694</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032181</v>
+        <v>129032767</v>
       </c>
       <c r="B75" t="n">
-        <v>79658</v>
+        <v>79039</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R75" t="n">
-        <v>6781806</v>
+        <v>6781848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032767</v>
+        <v>129032768</v>
       </c>
       <c r="B76" t="n">
         <v>79039</v>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781848</v>
+        <v>6781857</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032768</v>
+        <v>129011230</v>
       </c>
       <c r="B77" t="n">
         <v>79039</v>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R77" t="n">
-        <v>6781857</v>
+        <v>6781667</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,9 +8290,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8307,22 +8317,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011230</v>
+        <v>129032181</v>
       </c>
       <c r="B78" t="n">
-        <v>79039</v>
+        <v>79658</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,21 +8340,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8354,10 +8364,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412017</v>
+        <v>411425</v>
       </c>
       <c r="R78" t="n">
-        <v>6781667</v>
+        <v>6781806</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8387,19 +8397,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032199</v>
+        <v>129032775</v>
       </c>
       <c r="B2" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412062</v>
+        <v>411542</v>
       </c>
       <c r="R2" t="n">
-        <v>6781678</v>
+        <v>6781824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -775,7 +775,7 @@
         <v>129011223</v>
       </c>
       <c r="B3" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032775</v>
+        <v>129032199</v>
       </c>
       <c r="B4" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -914,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411542</v>
+        <v>412062</v>
       </c>
       <c r="R4" t="n">
-        <v>6781824</v>
+        <v>6781678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,12 +964,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -979,7 +979,7 @@
         <v>129032188</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1076,7 +1076,7 @@
         <v>129032756</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
         <v>129032745</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
         <v>129032781</v>
       </c>
       <c r="B8" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,7 +1367,7 @@
         <v>129011228</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1474,7 +1474,7 @@
         <v>129032766</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1571,7 +1571,7 @@
         <v>129011217</v>
       </c>
       <c r="B11" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         <v>129011211</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>129011208</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>129011209</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>129011212</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
         <v>129032749</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2203,7 +2203,7 @@
         <v>129032786</v>
       </c>
       <c r="B17" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011207</v>
+        <v>129032758</v>
       </c>
       <c r="B18" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411175</v>
+        <v>410842</v>
       </c>
       <c r="R18" t="n">
-        <v>6781624</v>
+        <v>6781713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,19 +2377,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,12 +2394,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2419,7 +2409,7 @@
         <v>129011219</v>
       </c>
       <c r="B19" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2523,10 +2513,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032758</v>
+        <v>129032751</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2558,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410842</v>
+        <v>410727</v>
       </c>
       <c r="R20" t="n">
-        <v>6781713</v>
+        <v>6781837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2620,10 +2610,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032751</v>
+        <v>129032780</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2655,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410727</v>
+        <v>411808</v>
       </c>
       <c r="R21" t="n">
-        <v>6781837</v>
+        <v>6781897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,10 +2707,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032780</v>
+        <v>129011207</v>
       </c>
       <c r="B22" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,10 +2742,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411808</v>
+        <v>411175</v>
       </c>
       <c r="R22" t="n">
-        <v>6781897</v>
+        <v>6781624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,9 +2775,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,22 +2802,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011222</v>
+        <v>129032754</v>
       </c>
       <c r="B23" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>411303</v>
+        <v>410774</v>
       </c>
       <c r="R23" t="n">
-        <v>6781896</v>
+        <v>6781776</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,19 +2882,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2909,68 +2899,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032787</v>
+        <v>129011222</v>
       </c>
       <c r="B24" t="n">
-        <v>92833</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410912</v>
+        <v>411303</v>
       </c>
       <c r="R24" t="n">
-        <v>6781662</v>
+        <v>6781896</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,40 +2979,49 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032754</v>
+        <v>129032755</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3065,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410774</v>
+        <v>410678</v>
       </c>
       <c r="R25" t="n">
-        <v>6781776</v>
+        <v>6781823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,10 +3115,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B26" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3162,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R26" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,10 +3212,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032759</v>
+        <v>129032761</v>
       </c>
       <c r="B27" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410870</v>
+        <v>410889</v>
       </c>
       <c r="R27" t="n">
-        <v>6781738</v>
+        <v>6781774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,45 +3309,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032761</v>
+        <v>129032787</v>
       </c>
       <c r="B28" t="n">
-        <v>79039</v>
+        <v>92835</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410889</v>
+        <v>410912</v>
       </c>
       <c r="R28" t="n">
-        <v>6781774</v>
+        <v>6781662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3400,6 +3399,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>129032762</v>
       </c>
       <c r="B29" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>129032771</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032779</v>
+        <v>129032180</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411808</v>
+        <v>411312</v>
       </c>
       <c r="R31" t="n">
-        <v>6781920</v>
+        <v>6781871</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,12 +3697,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3712,7 +3712,7 @@
         <v>129032201</v>
       </c>
       <c r="B32" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032180</v>
+        <v>129032779</v>
       </c>
       <c r="B33" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411312</v>
+        <v>411808</v>
       </c>
       <c r="R33" t="n">
-        <v>6781871</v>
+        <v>6781920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011216</v>
       </c>
       <c r="B34" t="n">
-        <v>79071</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>411316</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129011229</v>
       </c>
       <c r="B35" t="n">
-        <v>79071</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>412001</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,22 +4105,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011216</v>
+        <v>129032187</v>
       </c>
       <c r="B36" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411316</v>
+        <v>411321</v>
       </c>
       <c r="R36" t="n">
-        <v>6781674</v>
+        <v>6781689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4185,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,22 +4202,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011229</v>
+        <v>129032764</v>
       </c>
       <c r="B37" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>412001</v>
+        <v>410852</v>
       </c>
       <c r="R37" t="n">
-        <v>6781693</v>
+        <v>6781859</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,19 +4282,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4309,22 +4299,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032187</v>
+        <v>129032774</v>
       </c>
       <c r="B38" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4356,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411321</v>
+        <v>411548</v>
       </c>
       <c r="R38" t="n">
-        <v>6781689</v>
+        <v>6781798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,22 +4396,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032774</v>
+        <v>129011197</v>
       </c>
       <c r="B39" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4429,21 +4419,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4453,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411548</v>
+        <v>411531</v>
       </c>
       <c r="R39" t="n">
-        <v>6781798</v>
+        <v>6781805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,9 +4476,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032764</v>
+        <v>129032739</v>
       </c>
       <c r="B40" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410852</v>
+        <v>410877</v>
       </c>
       <c r="R40" t="n">
-        <v>6781859</v>
+        <v>6781741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4615,7 +4615,7 @@
         <v>128978125</v>
       </c>
       <c r="B41" t="n">
-        <v>79071</v>
+        <v>79073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4722,7 +4722,7 @@
         <v>129011215</v>
       </c>
       <c r="B42" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>129011221</v>
       </c>
       <c r="B43" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4933,10 +4933,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032183</v>
+        <v>129011202</v>
       </c>
       <c r="B44" t="n">
-        <v>79658</v>
+        <v>78798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>412070</v>
+        <v>411246</v>
       </c>
       <c r="R44" t="n">
-        <v>6781682</v>
+        <v>6781879</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5001,9 +5001,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5018,22 +5028,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011202</v>
+        <v>129032183</v>
       </c>
       <c r="B45" t="n">
-        <v>78796</v>
+        <v>79660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5041,21 +5051,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411246</v>
+        <v>412070</v>
       </c>
       <c r="R45" t="n">
-        <v>6781879</v>
+        <v>6781682</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,19 +5108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5140,7 +5140,7 @@
         <v>129032748</v>
       </c>
       <c r="B46" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>129032752</v>
       </c>
       <c r="B47" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032184</v>
+        <v>129011224</v>
       </c>
       <c r="B48" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411414</v>
+        <v>411539</v>
       </c>
       <c r="R48" t="n">
-        <v>6781817</v>
+        <v>6781802</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,9 +5399,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5416,22 +5426,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032191</v>
+        <v>129032184</v>
       </c>
       <c r="B49" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5463,10 +5473,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411495</v>
+        <v>411414</v>
       </c>
       <c r="R49" t="n">
-        <v>6781803</v>
+        <v>6781817</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5525,10 +5535,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011224</v>
+        <v>129011206</v>
       </c>
       <c r="B50" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5560,10 +5570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411539</v>
+        <v>411166</v>
       </c>
       <c r="R50" t="n">
-        <v>6781802</v>
+        <v>6781615</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5595,7 +5605,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5605,7 +5615,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5632,10 +5642,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011206</v>
+        <v>129032191</v>
       </c>
       <c r="B51" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5667,10 +5677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411166</v>
+        <v>411495</v>
       </c>
       <c r="R51" t="n">
-        <v>6781615</v>
+        <v>6781803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5700,19 +5710,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5727,12 +5727,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5742,7 +5742,7 @@
         <v>129032769</v>
       </c>
       <c r="B52" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5839,7 +5839,7 @@
         <v>129032196</v>
       </c>
       <c r="B53" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>129011225</v>
       </c>
       <c r="B54" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6043,7 +6043,7 @@
         <v>129011227</v>
       </c>
       <c r="B55" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6150,7 +6150,7 @@
         <v>129011213</v>
       </c>
       <c r="B56" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6254,10 +6254,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032750</v>
+        <v>129032192</v>
       </c>
       <c r="B57" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6289,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410717</v>
+        <v>411504</v>
       </c>
       <c r="R57" t="n">
-        <v>6781843</v>
+        <v>6781807</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6339,22 +6339,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032192</v>
+        <v>129032750</v>
       </c>
       <c r="B58" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411504</v>
+        <v>410717</v>
       </c>
       <c r="R58" t="n">
-        <v>6781807</v>
+        <v>6781843</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
         <v>129032185</v>
       </c>
       <c r="B59" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>129032778</v>
       </c>
       <c r="B60" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>129011218</v>
       </c>
       <c r="B61" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>129032770</v>
       </c>
       <c r="B62" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032740</v>
+        <v>129011220</v>
       </c>
       <c r="B63" t="n">
-        <v>79071</v>
+        <v>79041</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411020</v>
+        <v>411312</v>
       </c>
       <c r="R63" t="n">
-        <v>6781851</v>
+        <v>6781706</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,9 +6914,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6931,22 +6941,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B64" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6978,10 +6988,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R64" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,19 +7021,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,22 +7038,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032765</v>
+        <v>129032740</v>
       </c>
       <c r="B65" t="n">
-        <v>79039</v>
+        <v>79073</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410893</v>
+        <v>411020</v>
       </c>
       <c r="R65" t="n">
-        <v>6781859</v>
+        <v>6781851</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7147,32 +7147,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032200</v>
+        <v>129032772</v>
       </c>
       <c r="B66" t="n">
-        <v>92833</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411326</v>
+        <v>411565</v>
       </c>
       <c r="R66" t="n">
-        <v>6781874</v>
+        <v>6781780</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,22 +7232,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032772</v>
+        <v>129032746</v>
       </c>
       <c r="B67" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411565</v>
+        <v>410697</v>
       </c>
       <c r="R67" t="n">
-        <v>6781780</v>
+        <v>6781752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032746</v>
+        <v>129032189</v>
       </c>
       <c r="B68" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410697</v>
+        <v>411250</v>
       </c>
       <c r="R68" t="n">
-        <v>6781752</v>
+        <v>6781886</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,22 +7426,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032189</v>
+        <v>129032760</v>
       </c>
       <c r="B69" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411250</v>
+        <v>410875</v>
       </c>
       <c r="R69" t="n">
-        <v>6781886</v>
+        <v>6781746</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,44 +7523,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032760</v>
+        <v>129032200</v>
       </c>
       <c r="B70" t="n">
-        <v>79039</v>
+        <v>92835</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410875</v>
+        <v>411326</v>
       </c>
       <c r="R70" t="n">
-        <v>6781746</v>
+        <v>6781874</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,22 +7620,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032741</v>
+        <v>129032783</v>
       </c>
       <c r="B71" t="n">
-        <v>57722</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,42 +7643,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410958</v>
+        <v>411996</v>
       </c>
       <c r="R71" t="n">
-        <v>6781689</v>
+        <v>6781690</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,10 +7729,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032783</v>
+        <v>129032757</v>
       </c>
       <c r="B72" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7772,10 +7764,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>411996</v>
+        <v>410790</v>
       </c>
       <c r="R72" t="n">
-        <v>6781690</v>
+        <v>6781786</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7834,10 +7826,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032757</v>
+        <v>129032186</v>
       </c>
       <c r="B73" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7869,10 +7861,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>410790</v>
+        <v>411332</v>
       </c>
       <c r="R73" t="n">
-        <v>6781786</v>
+        <v>6781694</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7919,22 +7911,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032186</v>
+        <v>129032741</v>
       </c>
       <c r="B74" t="n">
-        <v>79039</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7942,34 +7934,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>411332</v>
+        <v>410958</v>
       </c>
       <c r="R74" t="n">
-        <v>6781694</v>
+        <v>6781689</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032767</v>
+        <v>129032181</v>
       </c>
       <c r="B75" t="n">
-        <v>79039</v>
+        <v>79660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R75" t="n">
-        <v>6781848</v>
+        <v>6781806</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,22 +8113,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032768</v>
+        <v>129032767</v>
       </c>
       <c r="B76" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781857</v>
+        <v>6781848</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129011230</v>
+        <v>129032768</v>
       </c>
       <c r="B77" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>412017</v>
+        <v>410959</v>
       </c>
       <c r="R77" t="n">
-        <v>6781667</v>
+        <v>6781857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,19 +8290,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8317,22 +8307,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032181</v>
+        <v>129011230</v>
       </c>
       <c r="B78" t="n">
-        <v>79658</v>
+        <v>79041</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8340,21 +8330,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8364,10 +8354,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411425</v>
+        <v>412017</v>
       </c>
       <c r="R78" t="n">
-        <v>6781806</v>
+        <v>6781667</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,9 +8387,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032188</v>
+        <v>129032745</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411295</v>
+        <v>411010</v>
       </c>
       <c r="R5" t="n">
-        <v>6781724</v>
+        <v>6781686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032745</v>
+        <v>129032188</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411010</v>
+        <v>411295</v>
       </c>
       <c r="R7" t="n">
-        <v>6781686</v>
+        <v>6781724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011228</v>
+        <v>129011217</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411779</v>
+        <v>411318</v>
       </c>
       <c r="R9" t="n">
-        <v>6781900</v>
+        <v>6781689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032766</v>
+        <v>129011228</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410949</v>
+        <v>411779</v>
       </c>
       <c r="R10" t="n">
-        <v>6781860</v>
+        <v>6781900</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,9 +1539,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,19 +1566,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011217</v>
+        <v>129032766</v>
       </c>
       <c r="B11" t="n">
         <v>79041</v>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411318</v>
+        <v>410949</v>
       </c>
       <c r="R11" t="n">
-        <v>6781689</v>
+        <v>6781860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1636,19 +1646,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,57 +1663,68 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011211</v>
+        <v>129032786</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>411303</v>
+        <v>410970</v>
       </c>
       <c r="R12" t="n">
-        <v>6781649</v>
+        <v>6781684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,46 +1754,37 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011208</v>
+        <v>129032749</v>
       </c>
       <c r="B13" t="n">
         <v>79041</v>
@@ -1817,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411221</v>
+        <v>410719</v>
       </c>
       <c r="R13" t="n">
-        <v>6781624</v>
+        <v>6781851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,19 +1852,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1877,19 +1869,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011209</v>
+        <v>129011212</v>
       </c>
       <c r="B14" t="n">
         <v>79041</v>
@@ -1924,10 +1916,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411237</v>
+        <v>411313</v>
       </c>
       <c r="R14" t="n">
-        <v>6781635</v>
+        <v>6781661</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1951,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1969,7 +1961,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1988,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011212</v>
+        <v>129011209</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2031,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411313</v>
+        <v>411237</v>
       </c>
       <c r="R15" t="n">
-        <v>6781661</v>
+        <v>6781635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2058,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2076,7 +2068,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2095,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032749</v>
+        <v>129011208</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2138,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410719</v>
+        <v>411221</v>
       </c>
       <c r="R16" t="n">
-        <v>6781851</v>
+        <v>6781624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2171,9 +2163,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,68 +2190,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032786</v>
+        <v>129011211</v>
       </c>
       <c r="B17" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410970</v>
+        <v>411303</v>
       </c>
       <c r="R17" t="n">
-        <v>6781684</v>
+        <v>6781649</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2279,37 +2270,46 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032758</v>
+        <v>129011207</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410842</v>
+        <v>411175</v>
       </c>
       <c r="R18" t="n">
-        <v>6781713</v>
+        <v>6781624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,9 +2377,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,19 +2404,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011219</v>
+        <v>129032751</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2441,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411315</v>
+        <v>410727</v>
       </c>
       <c r="R19" t="n">
-        <v>6781704</v>
+        <v>6781837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,19 +2484,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,19 +2501,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032751</v>
+        <v>129011219</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410727</v>
+        <v>411315</v>
       </c>
       <c r="R20" t="n">
-        <v>6781837</v>
+        <v>6781704</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,9 +2581,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,12 +2608,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2707,7 +2717,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011207</v>
+        <v>129032758</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2742,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411175</v>
+        <v>410842</v>
       </c>
       <c r="R22" t="n">
-        <v>6781624</v>
+        <v>6781713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,19 +2785,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,57 +2802,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032754</v>
+        <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>92835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410774</v>
+        <v>410912</v>
       </c>
       <c r="R23" t="n">
-        <v>6781776</v>
+        <v>6781662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2904,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2911,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011222</v>
+        <v>129032761</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -2946,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411303</v>
+        <v>410889</v>
       </c>
       <c r="R24" t="n">
-        <v>6781896</v>
+        <v>6781774</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,19 +2991,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3006,19 +3008,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3053,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R25" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032759</v>
+        <v>129032755</v>
       </c>
       <c r="B26" t="n">
         <v>79041</v>
@@ -3150,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410870</v>
+        <v>410678</v>
       </c>
       <c r="R26" t="n">
-        <v>6781738</v>
+        <v>6781823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3214,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032761</v>
+        <v>129011222</v>
       </c>
       <c r="B27" t="n">
         <v>79041</v>
@@ -3247,10 +3249,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410889</v>
+        <v>411303</v>
       </c>
       <c r="R27" t="n">
-        <v>6781774</v>
+        <v>6781896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,9 +3282,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3297,68 +3309,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032787</v>
+        <v>129032754</v>
       </c>
       <c r="B28" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410912</v>
+        <v>410774</v>
       </c>
       <c r="R28" t="n">
-        <v>6781662</v>
+        <v>6781776</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,7 +3400,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032762</v>
+        <v>129032771</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410890</v>
+        <v>411508</v>
       </c>
       <c r="R29" t="n">
-        <v>6781771</v>
+        <v>6781794</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032771</v>
+        <v>129032762</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411508</v>
+        <v>410890</v>
       </c>
       <c r="R30" t="n">
-        <v>6781794</v>
+        <v>6781771</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032180</v>
+        <v>129032779</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411312</v>
+        <v>411808</v>
       </c>
       <c r="R31" t="n">
-        <v>6781871</v>
+        <v>6781920</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,12 +3697,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032779</v>
+        <v>129032180</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411808</v>
+        <v>411312</v>
       </c>
       <c r="R33" t="n">
-        <v>6781920</v>
+        <v>6781871</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011216</v>
+        <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411316</v>
+        <v>411531</v>
       </c>
       <c r="R34" t="n">
-        <v>6781674</v>
+        <v>6781805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011229</v>
+        <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>412001</v>
+        <v>410877</v>
       </c>
       <c r="R35" t="n">
-        <v>6781693</v>
+        <v>6781741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,19 +4078,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,12 +4095,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4214,7 +4204,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032764</v>
+        <v>129032774</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4249,10 +4239,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410852</v>
+        <v>411548</v>
       </c>
       <c r="R37" t="n">
-        <v>6781859</v>
+        <v>6781798</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4311,7 +4301,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032774</v>
+        <v>129011229</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4346,10 +4336,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411548</v>
+        <v>412001</v>
       </c>
       <c r="R38" t="n">
-        <v>6781798</v>
+        <v>6781693</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4379,9 +4369,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4396,22 +4396,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011197</v>
+        <v>129011216</v>
       </c>
       <c r="B39" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,21 +4419,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4443,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411531</v>
+        <v>411316</v>
       </c>
       <c r="R39" t="n">
-        <v>6781805</v>
+        <v>6781674</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4478,7 +4478,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4515,10 +4515,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032739</v>
+        <v>129032764</v>
       </c>
       <c r="B40" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410877</v>
+        <v>410852</v>
       </c>
       <c r="R40" t="n">
-        <v>6781741</v>
+        <v>6781859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011215</v>
+        <v>129011221</v>
       </c>
       <c r="B42" t="n">
         <v>79041</v>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411330</v>
+        <v>411310</v>
       </c>
       <c r="R42" t="n">
-        <v>6781666</v>
+        <v>6781709</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011221</v>
+        <v>129032183</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411310</v>
+        <v>412070</v>
       </c>
       <c r="R43" t="n">
-        <v>6781709</v>
+        <v>6781682</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,19 +4894,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4921,12 +4911,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5040,10 +5030,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032183</v>
+        <v>129011215</v>
       </c>
       <c r="B45" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412070</v>
+        <v>411330</v>
       </c>
       <c r="R45" t="n">
-        <v>6781682</v>
+        <v>6781666</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,9 +5098,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011224</v>
+        <v>129032769</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411539</v>
+        <v>411017</v>
       </c>
       <c r="R48" t="n">
-        <v>6781802</v>
+        <v>6781839</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,19 +5399,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5426,19 +5416,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032184</v>
+        <v>129011206</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5473,10 +5463,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411414</v>
+        <v>411166</v>
       </c>
       <c r="R49" t="n">
-        <v>6781817</v>
+        <v>6781615</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5506,9 +5496,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5523,19 +5523,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011206</v>
+        <v>129011224</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411166</v>
+        <v>411539</v>
       </c>
       <c r="R50" t="n">
-        <v>6781615</v>
+        <v>6781802</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032191</v>
+        <v>129032184</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411495</v>
+        <v>411414</v>
       </c>
       <c r="R51" t="n">
-        <v>6781803</v>
+        <v>6781817</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032769</v>
+        <v>129032191</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411017</v>
+        <v>411495</v>
       </c>
       <c r="R52" t="n">
-        <v>6781839</v>
+        <v>6781803</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011225</v>
+        <v>129032750</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411536</v>
+        <v>410717</v>
       </c>
       <c r="R54" t="n">
-        <v>6781806</v>
+        <v>6781843</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,19 +6001,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6028,19 +6018,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011227</v>
+        <v>129011213</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6075,10 +6065,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411730</v>
+        <v>411327</v>
       </c>
       <c r="R55" t="n">
-        <v>6781958</v>
+        <v>6781657</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6110,7 +6100,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6120,7 +6110,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6147,7 +6137,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011213</v>
+        <v>129011225</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6182,10 +6172,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411327</v>
+        <v>411536</v>
       </c>
       <c r="R56" t="n">
-        <v>6781657</v>
+        <v>6781806</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,7 +6207,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6227,7 +6217,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6254,7 +6244,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032192</v>
+        <v>129011227</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6289,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411504</v>
+        <v>411730</v>
       </c>
       <c r="R57" t="n">
-        <v>6781807</v>
+        <v>6781958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6322,9 +6312,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032750</v>
+        <v>129032192</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410717</v>
+        <v>411504</v>
       </c>
       <c r="R58" t="n">
-        <v>6781843</v>
+        <v>6781807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R61" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,19 +6710,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,19 +6727,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032770</v>
+        <v>129011218</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6784,10 +6774,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411070</v>
+        <v>411322</v>
       </c>
       <c r="R62" t="n">
-        <v>6781879</v>
+        <v>6781695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6817,9 +6807,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,19 +6834,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R63" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,19 +6914,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,19 +6931,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032765</v>
+        <v>129011220</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -6988,10 +6978,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410893</v>
+        <v>411312</v>
       </c>
       <c r="R64" t="n">
-        <v>6781859</v>
+        <v>6781706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7021,9 +7011,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,12 +7038,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7147,32 +7147,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032772</v>
+        <v>129032200</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>92835</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411565</v>
+        <v>411326</v>
       </c>
       <c r="R66" t="n">
-        <v>6781780</v>
+        <v>6781874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,19 +7232,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032746</v>
+        <v>129032189</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410697</v>
+        <v>411250</v>
       </c>
       <c r="R67" t="n">
-        <v>6781752</v>
+        <v>6781886</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7329,19 +7329,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032189</v>
+        <v>129032772</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411250</v>
+        <v>411565</v>
       </c>
       <c r="R68" t="n">
-        <v>6781886</v>
+        <v>6781780</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,19 +7426,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032760</v>
+        <v>129032746</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410875</v>
+        <v>410697</v>
       </c>
       <c r="R69" t="n">
-        <v>6781746</v>
+        <v>6781752</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7535,32 +7535,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032200</v>
+        <v>129032760</v>
       </c>
       <c r="B70" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411326</v>
+        <v>410875</v>
       </c>
       <c r="R70" t="n">
-        <v>6781874</v>
+        <v>6781746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,19 +7620,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032783</v>
+        <v>129032186</v>
       </c>
       <c r="B71" t="n">
         <v>79041</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411996</v>
+        <v>411332</v>
       </c>
       <c r="R71" t="n">
-        <v>6781690</v>
+        <v>6781694</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,22 +7717,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032757</v>
+        <v>129032741</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7740,34 +7740,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410790</v>
+        <v>410958</v>
       </c>
       <c r="R72" t="n">
-        <v>6781786</v>
+        <v>6781689</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7826,7 +7834,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032186</v>
+        <v>129032783</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7861,10 +7869,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411332</v>
+        <v>411996</v>
       </c>
       <c r="R73" t="n">
-        <v>6781694</v>
+        <v>6781690</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,22 +7919,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032741</v>
+        <v>129032757</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7934,42 +7942,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410958</v>
+        <v>410790</v>
       </c>
       <c r="R74" t="n">
-        <v>6781689</v>
+        <v>6781786</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8028,10 +8028,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032181</v>
+        <v>129032767</v>
       </c>
       <c r="B75" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R75" t="n">
-        <v>6781806</v>
+        <v>6781848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032767</v>
+        <v>129011230</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R76" t="n">
-        <v>6781848</v>
+        <v>6781667</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,9 +8193,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8210,22 +8220,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032768</v>
+        <v>129032181</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8243,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8267,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R77" t="n">
-        <v>6781857</v>
+        <v>6781806</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8307,19 +8317,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011230</v>
+        <v>129032768</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8354,10 +8364,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412017</v>
+        <v>410959</v>
       </c>
       <c r="R78" t="n">
-        <v>6781667</v>
+        <v>6781857</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8387,19 +8397,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -4107,7 +4107,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032187</v>
+        <v>129011229</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411321</v>
+        <v>412001</v>
       </c>
       <c r="R36" t="n">
-        <v>6781689</v>
+        <v>6781693</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,9 +4175,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4192,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032774</v>
+        <v>129032187</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4239,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411548</v>
+        <v>411321</v>
       </c>
       <c r="R37" t="n">
-        <v>6781798</v>
+        <v>6781689</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4289,19 +4299,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011229</v>
+        <v>129011216</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4336,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>412001</v>
+        <v>411316</v>
       </c>
       <c r="R38" t="n">
-        <v>6781693</v>
+        <v>6781674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4371,7 +4381,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4381,7 +4391,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4408,7 +4418,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011216</v>
+        <v>129032774</v>
       </c>
       <c r="B39" t="n">
         <v>79041</v>
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411316</v>
+        <v>411548</v>
       </c>
       <c r="R39" t="n">
-        <v>6781674</v>
+        <v>6781798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,19 +4486,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,12 +4503,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128978125</v>
+        <v>129011221</v>
       </c>
       <c r="B41" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411776</v>
+        <v>411310</v>
       </c>
       <c r="R41" t="n">
-        <v>6781941</v>
+        <v>6781709</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011221</v>
+        <v>129032183</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411310</v>
+        <v>412070</v>
       </c>
       <c r="R42" t="n">
-        <v>6781709</v>
+        <v>6781682</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,19 +4787,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4814,22 +4804,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032183</v>
+        <v>129011202</v>
       </c>
       <c r="B43" t="n">
-        <v>79660</v>
+        <v>78798</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4827,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4851,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>412070</v>
+        <v>411246</v>
       </c>
       <c r="R43" t="n">
-        <v>6781682</v>
+        <v>6781879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,9 +4884,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4911,22 +4911,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011202</v>
+        <v>129011215</v>
       </c>
       <c r="B44" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4934,21 +4934,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4958,10 +4958,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>411246</v>
+        <v>411330</v>
       </c>
       <c r="R44" t="n">
-        <v>6781879</v>
+        <v>6781666</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5030,10 +5030,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011215</v>
+        <v>128978125</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5041,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411330</v>
+        <v>411776</v>
       </c>
       <c r="R45" t="n">
-        <v>6781666</v>
+        <v>6781941</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5100,7 +5100,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -7632,10 +7632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032186</v>
+        <v>129032741</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,34 +7643,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411332</v>
+        <v>410958</v>
       </c>
       <c r="R71" t="n">
-        <v>6781694</v>
+        <v>6781689</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,22 +7725,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032741</v>
+        <v>129032186</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7740,42 +7748,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410958</v>
+        <v>411332</v>
       </c>
       <c r="R72" t="n">
-        <v>6781689</v>
+        <v>6781694</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7822,12 +7822,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032775</v>
+        <v>129032199</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411542</v>
+        <v>412062</v>
       </c>
       <c r="R2" t="n">
-        <v>6781824</v>
+        <v>6781678</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011223</v>
+        <v>129032775</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411437</v>
+        <v>411542</v>
       </c>
       <c r="R3" t="n">
-        <v>6781809</v>
+        <v>6781824</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -840,19 +840,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,19 +857,19 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032199</v>
+        <v>129011223</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -914,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412062</v>
+        <v>411437</v>
       </c>
       <c r="R4" t="n">
-        <v>6781678</v>
+        <v>6781809</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +937,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,19 +964,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032745</v>
+        <v>129032756</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411010</v>
+        <v>410745</v>
       </c>
       <c r="R5" t="n">
-        <v>6781686</v>
+        <v>6781852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032756</v>
+        <v>129032745</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410745</v>
+        <v>411010</v>
       </c>
       <c r="R6" t="n">
-        <v>6781852</v>
+        <v>6781686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032188</v>
+        <v>129032781</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411295</v>
+        <v>411940</v>
       </c>
       <c r="R7" t="n">
-        <v>6781724</v>
+        <v>6781749</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,19 +1255,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032781</v>
+        <v>129032188</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411940</v>
+        <v>411295</v>
       </c>
       <c r="R8" t="n">
-        <v>6781749</v>
+        <v>6781724</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,19 +1352,19 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011217</v>
+        <v>129011228</v>
       </c>
       <c r="B9" t="n">
         <v>79041</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411318</v>
+        <v>411779</v>
       </c>
       <c r="R9" t="n">
-        <v>6781689</v>
+        <v>6781900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011228</v>
+        <v>129011217</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411779</v>
+        <v>411318</v>
       </c>
       <c r="R10" t="n">
-        <v>6781900</v>
+        <v>6781689</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,56 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032786</v>
+        <v>129011211</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410970</v>
+        <v>411303</v>
       </c>
       <c r="R12" t="n">
-        <v>6781684</v>
+        <v>6781649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,75 +1743,95 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032749</v>
+        <v>129032786</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>92821</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410719</v>
+        <v>410970</v>
       </c>
       <c r="R13" t="n">
-        <v>6781851</v>
+        <v>6781684</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1863,6 +1872,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -1881,7 +1891,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011212</v>
+        <v>129011208</v>
       </c>
       <c r="B14" t="n">
         <v>79041</v>
@@ -1916,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411313</v>
+        <v>411221</v>
       </c>
       <c r="R14" t="n">
-        <v>6781661</v>
+        <v>6781624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,7 +1961,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1961,7 +1971,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,7 +2105,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011208</v>
+        <v>129011212</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2130,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411221</v>
+        <v>411313</v>
       </c>
       <c r="R16" t="n">
-        <v>6781624</v>
+        <v>6781661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,7 +2175,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2175,7 +2185,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2202,7 +2212,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129011211</v>
+        <v>129032749</v>
       </c>
       <c r="B17" t="n">
         <v>79041</v>
@@ -2237,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411303</v>
+        <v>410719</v>
       </c>
       <c r="R17" t="n">
-        <v>6781649</v>
+        <v>6781851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,19 +2280,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,19 +2297,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011207</v>
+        <v>129032758</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411175</v>
+        <v>410842</v>
       </c>
       <c r="R18" t="n">
-        <v>6781624</v>
+        <v>6781713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,19 +2377,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,19 +2394,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032751</v>
+        <v>129011219</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2451,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410727</v>
+        <v>411315</v>
       </c>
       <c r="R19" t="n">
-        <v>6781837</v>
+        <v>6781704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,9 +2474,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,19 +2501,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011219</v>
+        <v>129032751</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>411315</v>
+        <v>410727</v>
       </c>
       <c r="R20" t="n">
-        <v>6781704</v>
+        <v>6781837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,19 +2581,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,19 +2598,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032780</v>
+        <v>129011207</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2655,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>411808</v>
+        <v>411175</v>
       </c>
       <c r="R21" t="n">
-        <v>6781897</v>
+        <v>6781624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,9 +2678,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,19 +2705,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032758</v>
+        <v>129032780</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410842</v>
+        <v>411808</v>
       </c>
       <c r="R22" t="n">
-        <v>6781713</v>
+        <v>6781897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2817,7 +2817,7 @@
         <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032761</v>
+        <v>129032754</v>
       </c>
       <c r="B24" t="n">
         <v>79041</v>
@@ -2958,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410889</v>
+        <v>410774</v>
       </c>
       <c r="R24" t="n">
-        <v>6781774</v>
+        <v>6781776</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032759</v>
+        <v>129011222</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3055,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410870</v>
+        <v>411303</v>
       </c>
       <c r="R25" t="n">
-        <v>6781738</v>
+        <v>6781896</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,9 +3088,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3105,12 +3115,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3214,7 +3224,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011222</v>
+        <v>129032759</v>
       </c>
       <c r="B27" t="n">
         <v>79041</v>
@@ -3249,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411303</v>
+        <v>410870</v>
       </c>
       <c r="R27" t="n">
-        <v>6781896</v>
+        <v>6781738</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3282,19 +3292,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3309,19 +3309,19 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032754</v>
+        <v>129032761</v>
       </c>
       <c r="B28" t="n">
         <v>79041</v>
@@ -3356,10 +3356,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410774</v>
+        <v>410889</v>
       </c>
       <c r="R28" t="n">
-        <v>6781776</v>
+        <v>6781774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032771</v>
+        <v>129032762</v>
       </c>
       <c r="B29" t="n">
         <v>79041</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411508</v>
+        <v>410890</v>
       </c>
       <c r="R29" t="n">
-        <v>6781794</v>
+        <v>6781771</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032762</v>
+        <v>129032771</v>
       </c>
       <c r="B30" t="n">
         <v>79041</v>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410890</v>
+        <v>411508</v>
       </c>
       <c r="R30" t="n">
-        <v>6781771</v>
+        <v>6781794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032201</v>
+        <v>129032180</v>
       </c>
       <c r="B32" t="n">
         <v>79660</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411198</v>
+        <v>411312</v>
       </c>
       <c r="R32" t="n">
-        <v>6781834</v>
+        <v>6781871</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032180</v>
+        <v>129032201</v>
       </c>
       <c r="B33" t="n">
         <v>79660</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411312</v>
+        <v>411198</v>
       </c>
       <c r="R33" t="n">
-        <v>6781871</v>
+        <v>6781834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011229</v>
       </c>
       <c r="B34" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>412001</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781693</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129032774</v>
       </c>
       <c r="B35" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>411548</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781798</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011229</v>
+        <v>129011216</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>412001</v>
+        <v>411316</v>
       </c>
       <c r="R36" t="n">
-        <v>6781693</v>
+        <v>6781674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4177,7 +4177,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4187,7 +4187,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4311,7 +4311,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011216</v>
+        <v>129032764</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411316</v>
+        <v>410852</v>
       </c>
       <c r="R38" t="n">
-        <v>6781674</v>
+        <v>6781859</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4379,19 +4379,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4406,22 +4396,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032774</v>
+        <v>129011197</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4429,21 +4419,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4453,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411548</v>
+        <v>411531</v>
       </c>
       <c r="R39" t="n">
-        <v>6781798</v>
+        <v>6781805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,9 +4476,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032764</v>
+        <v>129032739</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410852</v>
+        <v>410877</v>
       </c>
       <c r="R40" t="n">
-        <v>6781859</v>
+        <v>6781741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011221</v>
+        <v>128978125</v>
       </c>
       <c r="B41" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411310</v>
+        <v>411776</v>
       </c>
       <c r="R41" t="n">
-        <v>6781709</v>
+        <v>6781941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032183</v>
+        <v>129011215</v>
       </c>
       <c r="B42" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>412070</v>
+        <v>411330</v>
       </c>
       <c r="R42" t="n">
-        <v>6781682</v>
+        <v>6781666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,9 +4787,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4804,22 +4814,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011202</v>
+        <v>129011221</v>
       </c>
       <c r="B43" t="n">
-        <v>78798</v>
+        <v>79041</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4827,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4851,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411246</v>
+        <v>411310</v>
       </c>
       <c r="R43" t="n">
-        <v>6781879</v>
+        <v>6781709</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4886,7 +4896,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4896,7 +4906,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4923,10 +4933,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011215</v>
+        <v>129011202</v>
       </c>
       <c r="B44" t="n">
-        <v>79041</v>
+        <v>78798</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4934,21 +4944,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4958,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>411330</v>
+        <v>411246</v>
       </c>
       <c r="R44" t="n">
-        <v>6781666</v>
+        <v>6781879</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4993,7 +5003,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5003,7 +5013,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5030,10 +5040,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128978125</v>
+        <v>129032183</v>
       </c>
       <c r="B45" t="n">
-        <v>79073</v>
+        <v>79660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5041,21 +5051,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411776</v>
+        <v>412070</v>
       </c>
       <c r="R45" t="n">
-        <v>6781941</v>
+        <v>6781682</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,19 +5108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032769</v>
+        <v>129011224</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411017</v>
+        <v>411539</v>
       </c>
       <c r="R48" t="n">
-        <v>6781839</v>
+        <v>6781802</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,9 +5399,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5416,19 +5426,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011206</v>
+        <v>129032184</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5463,10 +5473,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411166</v>
+        <v>411414</v>
       </c>
       <c r="R49" t="n">
-        <v>6781615</v>
+        <v>6781817</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5496,19 +5506,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5523,19 +5523,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011224</v>
+        <v>129011206</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411539</v>
+        <v>411166</v>
       </c>
       <c r="R50" t="n">
-        <v>6781802</v>
+        <v>6781615</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032184</v>
+        <v>129032769</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411414</v>
+        <v>411017</v>
       </c>
       <c r="R51" t="n">
-        <v>6781817</v>
+        <v>6781839</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5727,12 +5727,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129032750</v>
+        <v>129011225</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410717</v>
+        <v>411536</v>
       </c>
       <c r="R54" t="n">
-        <v>6781843</v>
+        <v>6781806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,9 +6001,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6018,19 +6028,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011213</v>
+        <v>129011227</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6065,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411327</v>
+        <v>411730</v>
       </c>
       <c r="R55" t="n">
-        <v>6781657</v>
+        <v>6781958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6100,7 +6110,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6110,7 +6120,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6137,7 +6147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011225</v>
+        <v>129011213</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6172,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411536</v>
+        <v>411327</v>
       </c>
       <c r="R56" t="n">
-        <v>6781806</v>
+        <v>6781657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6207,7 +6217,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6217,7 +6227,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6244,7 +6254,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011227</v>
+        <v>129032192</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6279,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411730</v>
+        <v>411504</v>
       </c>
       <c r="R57" t="n">
-        <v>6781958</v>
+        <v>6781807</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6312,19 +6322,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032192</v>
+        <v>129032750</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411504</v>
+        <v>410717</v>
       </c>
       <c r="R58" t="n">
-        <v>6781807</v>
+        <v>6781843</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032770</v>
+        <v>129011218</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411070</v>
+        <v>411322</v>
       </c>
       <c r="R61" t="n">
-        <v>6781879</v>
+        <v>6781695</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,9 +6710,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6727,19 +6737,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6774,10 +6784,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R62" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,19 +6817,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,19 +6834,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032765</v>
+        <v>129011220</v>
       </c>
       <c r="B63" t="n">
         <v>79041</v>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>410893</v>
+        <v>411312</v>
       </c>
       <c r="R63" t="n">
-        <v>6781859</v>
+        <v>6781706</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,9 +6914,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6931,19 +6941,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -6978,10 +6988,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R64" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,19 +7021,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,12 +7038,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7150,7 +7150,7 @@
         <v>129032200</v>
       </c>
       <c r="B66" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032189</v>
+        <v>129032746</v>
       </c>
       <c r="B67" t="n">
         <v>79041</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411250</v>
+        <v>410697</v>
       </c>
       <c r="R67" t="n">
-        <v>6781886</v>
+        <v>6781752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7329,12 +7329,12 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
@@ -7438,7 +7438,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032746</v>
+        <v>129032189</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410697</v>
+        <v>411250</v>
       </c>
       <c r="R69" t="n">
-        <v>6781752</v>
+        <v>6781886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,12 +7523,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7632,10 +7632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032741</v>
+        <v>129032757</v>
       </c>
       <c r="B71" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,42 +7643,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410958</v>
+        <v>410790</v>
       </c>
       <c r="R71" t="n">
-        <v>6781689</v>
+        <v>6781786</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,10 +7729,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032186</v>
+        <v>129032741</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7748,34 +7740,42 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>411332</v>
+        <v>410958</v>
       </c>
       <c r="R72" t="n">
-        <v>6781694</v>
+        <v>6781689</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7822,12 +7822,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7931,7 +7931,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032757</v>
+        <v>129032186</v>
       </c>
       <c r="B74" t="n">
         <v>79041</v>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410790</v>
+        <v>411332</v>
       </c>
       <c r="R74" t="n">
-        <v>6781786</v>
+        <v>6781694</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032767</v>
+        <v>129032181</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R75" t="n">
-        <v>6781848</v>
+        <v>6781806</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129011230</v>
+        <v>129032767</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>412017</v>
+        <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781667</v>
+        <v>6781848</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,19 +8193,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8220,22 +8210,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032181</v>
+        <v>129032768</v>
       </c>
       <c r="B77" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8243,21 +8233,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8267,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R77" t="n">
-        <v>6781806</v>
+        <v>6781857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8317,19 +8307,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032768</v>
+        <v>129011230</v>
       </c>
       <c r="B78" t="n">
         <v>79041</v>
@@ -8364,10 +8354,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R78" t="n">
-        <v>6781857</v>
+        <v>6781667</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,9 +8387,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032199</v>
+        <v>129011223</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>412062</v>
+        <v>411437</v>
       </c>
       <c r="R2" t="n">
-        <v>6781678</v>
+        <v>6781809</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,12 +770,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -869,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129011223</v>
+        <v>129032199</v>
       </c>
       <c r="B4" t="n">
         <v>79041</v>
@@ -904,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>411437</v>
+        <v>412062</v>
       </c>
       <c r="R4" t="n">
-        <v>6781809</v>
+        <v>6781678</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -937,19 +947,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,19 +964,19 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032756</v>
+        <v>129032745</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410745</v>
+        <v>411010</v>
       </c>
       <c r="R5" t="n">
-        <v>6781852</v>
+        <v>6781686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032745</v>
+        <v>129032781</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411010</v>
+        <v>411940</v>
       </c>
       <c r="R6" t="n">
-        <v>6781686</v>
+        <v>6781749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032781</v>
+        <v>129032188</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411940</v>
+        <v>411295</v>
       </c>
       <c r="R7" t="n">
-        <v>6781749</v>
+        <v>6781724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,19 +1255,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032188</v>
+        <v>129032756</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411295</v>
+        <v>410745</v>
       </c>
       <c r="R8" t="n">
-        <v>6781724</v>
+        <v>6781852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1352,12 +1352,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011211</v>
+        <v>129011212</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>411303</v>
+        <v>411313</v>
       </c>
       <c r="R12" t="n">
-        <v>6781649</v>
+        <v>6781661</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,56 +1782,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032786</v>
+        <v>129011211</v>
       </c>
       <c r="B13" t="n">
-        <v>92821</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410970</v>
+        <v>411303</v>
       </c>
       <c r="R13" t="n">
-        <v>6781684</v>
+        <v>6781649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1861,30 +1850,39 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2105,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011212</v>
+        <v>129032749</v>
       </c>
       <c r="B16" t="n">
         <v>79041</v>
@@ -2140,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411313</v>
+        <v>410719</v>
       </c>
       <c r="R16" t="n">
-        <v>6781661</v>
+        <v>6781851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,19 +2171,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,57 +2188,68 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032749</v>
+        <v>129032786</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410719</v>
+        <v>410970</v>
       </c>
       <c r="R17" t="n">
-        <v>6781851</v>
+        <v>6781684</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,6 +2290,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2309,7 +2309,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032758</v>
+        <v>129032751</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410842</v>
+        <v>410727</v>
       </c>
       <c r="R18" t="n">
-        <v>6781713</v>
+        <v>6781837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2513,7 +2513,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032751</v>
+        <v>129011207</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410727</v>
+        <v>411175</v>
       </c>
       <c r="R20" t="n">
-        <v>6781837</v>
+        <v>6781624</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,9 +2581,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,19 +2608,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011207</v>
+        <v>129032758</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2645,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>411175</v>
+        <v>410842</v>
       </c>
       <c r="R21" t="n">
-        <v>6781624</v>
+        <v>6781713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,19 +2688,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,12 +2705,12 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -2814,56 +2814,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032787</v>
+        <v>129011222</v>
       </c>
       <c r="B23" t="n">
-        <v>92821</v>
+        <v>79041</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410912</v>
+        <v>411303</v>
       </c>
       <c r="R23" t="n">
-        <v>6781662</v>
+        <v>6781896</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,75 +2882,95 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032754</v>
+        <v>129032787</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410774</v>
+        <v>410912</v>
       </c>
       <c r="R24" t="n">
-        <v>6781776</v>
+        <v>6781662</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3002,6 +3011,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3020,7 +3030,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011222</v>
+        <v>129032754</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3055,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411303</v>
+        <v>410774</v>
       </c>
       <c r="R25" t="n">
-        <v>6781896</v>
+        <v>6781776</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,19 +3098,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,12 +3115,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011229</v>
+        <v>129011216</v>
       </c>
       <c r="B34" t="n">
         <v>79041</v>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>412001</v>
+        <v>411316</v>
       </c>
       <c r="R34" t="n">
-        <v>6781693</v>
+        <v>6781674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:14</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,7 +4010,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032774</v>
+        <v>129011229</v>
       </c>
       <c r="B35" t="n">
         <v>79041</v>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411548</v>
+        <v>412001</v>
       </c>
       <c r="R35" t="n">
-        <v>6781798</v>
+        <v>6781693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,19 +4105,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011216</v>
+        <v>129032187</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411316</v>
+        <v>411321</v>
       </c>
       <c r="R36" t="n">
-        <v>6781674</v>
+        <v>6781689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4185,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032187</v>
+        <v>129032764</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411321</v>
+        <v>410852</v>
       </c>
       <c r="R37" t="n">
-        <v>6781689</v>
+        <v>6781859</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4299,19 +4299,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032764</v>
+        <v>129032774</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>410852</v>
+        <v>411548</v>
       </c>
       <c r="R38" t="n">
-        <v>6781859</v>
+        <v>6781798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011215</v>
+        <v>129032183</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411330</v>
+        <v>412070</v>
       </c>
       <c r="R42" t="n">
-        <v>6781666</v>
+        <v>6781682</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,19 +4787,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4814,12 +4804,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5040,10 +5030,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032183</v>
+        <v>129011215</v>
       </c>
       <c r="B45" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412070</v>
+        <v>411330</v>
       </c>
       <c r="R45" t="n">
-        <v>6781682</v>
+        <v>6781666</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,9 +5098,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011224</v>
+        <v>129032184</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411539</v>
+        <v>411414</v>
       </c>
       <c r="R48" t="n">
-        <v>6781802</v>
+        <v>6781817</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,19 +5399,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5426,19 +5416,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032184</v>
+        <v>129032191</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5473,10 +5463,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411414</v>
+        <v>411495</v>
       </c>
       <c r="R49" t="n">
-        <v>6781817</v>
+        <v>6781803</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5535,7 +5525,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011206</v>
+        <v>129032769</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5570,10 +5560,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411166</v>
+        <v>411017</v>
       </c>
       <c r="R50" t="n">
-        <v>6781615</v>
+        <v>6781839</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5603,19 +5593,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5630,19 +5610,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032769</v>
+        <v>129011224</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5677,10 +5657,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411017</v>
+        <v>411539</v>
       </c>
       <c r="R51" t="n">
-        <v>6781839</v>
+        <v>6781802</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5710,9 +5690,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5727,19 +5717,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032191</v>
+        <v>129011206</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5774,10 +5764,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411495</v>
+        <v>411166</v>
       </c>
       <c r="R52" t="n">
-        <v>6781803</v>
+        <v>6781615</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5807,9 +5797,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011225</v>
+        <v>129011227</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411536</v>
+        <v>411730</v>
       </c>
       <c r="R54" t="n">
-        <v>6781806</v>
+        <v>6781958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6040,7 +6040,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011227</v>
+        <v>129011213</v>
       </c>
       <c r="B55" t="n">
         <v>79041</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411730</v>
+        <v>411327</v>
       </c>
       <c r="R55" t="n">
-        <v>6781958</v>
+        <v>6781657</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6147,7 +6147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011213</v>
+        <v>129011225</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411327</v>
+        <v>411536</v>
       </c>
       <c r="R56" t="n">
-        <v>6781657</v>
+        <v>6781806</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,7 +6217,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6227,7 +6227,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6642,7 +6642,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R61" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,19 +6710,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,19 +6727,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032770</v>
+        <v>129011218</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6784,10 +6774,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411070</v>
+        <v>411322</v>
       </c>
       <c r="R62" t="n">
-        <v>6781879</v>
+        <v>6781695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6817,9 +6807,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,22 +6834,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011220</v>
+        <v>129032740</v>
       </c>
       <c r="B63" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411312</v>
+        <v>411020</v>
       </c>
       <c r="R63" t="n">
-        <v>6781706</v>
+        <v>6781851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,19 +6914,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,12 +6931,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7050,10 +7040,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032740</v>
+        <v>129011220</v>
       </c>
       <c r="B65" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7061,21 +7051,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411020</v>
+        <v>411312</v>
       </c>
       <c r="R65" t="n">
-        <v>6781851</v>
+        <v>6781706</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,9 +7108,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7135,44 +7135,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032200</v>
+        <v>129032772</v>
       </c>
       <c r="B66" t="n">
-        <v>92821</v>
+        <v>79041</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411326</v>
+        <v>411565</v>
       </c>
       <c r="R66" t="n">
-        <v>6781874</v>
+        <v>6781780</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,12 +7232,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032772</v>
+        <v>129032189</v>
       </c>
       <c r="B68" t="n">
         <v>79041</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411565</v>
+        <v>411250</v>
       </c>
       <c r="R68" t="n">
-        <v>6781780</v>
+        <v>6781886</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,19 +7426,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032189</v>
+        <v>129032760</v>
       </c>
       <c r="B69" t="n">
         <v>79041</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411250</v>
+        <v>410875</v>
       </c>
       <c r="R69" t="n">
-        <v>6781886</v>
+        <v>6781746</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,44 +7523,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032760</v>
+        <v>129032200</v>
       </c>
       <c r="B70" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410875</v>
+        <v>411326</v>
       </c>
       <c r="R70" t="n">
-        <v>6781746</v>
+        <v>6781874</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,19 +7620,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032757</v>
+        <v>129032783</v>
       </c>
       <c r="B71" t="n">
         <v>79041</v>
@@ -7667,10 +7667,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410790</v>
+        <v>411996</v>
       </c>
       <c r="R71" t="n">
-        <v>6781786</v>
+        <v>6781690</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7729,10 +7729,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032741</v>
+        <v>129032757</v>
       </c>
       <c r="B72" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7740,42 +7740,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410958</v>
+        <v>410790</v>
       </c>
       <c r="R72" t="n">
-        <v>6781689</v>
+        <v>6781786</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7834,7 +7826,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032783</v>
+        <v>129032186</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7869,10 +7861,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411996</v>
+        <v>411332</v>
       </c>
       <c r="R73" t="n">
-        <v>6781690</v>
+        <v>6781694</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7919,22 +7911,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032186</v>
+        <v>129032741</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7942,34 +7934,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>411332</v>
+        <v>410958</v>
       </c>
       <c r="R74" t="n">
-        <v>6781694</v>
+        <v>6781689</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032181</v>
+        <v>129032767</v>
       </c>
       <c r="B75" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R75" t="n">
-        <v>6781806</v>
+        <v>6781848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032767</v>
+        <v>129032768</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781848</v>
+        <v>6781857</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032768</v>
+        <v>129032181</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8233,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R77" t="n">
-        <v>6781857</v>
+        <v>6781806</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8307,12 +8307,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129011223</v>
+        <v>129032775</v>
       </c>
       <c r="B2" t="n">
         <v>79041</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411437</v>
+        <v>411542</v>
       </c>
       <c r="R2" t="n">
-        <v>6781809</v>
+        <v>6781824</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,19 +743,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>14:22</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>14:22</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -770,19 +760,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129032775</v>
+        <v>129011223</v>
       </c>
       <c r="B3" t="n">
         <v>79041</v>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411542</v>
+        <v>411437</v>
       </c>
       <c r="R3" t="n">
-        <v>6781824</v>
+        <v>6781809</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -850,9 +840,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,12 +867,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032745</v>
+        <v>129032188</v>
       </c>
       <c r="B5" t="n">
         <v>79041</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411010</v>
+        <v>411295</v>
       </c>
       <c r="R5" t="n">
-        <v>6781686</v>
+        <v>6781724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,19 +1061,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032781</v>
+        <v>129032756</v>
       </c>
       <c r="B6" t="n">
         <v>79041</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411940</v>
+        <v>410745</v>
       </c>
       <c r="R6" t="n">
-        <v>6781749</v>
+        <v>6781852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032188</v>
+        <v>129032745</v>
       </c>
       <c r="B7" t="n">
         <v>79041</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411295</v>
+        <v>411010</v>
       </c>
       <c r="R7" t="n">
-        <v>6781724</v>
+        <v>6781686</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,19 +1255,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032756</v>
+        <v>129032781</v>
       </c>
       <c r="B8" t="n">
         <v>79041</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410745</v>
+        <v>411940</v>
       </c>
       <c r="R8" t="n">
-        <v>6781852</v>
+        <v>6781749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011217</v>
+        <v>129032766</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411318</v>
+        <v>410949</v>
       </c>
       <c r="R10" t="n">
-        <v>6781689</v>
+        <v>6781860</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,19 +1539,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,19 +1556,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032766</v>
+        <v>129011217</v>
       </c>
       <c r="B11" t="n">
         <v>79041</v>
@@ -1613,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410949</v>
+        <v>411318</v>
       </c>
       <c r="R11" t="n">
-        <v>6781860</v>
+        <v>6781689</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1636,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,19 +1663,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011212</v>
+        <v>129011211</v>
       </c>
       <c r="B12" t="n">
         <v>79041</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>411313</v>
+        <v>411303</v>
       </c>
       <c r="R12" t="n">
-        <v>6781661</v>
+        <v>6781649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1745,7 +1745,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1782,7 +1782,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011211</v>
+        <v>129011208</v>
       </c>
       <c r="B13" t="n">
         <v>79041</v>
@@ -1817,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411303</v>
+        <v>411221</v>
       </c>
       <c r="R13" t="n">
-        <v>6781649</v>
+        <v>6781624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1852,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011208</v>
+        <v>129011209</v>
       </c>
       <c r="B14" t="n">
         <v>79041</v>
@@ -1924,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411221</v>
+        <v>411237</v>
       </c>
       <c r="R14" t="n">
-        <v>6781624</v>
+        <v>6781635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1959,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1996,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011209</v>
+        <v>129011212</v>
       </c>
       <c r="B15" t="n">
         <v>79041</v>
@@ -2031,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411237</v>
+        <v>411313</v>
       </c>
       <c r="R15" t="n">
-        <v>6781635</v>
+        <v>6781661</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2309,7 +2309,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032751</v>
+        <v>129032780</v>
       </c>
       <c r="B18" t="n">
         <v>79041</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410727</v>
+        <v>411808</v>
       </c>
       <c r="R18" t="n">
-        <v>6781837</v>
+        <v>6781897</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2406,7 +2406,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011219</v>
+        <v>129011207</v>
       </c>
       <c r="B19" t="n">
         <v>79041</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411315</v>
+        <v>411175</v>
       </c>
       <c r="R19" t="n">
-        <v>6781704</v>
+        <v>6781624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2476,7 +2476,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2486,7 +2486,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2513,7 +2513,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011207</v>
+        <v>129032758</v>
       </c>
       <c r="B20" t="n">
         <v>79041</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>411175</v>
+        <v>410842</v>
       </c>
       <c r="R20" t="n">
-        <v>6781624</v>
+        <v>6781713</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,19 +2581,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,19 +2598,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032758</v>
+        <v>129011219</v>
       </c>
       <c r="B21" t="n">
         <v>79041</v>
@@ -2655,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410842</v>
+        <v>411315</v>
       </c>
       <c r="R21" t="n">
-        <v>6781713</v>
+        <v>6781704</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2688,9 +2678,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,19 +2705,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032780</v>
+        <v>129032751</v>
       </c>
       <c r="B22" t="n">
         <v>79041</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411808</v>
+        <v>410727</v>
       </c>
       <c r="R22" t="n">
-        <v>6781897</v>
+        <v>6781837</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2814,7 +2814,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129011222</v>
+        <v>129032754</v>
       </c>
       <c r="B23" t="n">
         <v>79041</v>
@@ -2849,10 +2849,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>411303</v>
+        <v>410774</v>
       </c>
       <c r="R23" t="n">
-        <v>6781896</v>
+        <v>6781776</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2882,19 +2882,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2909,68 +2899,57 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032787</v>
+        <v>129011222</v>
       </c>
       <c r="B24" t="n">
-        <v>92822</v>
+        <v>79041</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410912</v>
+        <v>411303</v>
       </c>
       <c r="R24" t="n">
-        <v>6781662</v>
+        <v>6781896</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3000,37 +2979,46 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032754</v>
+        <v>129032755</v>
       </c>
       <c r="B25" t="n">
         <v>79041</v>
@@ -3065,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410774</v>
+        <v>410678</v>
       </c>
       <c r="R25" t="n">
-        <v>6781776</v>
+        <v>6781823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3127,7 +3115,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B26" t="n">
         <v>79041</v>
@@ -3162,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R26" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,7 +3212,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032759</v>
+        <v>129032761</v>
       </c>
       <c r="B27" t="n">
         <v>79041</v>
@@ -3259,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410870</v>
+        <v>410889</v>
       </c>
       <c r="R27" t="n">
-        <v>6781738</v>
+        <v>6781774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,45 +3309,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032761</v>
+        <v>129032787</v>
       </c>
       <c r="B28" t="n">
-        <v>79041</v>
+        <v>92822</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410889</v>
+        <v>410912</v>
       </c>
       <c r="R28" t="n">
-        <v>6781774</v>
+        <v>6781662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3400,6 +3399,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032779</v>
+        <v>129032180</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411808</v>
+        <v>411312</v>
       </c>
       <c r="R31" t="n">
-        <v>6781920</v>
+        <v>6781871</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,19 +3697,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032180</v>
+        <v>129032201</v>
       </c>
       <c r="B32" t="n">
         <v>79660</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411312</v>
+        <v>411198</v>
       </c>
       <c r="R32" t="n">
-        <v>6781871</v>
+        <v>6781834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032201</v>
+        <v>129032779</v>
       </c>
       <c r="B33" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411198</v>
+        <v>411808</v>
       </c>
       <c r="R33" t="n">
-        <v>6781834</v>
+        <v>6781920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011216</v>
+        <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411316</v>
+        <v>411531</v>
       </c>
       <c r="R34" t="n">
-        <v>6781674</v>
+        <v>6781805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011229</v>
+        <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79041</v>
+        <v>79073</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>412001</v>
+        <v>410877</v>
       </c>
       <c r="R35" t="n">
-        <v>6781693</v>
+        <v>6781741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,19 +4078,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,19 +4095,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032187</v>
+        <v>129011216</v>
       </c>
       <c r="B36" t="n">
         <v>79041</v>
@@ -4152,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411321</v>
+        <v>411316</v>
       </c>
       <c r="R36" t="n">
-        <v>6781689</v>
+        <v>6781674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4185,9 +4175,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032764</v>
+        <v>129011229</v>
       </c>
       <c r="B37" t="n">
         <v>79041</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410852</v>
+        <v>412001</v>
       </c>
       <c r="R37" t="n">
-        <v>6781859</v>
+        <v>6781693</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,9 +4282,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,19 +4309,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032774</v>
+        <v>129032187</v>
       </c>
       <c r="B38" t="n">
         <v>79041</v>
@@ -4346,10 +4356,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411548</v>
+        <v>411321</v>
       </c>
       <c r="R38" t="n">
-        <v>6781798</v>
+        <v>6781689</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,22 +4406,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011197</v>
+        <v>129032764</v>
       </c>
       <c r="B39" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,21 +4429,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411531</v>
+        <v>410852</v>
       </c>
       <c r="R39" t="n">
-        <v>6781805</v>
+        <v>6781859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,19 +4486,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032739</v>
+        <v>129032774</v>
       </c>
       <c r="B40" t="n">
-        <v>79073</v>
+        <v>79041</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410877</v>
+        <v>411548</v>
       </c>
       <c r="R40" t="n">
-        <v>6781741</v>
+        <v>6781798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032183</v>
+        <v>129011215</v>
       </c>
       <c r="B42" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>412070</v>
+        <v>411330</v>
       </c>
       <c r="R42" t="n">
-        <v>6781682</v>
+        <v>6781666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,9 +4787,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4804,12 +4814,12 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5030,10 +5040,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011215</v>
+        <v>129032183</v>
       </c>
       <c r="B45" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5041,21 +5051,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411330</v>
+        <v>412070</v>
       </c>
       <c r="R45" t="n">
-        <v>6781666</v>
+        <v>6781682</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,19 +5108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,19 +5125,19 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032748</v>
+        <v>129032752</v>
       </c>
       <c r="B46" t="n">
         <v>79041</v>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>410685</v>
+        <v>410787</v>
       </c>
       <c r="R46" t="n">
-        <v>6781838</v>
+        <v>6781835</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5234,7 +5234,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032752</v>
+        <v>129032748</v>
       </c>
       <c r="B47" t="n">
         <v>79041</v>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410787</v>
+        <v>410685</v>
       </c>
       <c r="R47" t="n">
-        <v>6781835</v>
+        <v>6781838</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032184</v>
+        <v>129011224</v>
       </c>
       <c r="B48" t="n">
         <v>79041</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411414</v>
+        <v>411539</v>
       </c>
       <c r="R48" t="n">
-        <v>6781817</v>
+        <v>6781802</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,9 +5399,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5416,19 +5426,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032191</v>
+        <v>129032184</v>
       </c>
       <c r="B49" t="n">
         <v>79041</v>
@@ -5463,10 +5473,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411495</v>
+        <v>411414</v>
       </c>
       <c r="R49" t="n">
-        <v>6781803</v>
+        <v>6781817</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5525,7 +5535,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129032769</v>
+        <v>129011206</v>
       </c>
       <c r="B50" t="n">
         <v>79041</v>
@@ -5560,10 +5570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411017</v>
+        <v>411166</v>
       </c>
       <c r="R50" t="n">
-        <v>6781839</v>
+        <v>6781615</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,9 +5603,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5610,19 +5630,19 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011224</v>
+        <v>129032191</v>
       </c>
       <c r="B51" t="n">
         <v>79041</v>
@@ -5657,10 +5677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411539</v>
+        <v>411495</v>
       </c>
       <c r="R51" t="n">
-        <v>6781802</v>
+        <v>6781803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5690,19 +5710,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5717,19 +5727,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011206</v>
+        <v>129032769</v>
       </c>
       <c r="B52" t="n">
         <v>79041</v>
@@ -5764,10 +5774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411166</v>
+        <v>411017</v>
       </c>
       <c r="R52" t="n">
-        <v>6781615</v>
+        <v>6781839</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5797,19 +5807,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011227</v>
+        <v>129011225</v>
       </c>
       <c r="B54" t="n">
         <v>79041</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411730</v>
+        <v>411536</v>
       </c>
       <c r="R54" t="n">
-        <v>6781958</v>
+        <v>6781806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6147,7 +6147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011225</v>
+        <v>129032192</v>
       </c>
       <c r="B56" t="n">
         <v>79041</v>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411536</v>
+        <v>411504</v>
       </c>
       <c r="R56" t="n">
-        <v>6781806</v>
+        <v>6781807</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6215,19 +6215,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6242,19 +6232,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032192</v>
+        <v>129032750</v>
       </c>
       <c r="B57" t="n">
         <v>79041</v>
@@ -6289,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411504</v>
+        <v>410717</v>
       </c>
       <c r="R57" t="n">
-        <v>6781807</v>
+        <v>6781843</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6339,19 +6329,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032750</v>
+        <v>129011227</v>
       </c>
       <c r="B58" t="n">
         <v>79041</v>
@@ -6386,10 +6376,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410717</v>
+        <v>411730</v>
       </c>
       <c r="R58" t="n">
-        <v>6781843</v>
+        <v>6781958</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6419,9 +6409,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032770</v>
+        <v>129011218</v>
       </c>
       <c r="B61" t="n">
         <v>79041</v>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411070</v>
+        <v>411322</v>
       </c>
       <c r="R61" t="n">
-        <v>6781879</v>
+        <v>6781695</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,9 +6710,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6727,19 +6737,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B62" t="n">
         <v>79041</v>
@@ -6774,10 +6784,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R62" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,19 +6817,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,12 +6834,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6943,7 +6943,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032765</v>
+        <v>129011220</v>
       </c>
       <c r="B64" t="n">
         <v>79041</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410893</v>
+        <v>411312</v>
       </c>
       <c r="R64" t="n">
-        <v>6781859</v>
+        <v>6781706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,9 +7011,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7028,19 +7038,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B65" t="n">
         <v>79041</v>
@@ -7075,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R65" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7108,19 +7118,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7135,12 +7135,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7632,10 +7632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032783</v>
+        <v>129032741</v>
       </c>
       <c r="B71" t="n">
-        <v>79041</v>
+        <v>57724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,34 +7643,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411996</v>
+        <v>410958</v>
       </c>
       <c r="R71" t="n">
-        <v>6781690</v>
+        <v>6781689</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7729,7 +7737,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032757</v>
+        <v>129032783</v>
       </c>
       <c r="B72" t="n">
         <v>79041</v>
@@ -7764,10 +7772,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410790</v>
+        <v>411996</v>
       </c>
       <c r="R72" t="n">
-        <v>6781786</v>
+        <v>6781690</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7826,7 +7834,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032186</v>
+        <v>129032757</v>
       </c>
       <c r="B73" t="n">
         <v>79041</v>
@@ -7861,10 +7869,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411332</v>
+        <v>410790</v>
       </c>
       <c r="R73" t="n">
-        <v>6781694</v>
+        <v>6781786</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,22 +7919,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032741</v>
+        <v>129032186</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>79041</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7934,42 +7942,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410958</v>
+        <v>411332</v>
       </c>
       <c r="R74" t="n">
-        <v>6781689</v>
+        <v>6781694</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032767</v>
+        <v>129032181</v>
       </c>
       <c r="B75" t="n">
-        <v>79041</v>
+        <v>79660</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R75" t="n">
-        <v>6781848</v>
+        <v>6781806</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032768</v>
+        <v>129032767</v>
       </c>
       <c r="B76" t="n">
         <v>79041</v>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781857</v>
+        <v>6781848</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032181</v>
+        <v>129032768</v>
       </c>
       <c r="B77" t="n">
-        <v>79660</v>
+        <v>79041</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8233,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R77" t="n">
-        <v>6781806</v>
+        <v>6781857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8307,12 +8307,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129032775</v>
       </c>
       <c r="B2" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129011223</v>
       </c>
       <c r="B3" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129032199</v>
       </c>
       <c r="B4" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032188</v>
+        <v>129032745</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411295</v>
+        <v>411010</v>
       </c>
       <c r="R5" t="n">
-        <v>6781724</v>
+        <v>6781686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032756</v>
+        <v>129032781</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410745</v>
+        <v>411940</v>
       </c>
       <c r="R6" t="n">
-        <v>6781852</v>
+        <v>6781749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032745</v>
+        <v>129032188</v>
       </c>
       <c r="B7" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411010</v>
+        <v>411295</v>
       </c>
       <c r="R7" t="n">
-        <v>6781686</v>
+        <v>6781724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032781</v>
+        <v>129032756</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411940</v>
+        <v>410745</v>
       </c>
       <c r="R8" t="n">
-        <v>6781749</v>
+        <v>6781852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>129011228</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032766</v>
+        <v>129011217</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410949</v>
+        <v>411318</v>
       </c>
       <c r="R10" t="n">
-        <v>6781860</v>
+        <v>6781689</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,9 +1539,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011217</v>
+        <v>129032766</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411318</v>
+        <v>410949</v>
       </c>
       <c r="R11" t="n">
-        <v>6781689</v>
+        <v>6781860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1636,19 +1646,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,12 +1663,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1678,7 +1678,7 @@
         <v>129011211</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>129011208</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1892,7 +1892,7 @@
         <v>129011209</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
         <v>129011212</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2103,45 +2103,56 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032749</v>
+        <v>129032786</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>92825</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410719</v>
+        <v>410970</v>
       </c>
       <c r="R16" t="n">
-        <v>6781851</v>
+        <v>6781684</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2182,6 +2193,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2200,56 +2212,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032786</v>
+        <v>129032749</v>
       </c>
       <c r="B17" t="n">
-        <v>92822</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410970</v>
+        <v>410719</v>
       </c>
       <c r="R17" t="n">
-        <v>6781684</v>
+        <v>6781851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2290,7 +2291,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2312,7 +2312,7 @@
         <v>129032780</v>
       </c>
       <c r="B18" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>129011207</v>
       </c>
       <c r="B19" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         <v>129032758</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>129011219</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2720,7 +2720,7 @@
         <v>129032751</v>
       </c>
       <c r="B22" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>129032754</v>
       </c>
       <c r="B23" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129011222</v>
       </c>
       <c r="B24" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R25" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,45 +3115,56 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032759</v>
+        <v>129032787</v>
       </c>
       <c r="B26" t="n">
-        <v>79041</v>
+        <v>92825</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410870</v>
+        <v>410912</v>
       </c>
       <c r="R26" t="n">
-        <v>6781738</v>
+        <v>6781662</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3194,6 +3205,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3212,10 +3224,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032761</v>
+        <v>129032755</v>
       </c>
       <c r="B27" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3247,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410889</v>
+        <v>410678</v>
       </c>
       <c r="R27" t="n">
-        <v>6781774</v>
+        <v>6781823</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,56 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032787</v>
+        <v>129032761</v>
       </c>
       <c r="B28" t="n">
-        <v>92822</v>
+        <v>79043</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410912</v>
+        <v>410889</v>
       </c>
       <c r="R28" t="n">
-        <v>6781662</v>
+        <v>6781774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,7 +3400,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>129032762</v>
       </c>
       <c r="B29" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3518,7 +3518,7 @@
         <v>129032771</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032180</v>
+        <v>129032779</v>
       </c>
       <c r="B31" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411312</v>
+        <v>411808</v>
       </c>
       <c r="R31" t="n">
-        <v>6781871</v>
+        <v>6781920</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,22 +3697,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032201</v>
+        <v>129032180</v>
       </c>
       <c r="B32" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411198</v>
+        <v>411312</v>
       </c>
       <c r="R32" t="n">
-        <v>6781834</v>
+        <v>6781871</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032779</v>
+        <v>129032201</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411808</v>
+        <v>411198</v>
       </c>
       <c r="R33" t="n">
-        <v>6781920</v>
+        <v>6781834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,22 +3891,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011216</v>
       </c>
       <c r="B34" t="n">
-        <v>79073</v>
+        <v>79043</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>411316</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129011229</v>
       </c>
       <c r="B35" t="n">
-        <v>79073</v>
+        <v>79043</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>412001</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,22 +4105,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011216</v>
+        <v>129032774</v>
       </c>
       <c r="B36" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411316</v>
+        <v>411548</v>
       </c>
       <c r="R36" t="n">
-        <v>6781674</v>
+        <v>6781798</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4185,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,22 +4202,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011229</v>
+        <v>129032764</v>
       </c>
       <c r="B37" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>412001</v>
+        <v>410852</v>
       </c>
       <c r="R37" t="n">
-        <v>6781693</v>
+        <v>6781859</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,19 +4282,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4309,12 +4299,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4324,7 +4314,7 @@
         <v>129032187</v>
       </c>
       <c r="B38" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4418,10 +4408,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032764</v>
+        <v>129011197</v>
       </c>
       <c r="B39" t="n">
-        <v>79041</v>
+        <v>79075</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4429,21 +4419,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4453,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410852</v>
+        <v>411531</v>
       </c>
       <c r="R39" t="n">
-        <v>6781859</v>
+        <v>6781805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,9 +4476,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032774</v>
+        <v>129032739</v>
       </c>
       <c r="B40" t="n">
-        <v>79041</v>
+        <v>79075</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411548</v>
+        <v>410877</v>
       </c>
       <c r="R40" t="n">
-        <v>6781798</v>
+        <v>6781741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128978125</v>
+        <v>129011221</v>
       </c>
       <c r="B41" t="n">
-        <v>79073</v>
+        <v>79043</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411776</v>
+        <v>411310</v>
       </c>
       <c r="R41" t="n">
-        <v>6781941</v>
+        <v>6781709</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4722,7 +4722,7 @@
         <v>129011215</v>
       </c>
       <c r="B42" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011221</v>
+        <v>129011202</v>
       </c>
       <c r="B43" t="n">
-        <v>79041</v>
+        <v>78800</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411310</v>
+        <v>411246</v>
       </c>
       <c r="R43" t="n">
-        <v>6781709</v>
+        <v>6781879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4933,10 +4933,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011202</v>
+        <v>129032183</v>
       </c>
       <c r="B44" t="n">
-        <v>78798</v>
+        <v>79662</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>411246</v>
+        <v>412070</v>
       </c>
       <c r="R44" t="n">
-        <v>6781879</v>
+        <v>6781682</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5001,19 +5001,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5028,22 +5018,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032183</v>
+        <v>128978125</v>
       </c>
       <c r="B45" t="n">
-        <v>79660</v>
+        <v>79075</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412070</v>
+        <v>411776</v>
       </c>
       <c r="R45" t="n">
-        <v>6781682</v>
+        <v>6781941</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,9 +5098,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,22 +5125,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032752</v>
+        <v>129032748</v>
       </c>
       <c r="B46" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5172,10 +5172,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>410787</v>
+        <v>410685</v>
       </c>
       <c r="R46" t="n">
-        <v>6781835</v>
+        <v>6781838</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032748</v>
+        <v>129032752</v>
       </c>
       <c r="B47" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5269,10 +5269,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410685</v>
+        <v>410787</v>
       </c>
       <c r="R47" t="n">
-        <v>6781838</v>
+        <v>6781835</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011224</v>
+        <v>129032769</v>
       </c>
       <c r="B48" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411539</v>
+        <v>411017</v>
       </c>
       <c r="R48" t="n">
-        <v>6781802</v>
+        <v>6781839</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,19 +5399,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5426,12 +5416,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5441,7 +5431,7 @@
         <v>129032184</v>
       </c>
       <c r="B49" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5538,7 +5528,7 @@
         <v>129011206</v>
       </c>
       <c r="B50" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5645,7 +5635,7 @@
         <v>129032191</v>
       </c>
       <c r="B51" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5739,10 +5729,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032769</v>
+        <v>129011224</v>
       </c>
       <c r="B52" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5774,10 +5764,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411017</v>
+        <v>411539</v>
       </c>
       <c r="R52" t="n">
-        <v>6781839</v>
+        <v>6781802</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5807,9 +5797,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5839,7 +5839,7 @@
         <v>129032196</v>
       </c>
       <c r="B53" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5936,7 +5936,7 @@
         <v>129011225</v>
       </c>
       <c r="B54" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6040,10 +6040,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011213</v>
+        <v>129011227</v>
       </c>
       <c r="B55" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411327</v>
+        <v>411730</v>
       </c>
       <c r="R55" t="n">
-        <v>6781657</v>
+        <v>6781958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032192</v>
+        <v>129011213</v>
       </c>
       <c r="B56" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411504</v>
+        <v>411327</v>
       </c>
       <c r="R56" t="n">
-        <v>6781807</v>
+        <v>6781657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6215,9 +6215,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6232,22 +6242,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032750</v>
+        <v>129032192</v>
       </c>
       <c r="B57" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6279,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410717</v>
+        <v>411504</v>
       </c>
       <c r="R57" t="n">
-        <v>6781843</v>
+        <v>6781807</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6329,22 +6339,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011227</v>
+        <v>129032750</v>
       </c>
       <c r="B58" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6376,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411730</v>
+        <v>410717</v>
       </c>
       <c r="R58" t="n">
-        <v>6781958</v>
+        <v>6781843</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6409,19 +6419,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
         <v>129032185</v>
       </c>
       <c r="B59" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6548,7 +6548,7 @@
         <v>129032778</v>
       </c>
       <c r="B60" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6642,10 +6642,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B61" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R61" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,19 +6710,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,22 +6727,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032770</v>
+        <v>129011218</v>
       </c>
       <c r="B62" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6784,10 +6774,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411070</v>
+        <v>411322</v>
       </c>
       <c r="R62" t="n">
-        <v>6781879</v>
+        <v>6781695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6817,9 +6807,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,22 +6834,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032740</v>
+        <v>129011220</v>
       </c>
       <c r="B63" t="n">
-        <v>79073</v>
+        <v>79043</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411020</v>
+        <v>411312</v>
       </c>
       <c r="R63" t="n">
-        <v>6781851</v>
+        <v>6781706</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,9 +6914,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6931,22 +6941,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011220</v>
+        <v>129032740</v>
       </c>
       <c r="B64" t="n">
-        <v>79041</v>
+        <v>79075</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6954,21 +6964,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6978,10 +6988,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411312</v>
+        <v>411020</v>
       </c>
       <c r="R64" t="n">
-        <v>6781706</v>
+        <v>6781851</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,19 +7021,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,12 +7038,12 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -7053,7 +7053,7 @@
         <v>129032765</v>
       </c>
       <c r="B65" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032772</v>
+        <v>129032189</v>
       </c>
       <c r="B66" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411565</v>
+        <v>411250</v>
       </c>
       <c r="R66" t="n">
-        <v>6781780</v>
+        <v>6781886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,44 +7232,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032746</v>
+        <v>129032200</v>
       </c>
       <c r="B67" t="n">
-        <v>79041</v>
+        <v>92825</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410697</v>
+        <v>411326</v>
       </c>
       <c r="R67" t="n">
-        <v>6781752</v>
+        <v>6781874</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7329,22 +7329,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032189</v>
+        <v>129032746</v>
       </c>
       <c r="B68" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411250</v>
+        <v>410697</v>
       </c>
       <c r="R68" t="n">
-        <v>6781886</v>
+        <v>6781752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,22 +7426,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032760</v>
+        <v>129032772</v>
       </c>
       <c r="B69" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410875</v>
+        <v>411565</v>
       </c>
       <c r="R69" t="n">
-        <v>6781746</v>
+        <v>6781780</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7535,32 +7535,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032200</v>
+        <v>129032760</v>
       </c>
       <c r="B70" t="n">
-        <v>92822</v>
+        <v>79043</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411326</v>
+        <v>410875</v>
       </c>
       <c r="R70" t="n">
-        <v>6781874</v>
+        <v>6781746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,12 +7620,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7740,7 +7740,7 @@
         <v>129032783</v>
       </c>
       <c r="B72" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7834,10 +7834,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032757</v>
+        <v>129032186</v>
       </c>
       <c r="B73" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>410790</v>
+        <v>411332</v>
       </c>
       <c r="R73" t="n">
-        <v>6781786</v>
+        <v>6781694</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7919,22 +7919,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032186</v>
+        <v>129032757</v>
       </c>
       <c r="B74" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>411332</v>
+        <v>410790</v>
       </c>
       <c r="R74" t="n">
-        <v>6781694</v>
+        <v>6781786</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032181</v>
+        <v>129032767</v>
       </c>
       <c r="B75" t="n">
-        <v>79660</v>
+        <v>79043</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R75" t="n">
-        <v>6781806</v>
+        <v>6781848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,22 +8113,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032767</v>
+        <v>129032768</v>
       </c>
       <c r="B76" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781848</v>
+        <v>6781857</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032768</v>
+        <v>129032181</v>
       </c>
       <c r="B77" t="n">
-        <v>79041</v>
+        <v>79662</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8233,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R77" t="n">
-        <v>6781857</v>
+        <v>6781806</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8307,12 +8307,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
@@ -8322,7 +8322,7 @@
         <v>129011230</v>
       </c>
       <c r="B78" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -1675,7 +1675,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011211</v>
+        <v>129032749</v>
       </c>
       <c r="B12" t="n">
         <v>79043</v>
@@ -1710,10 +1710,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>411303</v>
+        <v>410719</v>
       </c>
       <c r="R12" t="n">
-        <v>6781649</v>
+        <v>6781851</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,19 +1743,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1770,19 +1760,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011208</v>
+        <v>129011211</v>
       </c>
       <c r="B13" t="n">
         <v>79043</v>
@@ -1817,10 +1807,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411221</v>
+        <v>411303</v>
       </c>
       <c r="R13" t="n">
-        <v>6781624</v>
+        <v>6781649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,7 +1842,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1862,7 +1852,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1889,7 +1879,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011209</v>
+        <v>129011208</v>
       </c>
       <c r="B14" t="n">
         <v>79043</v>
@@ -1924,10 +1914,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411237</v>
+        <v>411221</v>
       </c>
       <c r="R14" t="n">
-        <v>6781635</v>
+        <v>6781624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1949,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1969,7 +1959,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1986,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011212</v>
+        <v>129011209</v>
       </c>
       <c r="B15" t="n">
         <v>79043</v>
@@ -2031,10 +2021,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411313</v>
+        <v>411237</v>
       </c>
       <c r="R15" t="n">
-        <v>6781661</v>
+        <v>6781635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2056,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2076,7 +2066,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,56 +2093,45 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032786</v>
+        <v>129011212</v>
       </c>
       <c r="B16" t="n">
-        <v>92825</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410970</v>
+        <v>411313</v>
       </c>
       <c r="R16" t="n">
-        <v>6781684</v>
+        <v>6781661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2182,75 +2161,95 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032749</v>
+        <v>129032786</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>92825</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410719</v>
+        <v>410970</v>
       </c>
       <c r="R17" t="n">
-        <v>6781851</v>
+        <v>6781684</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,6 +2290,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011216</v>
+        <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79043</v>
+        <v>79075</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411316</v>
+        <v>411531</v>
       </c>
       <c r="R34" t="n">
-        <v>6781674</v>
+        <v>6781805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011229</v>
+        <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79043</v>
+        <v>79075</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>412001</v>
+        <v>410877</v>
       </c>
       <c r="R35" t="n">
-        <v>6781693</v>
+        <v>6781741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,19 +4078,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,19 +4095,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032774</v>
+        <v>129011216</v>
       </c>
       <c r="B36" t="n">
         <v>79043</v>
@@ -4152,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411548</v>
+        <v>411316</v>
       </c>
       <c r="R36" t="n">
-        <v>6781798</v>
+        <v>6781674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4185,9 +4175,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032764</v>
+        <v>129011229</v>
       </c>
       <c r="B37" t="n">
         <v>79043</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410852</v>
+        <v>412001</v>
       </c>
       <c r="R37" t="n">
-        <v>6781859</v>
+        <v>6781693</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,9 +4282,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,19 +4309,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032187</v>
+        <v>129032774</v>
       </c>
       <c r="B38" t="n">
         <v>79043</v>
@@ -4346,10 +4356,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411321</v>
+        <v>411548</v>
       </c>
       <c r="R38" t="n">
-        <v>6781689</v>
+        <v>6781798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,22 +4406,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011197</v>
+        <v>129032187</v>
       </c>
       <c r="B39" t="n">
-        <v>79075</v>
+        <v>79043</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,21 +4429,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411531</v>
+        <v>411321</v>
       </c>
       <c r="R39" t="n">
-        <v>6781805</v>
+        <v>6781689</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,19 +4486,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032739</v>
+        <v>129032764</v>
       </c>
       <c r="B40" t="n">
-        <v>79075</v>
+        <v>79043</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410877</v>
+        <v>410852</v>
       </c>
       <c r="R40" t="n">
-        <v>6781741</v>
+        <v>6781859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032778</v>
+        <v>129011218</v>
       </c>
       <c r="B60" t="n">
         <v>79043</v>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411824</v>
+        <v>411322</v>
       </c>
       <c r="R60" t="n">
-        <v>6781940</v>
+        <v>6781695</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6613,9 +6613,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6630,19 +6640,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032770</v>
+        <v>129032778</v>
       </c>
       <c r="B61" t="n">
         <v>79043</v>
@@ -6677,10 +6687,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411070</v>
+        <v>411824</v>
       </c>
       <c r="R61" t="n">
-        <v>6781879</v>
+        <v>6781940</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6739,7 +6749,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B62" t="n">
         <v>79043</v>
@@ -6774,10 +6784,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R62" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,19 +6817,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,12 +6834,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -6953,10 +6953,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032740</v>
+        <v>129032765</v>
       </c>
       <c r="B64" t="n">
-        <v>79075</v>
+        <v>79043</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6964,21 +6964,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6988,10 +6988,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411020</v>
+        <v>410893</v>
       </c>
       <c r="R64" t="n">
-        <v>6781851</v>
+        <v>6781859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7050,10 +7050,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032765</v>
+        <v>129032740</v>
       </c>
       <c r="B65" t="n">
-        <v>79043</v>
+        <v>79075</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410893</v>
+        <v>411020</v>
       </c>
       <c r="R65" t="n">
-        <v>6781859</v>
+        <v>6781851</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7244,32 +7244,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032200</v>
+        <v>129032746</v>
       </c>
       <c r="B67" t="n">
-        <v>92825</v>
+        <v>79043</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411326</v>
+        <v>410697</v>
       </c>
       <c r="R67" t="n">
-        <v>6781874</v>
+        <v>6781752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7329,19 +7329,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032746</v>
+        <v>129032772</v>
       </c>
       <c r="B68" t="n">
         <v>79043</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410697</v>
+        <v>411565</v>
       </c>
       <c r="R68" t="n">
-        <v>6781752</v>
+        <v>6781780</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7438,7 +7438,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032772</v>
+        <v>129032760</v>
       </c>
       <c r="B69" t="n">
         <v>79043</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411565</v>
+        <v>410875</v>
       </c>
       <c r="R69" t="n">
-        <v>6781780</v>
+        <v>6781746</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7535,32 +7535,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032760</v>
+        <v>129032200</v>
       </c>
       <c r="B70" t="n">
-        <v>79043</v>
+        <v>92825</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410875</v>
+        <v>411326</v>
       </c>
       <c r="R70" t="n">
-        <v>6781746</v>
+        <v>6781874</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,12 +7620,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129032775</v>
       </c>
       <c r="B2" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129011223</v>
       </c>
       <c r="B3" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>129032199</v>
       </c>
       <c r="B4" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -976,10 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032745</v>
+        <v>129032188</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411010</v>
+        <v>411295</v>
       </c>
       <c r="R5" t="n">
-        <v>6781686</v>
+        <v>6781724</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,22 +1061,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032781</v>
+        <v>129032756</v>
       </c>
       <c r="B6" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411940</v>
+        <v>410745</v>
       </c>
       <c r="R6" t="n">
-        <v>6781749</v>
+        <v>6781852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1170,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032188</v>
+        <v>129032745</v>
       </c>
       <c r="B7" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411295</v>
+        <v>411010</v>
       </c>
       <c r="R7" t="n">
-        <v>6781724</v>
+        <v>6781686</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,22 +1255,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032756</v>
+        <v>129032781</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410745</v>
+        <v>411940</v>
       </c>
       <c r="R8" t="n">
-        <v>6781852</v>
+        <v>6781749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1367,7 +1367,7 @@
         <v>129011228</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1471,10 +1471,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011217</v>
+        <v>129032766</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411318</v>
+        <v>410949</v>
       </c>
       <c r="R10" t="n">
-        <v>6781689</v>
+        <v>6781860</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,19 +1539,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,22 +1556,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032766</v>
+        <v>129011217</v>
       </c>
       <c r="B11" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1613,10 +1603,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410949</v>
+        <v>411318</v>
       </c>
       <c r="R11" t="n">
-        <v>6781860</v>
+        <v>6781689</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1646,9 +1636,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,57 +1663,68 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032749</v>
+        <v>129032786</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>92827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410719</v>
+        <v>410970</v>
       </c>
       <c r="R12" t="n">
-        <v>6781851</v>
+        <v>6781684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,6 +1765,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1772,10 +1784,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011211</v>
+        <v>129011212</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1807,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411303</v>
+        <v>411313</v>
       </c>
       <c r="R13" t="n">
-        <v>6781649</v>
+        <v>6781661</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1854,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1852,7 +1864,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1879,10 +1891,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011208</v>
+        <v>129032749</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1914,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411221</v>
+        <v>410719</v>
       </c>
       <c r="R14" t="n">
-        <v>6781624</v>
+        <v>6781851</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1947,19 +1959,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1974,22 +1976,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011209</v>
+        <v>129011211</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2021,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411237</v>
+        <v>411303</v>
       </c>
       <c r="R15" t="n">
-        <v>6781635</v>
+        <v>6781649</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2056,7 +2058,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2066,7 +2068,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2093,10 +2095,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011212</v>
+        <v>129011208</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2128,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411313</v>
+        <v>411221</v>
       </c>
       <c r="R16" t="n">
-        <v>6781661</v>
+        <v>6781624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2163,7 +2165,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2173,7 +2175,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,56 +2202,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032786</v>
+        <v>129011209</v>
       </c>
       <c r="B17" t="n">
-        <v>92825</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410970</v>
+        <v>411237</v>
       </c>
       <c r="R17" t="n">
-        <v>6781684</v>
+        <v>6781635</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2279,40 +2270,49 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032780</v>
+        <v>129011219</v>
       </c>
       <c r="B18" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411808</v>
+        <v>411315</v>
       </c>
       <c r="R18" t="n">
-        <v>6781897</v>
+        <v>6781704</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,9 +2377,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,22 +2404,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011207</v>
+        <v>129032751</v>
       </c>
       <c r="B19" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2441,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411175</v>
+        <v>410727</v>
       </c>
       <c r="R19" t="n">
-        <v>6781624</v>
+        <v>6781837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,19 +2484,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,12 +2501,12 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2516,7 +2516,7 @@
         <v>129032758</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2610,10 +2610,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129011219</v>
+        <v>129032780</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2645,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>411315</v>
+        <v>411808</v>
       </c>
       <c r="R21" t="n">
-        <v>6781704</v>
+        <v>6781897</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,19 +2678,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2705,22 +2695,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032751</v>
+        <v>129011207</v>
       </c>
       <c r="B22" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,10 +2742,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410727</v>
+        <v>411175</v>
       </c>
       <c r="R22" t="n">
-        <v>6781837</v>
+        <v>6781624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,9 +2775,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,12 +2802,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -2817,7 +2817,7 @@
         <v>129032754</v>
       </c>
       <c r="B23" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
         <v>129011222</v>
       </c>
       <c r="B24" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3018,10 +3018,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032759</v>
+        <v>129032755</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3053,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410870</v>
+        <v>410678</v>
       </c>
       <c r="R25" t="n">
-        <v>6781738</v>
+        <v>6781823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,56 +3115,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032787</v>
+        <v>129032759</v>
       </c>
       <c r="B26" t="n">
-        <v>92825</v>
+        <v>79044</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410912</v>
+        <v>410870</v>
       </c>
       <c r="R26" t="n">
-        <v>6781662</v>
+        <v>6781738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3205,7 +3194,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3224,10 +3212,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032755</v>
+        <v>129032761</v>
       </c>
       <c r="B27" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3259,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410678</v>
+        <v>410889</v>
       </c>
       <c r="R27" t="n">
-        <v>6781823</v>
+        <v>6781774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,45 +3309,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032761</v>
+        <v>129032787</v>
       </c>
       <c r="B28" t="n">
-        <v>79043</v>
+        <v>92827</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410889</v>
+        <v>410912</v>
       </c>
       <c r="R28" t="n">
-        <v>6781774</v>
+        <v>6781662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3400,6 +3399,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3418,10 +3418,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032762</v>
+        <v>129032771</v>
       </c>
       <c r="B29" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410890</v>
+        <v>411508</v>
       </c>
       <c r="R29" t="n">
-        <v>6781771</v>
+        <v>6781794</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,10 +3515,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032771</v>
+        <v>129032762</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411508</v>
+        <v>410890</v>
       </c>
       <c r="R30" t="n">
-        <v>6781794</v>
+        <v>6781771</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3615,7 +3615,7 @@
         <v>129032779</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3712,7 +3712,7 @@
         <v>129032180</v>
       </c>
       <c r="B32" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3809,7 +3809,7 @@
         <v>129032201</v>
       </c>
       <c r="B33" t="n">
-        <v>79662</v>
+        <v>79663</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011216</v>
       </c>
       <c r="B34" t="n">
-        <v>79075</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>411316</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129011229</v>
       </c>
       <c r="B35" t="n">
-        <v>79075</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>412001</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,22 +4105,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011216</v>
+        <v>129032187</v>
       </c>
       <c r="B36" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411316</v>
+        <v>411321</v>
       </c>
       <c r="R36" t="n">
-        <v>6781674</v>
+        <v>6781689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4185,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,22 +4202,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011229</v>
+        <v>129032764</v>
       </c>
       <c r="B37" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>412001</v>
+        <v>410852</v>
       </c>
       <c r="R37" t="n">
-        <v>6781693</v>
+        <v>6781859</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,19 +4282,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4309,12 +4299,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4324,7 +4314,7 @@
         <v>129032774</v>
       </c>
       <c r="B38" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4418,10 +4408,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032187</v>
+        <v>129011197</v>
       </c>
       <c r="B39" t="n">
-        <v>79043</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4429,21 +4419,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4453,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411321</v>
+        <v>411531</v>
       </c>
       <c r="R39" t="n">
-        <v>6781689</v>
+        <v>6781805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,9 +4476,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032764</v>
+        <v>129032739</v>
       </c>
       <c r="B40" t="n">
-        <v>79043</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410852</v>
+        <v>410877</v>
       </c>
       <c r="R40" t="n">
-        <v>6781859</v>
+        <v>6781741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011221</v>
+        <v>129011202</v>
       </c>
       <c r="B41" t="n">
-        <v>79043</v>
+        <v>78801</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411310</v>
+        <v>411246</v>
       </c>
       <c r="R41" t="n">
-        <v>6781709</v>
+        <v>6781879</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011215</v>
+        <v>129032183</v>
       </c>
       <c r="B42" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411330</v>
+        <v>412070</v>
       </c>
       <c r="R42" t="n">
-        <v>6781666</v>
+        <v>6781682</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,19 +4787,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4814,22 +4804,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011202</v>
+        <v>129011215</v>
       </c>
       <c r="B43" t="n">
-        <v>78800</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4827,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4851,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411246</v>
+        <v>411330</v>
       </c>
       <c r="R43" t="n">
-        <v>6781879</v>
+        <v>6781666</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,7 +4886,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4906,7 +4896,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4933,10 +4923,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032183</v>
+        <v>129011221</v>
       </c>
       <c r="B44" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,21 +4934,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4958,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>412070</v>
+        <v>411310</v>
       </c>
       <c r="R44" t="n">
-        <v>6781682</v>
+        <v>6781709</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5001,9 +4991,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5018,12 +5018,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5033,7 +5033,7 @@
         <v>128978125</v>
       </c>
       <c r="B45" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>129032748</v>
       </c>
       <c r="B46" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5237,7 +5237,7 @@
         <v>129032752</v>
       </c>
       <c r="B47" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5331,10 +5331,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032769</v>
+        <v>129011224</v>
       </c>
       <c r="B48" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411017</v>
+        <v>411539</v>
       </c>
       <c r="R48" t="n">
-        <v>6781839</v>
+        <v>6781802</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,9 +5399,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5416,12 +5426,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5431,7 +5441,7 @@
         <v>129032184</v>
       </c>
       <c r="B49" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5528,7 +5538,7 @@
         <v>129011206</v>
       </c>
       <c r="B50" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5635,7 +5645,7 @@
         <v>129032191</v>
       </c>
       <c r="B51" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5729,10 +5739,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129011224</v>
+        <v>129032769</v>
       </c>
       <c r="B52" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5764,10 +5774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411539</v>
+        <v>411017</v>
       </c>
       <c r="R52" t="n">
-        <v>6781802</v>
+        <v>6781839</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5797,19 +5807,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5839,7 +5839,7 @@
         <v>129032196</v>
       </c>
       <c r="B53" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5933,10 +5933,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011225</v>
+        <v>129011227</v>
       </c>
       <c r="B54" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411536</v>
+        <v>411730</v>
       </c>
       <c r="R54" t="n">
-        <v>6781806</v>
+        <v>6781958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6040,10 +6040,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011227</v>
+        <v>129011213</v>
       </c>
       <c r="B55" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411730</v>
+        <v>411327</v>
       </c>
       <c r="R55" t="n">
-        <v>6781958</v>
+        <v>6781657</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6147,10 +6147,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011213</v>
+        <v>129032192</v>
       </c>
       <c r="B56" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411327</v>
+        <v>411504</v>
       </c>
       <c r="R56" t="n">
-        <v>6781657</v>
+        <v>6781807</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6215,19 +6215,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6242,22 +6232,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032192</v>
+        <v>129032750</v>
       </c>
       <c r="B57" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6289,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411504</v>
+        <v>410717</v>
       </c>
       <c r="R57" t="n">
-        <v>6781807</v>
+        <v>6781843</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6339,22 +6329,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032750</v>
+        <v>129011225</v>
       </c>
       <c r="B58" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6386,10 +6376,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410717</v>
+        <v>411536</v>
       </c>
       <c r="R58" t="n">
-        <v>6781843</v>
+        <v>6781806</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6419,9 +6409,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6451,7 +6451,7 @@
         <v>129032185</v>
       </c>
       <c r="B59" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6545,10 +6545,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011218</v>
+        <v>129032778</v>
       </c>
       <c r="B60" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411322</v>
+        <v>411824</v>
       </c>
       <c r="R60" t="n">
-        <v>6781695</v>
+        <v>6781940</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6613,19 +6613,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6640,22 +6630,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032778</v>
+        <v>129011218</v>
       </c>
       <c r="B61" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6687,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411824</v>
+        <v>411322</v>
       </c>
       <c r="R61" t="n">
-        <v>6781940</v>
+        <v>6781695</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6720,9 +6710,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,12 +6737,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6752,7 +6752,7 @@
         <v>129032770</v>
       </c>
       <c r="B62" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011220</v>
+        <v>129032740</v>
       </c>
       <c r="B63" t="n">
-        <v>79043</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411312</v>
+        <v>411020</v>
       </c>
       <c r="R63" t="n">
-        <v>6781706</v>
+        <v>6781851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,19 +6914,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,22 +6931,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032765</v>
+        <v>129011220</v>
       </c>
       <c r="B64" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6988,10 +6978,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410893</v>
+        <v>411312</v>
       </c>
       <c r="R64" t="n">
-        <v>6781859</v>
+        <v>6781706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7021,9 +7011,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,22 +7038,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032740</v>
+        <v>129032765</v>
       </c>
       <c r="B65" t="n">
-        <v>79075</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411020</v>
+        <v>410893</v>
       </c>
       <c r="R65" t="n">
-        <v>6781851</v>
+        <v>6781859</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7147,10 +7147,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032189</v>
+        <v>129032772</v>
       </c>
       <c r="B66" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411250</v>
+        <v>411565</v>
       </c>
       <c r="R66" t="n">
-        <v>6781886</v>
+        <v>6781780</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,44 +7232,44 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032746</v>
+        <v>129032200</v>
       </c>
       <c r="B67" t="n">
-        <v>79043</v>
+        <v>92827</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410697</v>
+        <v>411326</v>
       </c>
       <c r="R67" t="n">
-        <v>6781752</v>
+        <v>6781874</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7329,22 +7329,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032772</v>
+        <v>129032746</v>
       </c>
       <c r="B68" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411565</v>
+        <v>410697</v>
       </c>
       <c r="R68" t="n">
-        <v>6781780</v>
+        <v>6781752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7438,10 +7438,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032760</v>
+        <v>129032189</v>
       </c>
       <c r="B69" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410875</v>
+        <v>411250</v>
       </c>
       <c r="R69" t="n">
-        <v>6781746</v>
+        <v>6781886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,44 +7523,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032200</v>
+        <v>129032760</v>
       </c>
       <c r="B70" t="n">
-        <v>92825</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411326</v>
+        <v>410875</v>
       </c>
       <c r="R70" t="n">
-        <v>6781874</v>
+        <v>6781746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,12 +7620,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7740,7 +7740,7 @@
         <v>129032783</v>
       </c>
       <c r="B72" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7834,10 +7834,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032186</v>
+        <v>129032757</v>
       </c>
       <c r="B73" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7869,10 +7869,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411332</v>
+        <v>410790</v>
       </c>
       <c r="R73" t="n">
-        <v>6781694</v>
+        <v>6781786</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7919,22 +7919,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032757</v>
+        <v>129032186</v>
       </c>
       <c r="B74" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7966,10 +7966,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410790</v>
+        <v>411332</v>
       </c>
       <c r="R74" t="n">
-        <v>6781786</v>
+        <v>6781694</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032767</v>
+        <v>129032768</v>
       </c>
       <c r="B75" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>410959</v>
       </c>
       <c r="R75" t="n">
-        <v>6781848</v>
+        <v>6781857</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8125,10 +8125,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032768</v>
+        <v>129011230</v>
       </c>
       <c r="B76" t="n">
-        <v>79043</v>
+        <v>79044</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R76" t="n">
-        <v>6781857</v>
+        <v>6781667</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,9 +8193,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8210,22 +8220,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032181</v>
+        <v>129032767</v>
       </c>
       <c r="B77" t="n">
-        <v>79662</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8243,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8267,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R77" t="n">
-        <v>6781806</v>
+        <v>6781848</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8307,22 +8317,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011230</v>
+        <v>129032181</v>
       </c>
       <c r="B78" t="n">
-        <v>79043</v>
+        <v>79663</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,21 +8340,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8354,10 +8364,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412017</v>
+        <v>411425</v>
       </c>
       <c r="R78" t="n">
-        <v>6781667</v>
+        <v>6781806</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8387,19 +8397,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -1678,7 +1678,7 @@
         <v>129032786</v>
       </c>
       <c r="B12" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011212</v>
+        <v>129011211</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411313</v>
+        <v>411303</v>
       </c>
       <c r="R13" t="n">
-        <v>6781661</v>
+        <v>6781649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1891,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032749</v>
+        <v>129011208</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410719</v>
+        <v>411221</v>
       </c>
       <c r="R14" t="n">
-        <v>6781851</v>
+        <v>6781624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,9 +1959,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,19 +1986,19 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011211</v>
+        <v>129011209</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2023,10 +2033,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411303</v>
+        <v>411237</v>
       </c>
       <c r="R15" t="n">
-        <v>6781649</v>
+        <v>6781635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,7 +2068,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2068,7 +2078,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,7 +2105,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011208</v>
+        <v>129011212</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2130,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411221</v>
+        <v>411313</v>
       </c>
       <c r="R16" t="n">
-        <v>6781624</v>
+        <v>6781661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,7 +2175,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2175,7 +2185,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2202,7 +2212,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129011209</v>
+        <v>129032749</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2237,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411237</v>
+        <v>410719</v>
       </c>
       <c r="R17" t="n">
-        <v>6781635</v>
+        <v>6781851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,19 +2280,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:55</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,19 +2297,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011219</v>
+        <v>129032758</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411315</v>
+        <v>410842</v>
       </c>
       <c r="R18" t="n">
-        <v>6781704</v>
+        <v>6781713</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,19 +2377,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,19 +2394,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032751</v>
+        <v>129011219</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2451,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410727</v>
+        <v>411315</v>
       </c>
       <c r="R19" t="n">
-        <v>6781837</v>
+        <v>6781704</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,9 +2474,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,19 +2501,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032758</v>
+        <v>129032751</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410842</v>
+        <v>410727</v>
       </c>
       <c r="R20" t="n">
-        <v>6781713</v>
+        <v>6781837</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2814,45 +2814,56 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032754</v>
+        <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>92831</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410774</v>
+        <v>410912</v>
       </c>
       <c r="R23" t="n">
-        <v>6781776</v>
+        <v>6781662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2904,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2911,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011222</v>
+        <v>129032754</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -2946,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411303</v>
+        <v>410774</v>
       </c>
       <c r="R24" t="n">
-        <v>6781896</v>
+        <v>6781776</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,19 +2991,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3006,19 +3008,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032755</v>
+        <v>129011222</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3053,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410678</v>
+        <v>411303</v>
       </c>
       <c r="R25" t="n">
-        <v>6781823</v>
+        <v>6781896</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3086,9 +3088,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3103,19 +3115,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032759</v>
+        <v>129032755</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3150,10 +3162,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410870</v>
+        <v>410678</v>
       </c>
       <c r="R26" t="n">
-        <v>6781738</v>
+        <v>6781823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3224,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032761</v>
+        <v>129032759</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3247,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410889</v>
+        <v>410870</v>
       </c>
       <c r="R27" t="n">
-        <v>6781774</v>
+        <v>6781738</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,56 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032787</v>
+        <v>129032761</v>
       </c>
       <c r="B28" t="n">
-        <v>92827</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410912</v>
+        <v>410889</v>
       </c>
       <c r="R28" t="n">
-        <v>6781662</v>
+        <v>6781774</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,7 +3400,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032771</v>
+        <v>129032762</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411508</v>
+        <v>410890</v>
       </c>
       <c r="R29" t="n">
-        <v>6781794</v>
+        <v>6781771</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032762</v>
+        <v>129032771</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410890</v>
+        <v>411508</v>
       </c>
       <c r="R30" t="n">
-        <v>6781771</v>
+        <v>6781794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011216</v>
+        <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411316</v>
+        <v>411531</v>
       </c>
       <c r="R34" t="n">
-        <v>6781674</v>
+        <v>6781805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011229</v>
+        <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>412001</v>
+        <v>410877</v>
       </c>
       <c r="R35" t="n">
-        <v>6781693</v>
+        <v>6781741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,19 +4078,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,19 +4095,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032187</v>
+        <v>129011216</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4152,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411321</v>
+        <v>411316</v>
       </c>
       <c r="R36" t="n">
-        <v>6781689</v>
+        <v>6781674</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4185,9 +4175,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032764</v>
+        <v>129011229</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410852</v>
+        <v>412001</v>
       </c>
       <c r="R37" t="n">
-        <v>6781859</v>
+        <v>6781693</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,9 +4282,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,19 +4309,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032774</v>
+        <v>129032187</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4346,10 +4356,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411548</v>
+        <v>411321</v>
       </c>
       <c r="R38" t="n">
-        <v>6781798</v>
+        <v>6781689</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4396,22 +4406,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011197</v>
+        <v>129032764</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,21 +4429,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411531</v>
+        <v>410852</v>
       </c>
       <c r="R39" t="n">
-        <v>6781805</v>
+        <v>6781859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,19 +4486,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032739</v>
+        <v>129032774</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410877</v>
+        <v>411548</v>
       </c>
       <c r="R40" t="n">
-        <v>6781741</v>
+        <v>6781798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011202</v>
+        <v>129011215</v>
       </c>
       <c r="B41" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411246</v>
+        <v>411330</v>
       </c>
       <c r="R41" t="n">
-        <v>6781879</v>
+        <v>6781666</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,10 +4719,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129032183</v>
+        <v>129011221</v>
       </c>
       <c r="B42" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4730,21 +4730,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>412070</v>
+        <v>411310</v>
       </c>
       <c r="R42" t="n">
-        <v>6781682</v>
+        <v>6781709</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,9 +4787,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4804,22 +4814,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011215</v>
+        <v>129011202</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4827,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4851,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411330</v>
+        <v>411246</v>
       </c>
       <c r="R43" t="n">
-        <v>6781666</v>
+        <v>6781879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4886,7 +4896,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4896,7 +4906,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4923,10 +4933,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011221</v>
+        <v>129032183</v>
       </c>
       <c r="B44" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4934,21 +4944,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4958,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>411310</v>
+        <v>412070</v>
       </c>
       <c r="R44" t="n">
-        <v>6781709</v>
+        <v>6781682</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4991,19 +5001,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5018,12 +5018,12 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011227</v>
+        <v>129011225</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411730</v>
+        <v>411536</v>
       </c>
       <c r="R54" t="n">
-        <v>6781958</v>
+        <v>6781806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6040,7 +6040,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011213</v>
+        <v>129032750</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411327</v>
+        <v>410717</v>
       </c>
       <c r="R55" t="n">
-        <v>6781657</v>
+        <v>6781843</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,19 +6108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6135,19 +6125,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129032192</v>
+        <v>129011227</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6182,10 +6172,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411504</v>
+        <v>411730</v>
       </c>
       <c r="R56" t="n">
-        <v>6781807</v>
+        <v>6781958</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6215,9 +6205,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6232,19 +6232,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032750</v>
+        <v>129011213</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6279,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>410717</v>
+        <v>411327</v>
       </c>
       <c r="R57" t="n">
-        <v>6781843</v>
+        <v>6781657</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6312,9 +6312,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6329,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129011225</v>
+        <v>129032192</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6376,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411536</v>
+        <v>411504</v>
       </c>
       <c r="R58" t="n">
-        <v>6781806</v>
+        <v>6781807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6409,19 +6419,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032740</v>
+        <v>129011220</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411020</v>
+        <v>411312</v>
       </c>
       <c r="R63" t="n">
-        <v>6781851</v>
+        <v>6781706</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,9 +6914,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6931,19 +6941,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6978,10 +6988,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R64" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,19 +7021,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,22 +7038,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032765</v>
+        <v>129032740</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410893</v>
+        <v>411020</v>
       </c>
       <c r="R65" t="n">
-        <v>6781859</v>
+        <v>6781851</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032772</v>
+        <v>129032746</v>
       </c>
       <c r="B66" t="n">
         <v>79044</v>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411565</v>
+        <v>410697</v>
       </c>
       <c r="R66" t="n">
-        <v>6781780</v>
+        <v>6781752</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7247,7 +7247,7 @@
         <v>129032200</v>
       </c>
       <c r="B67" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032746</v>
+        <v>129032772</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410697</v>
+        <v>411565</v>
       </c>
       <c r="R68" t="n">
-        <v>6781752</v>
+        <v>6781780</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7632,10 +7632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032741</v>
+        <v>129032783</v>
       </c>
       <c r="B71" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,42 +7643,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410958</v>
+        <v>411996</v>
       </c>
       <c r="R71" t="n">
-        <v>6781689</v>
+        <v>6781690</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,7 +7729,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032783</v>
+        <v>129032757</v>
       </c>
       <c r="B72" t="n">
         <v>79044</v>
@@ -7772,10 +7764,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>411996</v>
+        <v>410790</v>
       </c>
       <c r="R72" t="n">
-        <v>6781690</v>
+        <v>6781786</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7834,7 +7826,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032757</v>
+        <v>129032186</v>
       </c>
       <c r="B73" t="n">
         <v>79044</v>
@@ -7869,10 +7861,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>410790</v>
+        <v>411332</v>
       </c>
       <c r="R73" t="n">
-        <v>6781786</v>
+        <v>6781694</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7919,22 +7911,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032186</v>
+        <v>129032741</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7942,34 +7934,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>411332</v>
+        <v>410958</v>
       </c>
       <c r="R74" t="n">
-        <v>6781694</v>
+        <v>6781689</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8016,22 +8016,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032768</v>
+        <v>129032181</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R75" t="n">
-        <v>6781857</v>
+        <v>6781806</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129011230</v>
+        <v>129032767</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>412017</v>
+        <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781667</v>
+        <v>6781848</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,19 +8193,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8220,19 +8210,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032767</v>
+        <v>129032768</v>
       </c>
       <c r="B77" t="n">
         <v>79044</v>
@@ -8270,7 +8260,7 @@
         <v>410959</v>
       </c>
       <c r="R77" t="n">
-        <v>6781848</v>
+        <v>6781857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8329,10 +8319,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032181</v>
+        <v>129011230</v>
       </c>
       <c r="B78" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8340,21 +8330,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8364,10 +8354,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411425</v>
+        <v>412017</v>
       </c>
       <c r="R78" t="n">
-        <v>6781806</v>
+        <v>6781667</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,9 +8387,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -1675,56 +1675,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032786</v>
+        <v>129011211</v>
       </c>
       <c r="B12" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410970</v>
+        <v>411303</v>
       </c>
       <c r="R12" t="n">
-        <v>6781684</v>
+        <v>6781649</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1754,37 +1743,46 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011211</v>
+        <v>129011208</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1819,10 +1817,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411303</v>
+        <v>411221</v>
       </c>
       <c r="R13" t="n">
-        <v>6781649</v>
+        <v>6781624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,7 +1852,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1864,7 +1862,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1889,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011208</v>
+        <v>129011209</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1926,10 +1924,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411221</v>
+        <v>411237</v>
       </c>
       <c r="R14" t="n">
-        <v>6781624</v>
+        <v>6781635</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1961,7 +1959,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1971,7 +1969,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1998,7 +1996,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011209</v>
+        <v>129011212</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2033,10 +2031,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411237</v>
+        <v>411313</v>
       </c>
       <c r="R15" t="n">
-        <v>6781635</v>
+        <v>6781661</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2068,7 +2066,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2078,7 +2076,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2105,7 +2103,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011212</v>
+        <v>129032749</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2140,10 +2138,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411313</v>
+        <v>410719</v>
       </c>
       <c r="R16" t="n">
-        <v>6781661</v>
+        <v>6781851</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,19 +2171,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15:43</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2200,57 +2188,68 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032749</v>
+        <v>129032786</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410719</v>
+        <v>410970</v>
       </c>
       <c r="R17" t="n">
-        <v>6781851</v>
+        <v>6781684</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2291,6 +2290,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2814,56 +2814,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032787</v>
+        <v>129032754</v>
       </c>
       <c r="B23" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410912</v>
+        <v>410774</v>
       </c>
       <c r="R23" t="n">
-        <v>6781662</v>
+        <v>6781776</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,7 +2893,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2911,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032754</v>
+        <v>129011222</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -2958,10 +2946,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410774</v>
+        <v>411303</v>
       </c>
       <c r="R24" t="n">
-        <v>6781776</v>
+        <v>6781896</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2991,9 +2979,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3008,19 +3006,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011222</v>
+        <v>129032755</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3055,10 +3053,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411303</v>
+        <v>410678</v>
       </c>
       <c r="R25" t="n">
-        <v>6781896</v>
+        <v>6781823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,19 +3086,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,19 +3103,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3162,10 +3150,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R26" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,7 +3212,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032759</v>
+        <v>129032761</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3259,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410870</v>
+        <v>410889</v>
       </c>
       <c r="R27" t="n">
-        <v>6781738</v>
+        <v>6781774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3321,45 +3309,56 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032761</v>
+        <v>129032787</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410889</v>
+        <v>410912</v>
       </c>
       <c r="R28" t="n">
-        <v>6781774</v>
+        <v>6781662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3400,6 +3399,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011216</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>411316</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781674</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129011229</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>412001</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,19 +4105,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011216</v>
+        <v>129032187</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411316</v>
+        <v>411321</v>
       </c>
       <c r="R36" t="n">
-        <v>6781674</v>
+        <v>6781689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4185,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011229</v>
+        <v>129032764</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>412001</v>
+        <v>410852</v>
       </c>
       <c r="R37" t="n">
-        <v>6781693</v>
+        <v>6781859</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,19 +4282,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4309,19 +4299,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032187</v>
+        <v>129032774</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4356,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411321</v>
+        <v>411548</v>
       </c>
       <c r="R38" t="n">
-        <v>6781689</v>
+        <v>6781798</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4406,22 +4396,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032764</v>
+        <v>129011197</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4429,21 +4419,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4453,10 +4443,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410852</v>
+        <v>411531</v>
       </c>
       <c r="R39" t="n">
-        <v>6781859</v>
+        <v>6781805</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4486,9 +4476,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032774</v>
+        <v>129032739</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411548</v>
+        <v>410877</v>
       </c>
       <c r="R40" t="n">
-        <v>6781798</v>
+        <v>6781741</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011215</v>
+        <v>128978125</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411330</v>
+        <v>411776</v>
       </c>
       <c r="R41" t="n">
-        <v>6781666</v>
+        <v>6781941</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4719,7 +4719,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011221</v>
+        <v>129011215</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411310</v>
+        <v>411330</v>
       </c>
       <c r="R42" t="n">
-        <v>6781709</v>
+        <v>6781666</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011202</v>
+        <v>129011221</v>
       </c>
       <c r="B43" t="n">
-        <v>78801</v>
+        <v>79044</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411246</v>
+        <v>411310</v>
       </c>
       <c r="R43" t="n">
-        <v>6781879</v>
+        <v>6781709</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4933,10 +4933,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032183</v>
+        <v>129011202</v>
       </c>
       <c r="B44" t="n">
-        <v>79663</v>
+        <v>78801</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>412070</v>
+        <v>411246</v>
       </c>
       <c r="R44" t="n">
-        <v>6781682</v>
+        <v>6781879</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5001,9 +5001,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5018,22 +5028,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128978125</v>
+        <v>129032183</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5041,21 +5051,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411776</v>
+        <v>412070</v>
       </c>
       <c r="R45" t="n">
-        <v>6781941</v>
+        <v>6781682</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,19 +5108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6040,7 +6040,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129032750</v>
+        <v>129011227</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>410717</v>
+        <v>411730</v>
       </c>
       <c r="R55" t="n">
-        <v>6781843</v>
+        <v>6781958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,9 +6108,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6125,19 +6135,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011227</v>
+        <v>129011213</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6172,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411730</v>
+        <v>411327</v>
       </c>
       <c r="R56" t="n">
-        <v>6781958</v>
+        <v>6781657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6207,7 +6217,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6217,7 +6227,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6244,7 +6254,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011213</v>
+        <v>129032192</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6279,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411327</v>
+        <v>411504</v>
       </c>
       <c r="R57" t="n">
-        <v>6781657</v>
+        <v>6781807</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6312,19 +6322,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032192</v>
+        <v>129032750</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411504</v>
+        <v>410717</v>
       </c>
       <c r="R58" t="n">
-        <v>6781807</v>
+        <v>6781843</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011220</v>
+        <v>129032740</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411312</v>
+        <v>411020</v>
       </c>
       <c r="R63" t="n">
-        <v>6781706</v>
+        <v>6781851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,19 +6914,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,19 +6931,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032765</v>
+        <v>129011220</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6988,10 +6978,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410893</v>
+        <v>411312</v>
       </c>
       <c r="R64" t="n">
-        <v>6781859</v>
+        <v>6781706</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7021,9 +7011,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,22 +7038,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032740</v>
+        <v>129032765</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411020</v>
+        <v>410893</v>
       </c>
       <c r="R65" t="n">
-        <v>6781851</v>
+        <v>6781859</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032746</v>
+        <v>129032772</v>
       </c>
       <c r="B66" t="n">
         <v>79044</v>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>410697</v>
+        <v>411565</v>
       </c>
       <c r="R66" t="n">
-        <v>6781752</v>
+        <v>6781780</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7244,32 +7244,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032200</v>
+        <v>129032746</v>
       </c>
       <c r="B67" t="n">
-        <v>92831</v>
+        <v>79044</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411326</v>
+        <v>410697</v>
       </c>
       <c r="R67" t="n">
-        <v>6781874</v>
+        <v>6781752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7329,19 +7329,19 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032772</v>
+        <v>129032189</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411565</v>
+        <v>411250</v>
       </c>
       <c r="R68" t="n">
-        <v>6781780</v>
+        <v>6781886</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,19 +7426,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032189</v>
+        <v>129032760</v>
       </c>
       <c r="B69" t="n">
         <v>79044</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411250</v>
+        <v>410875</v>
       </c>
       <c r="R69" t="n">
-        <v>6781886</v>
+        <v>6781746</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,44 +7523,44 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032760</v>
+        <v>129032200</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410875</v>
+        <v>411326</v>
       </c>
       <c r="R70" t="n">
-        <v>6781746</v>
+        <v>6781874</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,12 +7620,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -8028,10 +8028,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032181</v>
+        <v>129032767</v>
       </c>
       <c r="B75" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R75" t="n">
-        <v>6781806</v>
+        <v>6781848</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032767</v>
+        <v>129032768</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781848</v>
+        <v>6781857</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,7 +8222,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032768</v>
+        <v>129011230</v>
       </c>
       <c r="B77" t="n">
         <v>79044</v>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R77" t="n">
-        <v>6781857</v>
+        <v>6781667</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,9 +8290,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8307,22 +8317,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011230</v>
+        <v>129032181</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8330,21 +8340,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8354,10 +8364,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412017</v>
+        <v>411425</v>
       </c>
       <c r="R78" t="n">
-        <v>6781667</v>
+        <v>6781806</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8387,19 +8397,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032188</v>
+        <v>129032745</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411295</v>
+        <v>411010</v>
       </c>
       <c r="R5" t="n">
-        <v>6781724</v>
+        <v>6781686</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1061,12 +1061,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1170,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032745</v>
+        <v>129032188</v>
       </c>
       <c r="B7" t="n">
         <v>79044</v>
@@ -1205,10 +1205,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411010</v>
+        <v>411295</v>
       </c>
       <c r="R7" t="n">
-        <v>6781686</v>
+        <v>6781724</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1255,12 +1255,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011228</v>
+        <v>129011217</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411779</v>
+        <v>411318</v>
       </c>
       <c r="R9" t="n">
-        <v>6781900</v>
+        <v>6781689</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129032766</v>
+        <v>129011228</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>410949</v>
+        <v>411779</v>
       </c>
       <c r="R10" t="n">
-        <v>6781860</v>
+        <v>6781900</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,9 +1539,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:03</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1556,19 +1566,19 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129011217</v>
+        <v>129032766</v>
       </c>
       <c r="B11" t="n">
         <v>79044</v>
@@ -1603,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>411318</v>
+        <v>410949</v>
       </c>
       <c r="R11" t="n">
-        <v>6781689</v>
+        <v>6781860</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1636,19 +1646,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1663,57 +1663,68 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129011211</v>
+        <v>129032786</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>411303</v>
+        <v>410970</v>
       </c>
       <c r="R12" t="n">
-        <v>6781649</v>
+        <v>6781684</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1743,46 +1754,37 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011208</v>
+        <v>129032749</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1817,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411221</v>
+        <v>410719</v>
       </c>
       <c r="R13" t="n">
-        <v>6781624</v>
+        <v>6781851</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1850,19 +1852,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1877,19 +1869,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011209</v>
+        <v>129011212</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1924,10 +1916,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411237</v>
+        <v>411313</v>
       </c>
       <c r="R14" t="n">
-        <v>6781635</v>
+        <v>6781661</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,7 +1951,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1969,7 +1961,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1996,7 +1988,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011212</v>
+        <v>129011209</v>
       </c>
       <c r="B15" t="n">
         <v>79044</v>
@@ -2031,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411313</v>
+        <v>411237</v>
       </c>
       <c r="R15" t="n">
-        <v>6781661</v>
+        <v>6781635</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2066,7 +2058,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2076,7 +2068,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2103,7 +2095,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129032749</v>
+        <v>129011208</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2138,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>410719</v>
+        <v>411221</v>
       </c>
       <c r="R16" t="n">
-        <v>6781851</v>
+        <v>6781624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2171,9 +2163,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,68 +2190,57 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032786</v>
+        <v>129011211</v>
       </c>
       <c r="B17" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410970</v>
+        <v>411303</v>
       </c>
       <c r="R17" t="n">
-        <v>6781684</v>
+        <v>6781649</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2279,37 +2270,46 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032758</v>
+        <v>129011207</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410842</v>
+        <v>411175</v>
       </c>
       <c r="R18" t="n">
-        <v>6781713</v>
+        <v>6781624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,9 +2377,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,19 +2404,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011219</v>
+        <v>129032751</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2441,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411315</v>
+        <v>410727</v>
       </c>
       <c r="R19" t="n">
-        <v>6781704</v>
+        <v>6781837</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,19 +2484,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,19 +2501,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032751</v>
+        <v>129011219</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2548,10 +2548,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410727</v>
+        <v>411315</v>
       </c>
       <c r="R20" t="n">
-        <v>6781837</v>
+        <v>6781704</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,9 +2581,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2598,12 +2608,12 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2707,7 +2717,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011207</v>
+        <v>129032758</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2742,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411175</v>
+        <v>410842</v>
       </c>
       <c r="R22" t="n">
-        <v>6781624</v>
+        <v>6781713</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2775,19 +2785,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,57 +2802,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032754</v>
+        <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410774</v>
+        <v>410912</v>
       </c>
       <c r="R23" t="n">
-        <v>6781776</v>
+        <v>6781662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2904,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2911,7 +2923,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011222</v>
+        <v>129032761</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -2946,10 +2958,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411303</v>
+        <v>410889</v>
       </c>
       <c r="R24" t="n">
-        <v>6781896</v>
+        <v>6781774</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2979,19 +2991,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3006,19 +3008,19 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3053,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R25" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3115,7 +3117,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032759</v>
+        <v>129032755</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3150,10 +3152,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410870</v>
+        <v>410678</v>
       </c>
       <c r="R26" t="n">
-        <v>6781738</v>
+        <v>6781823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,7 +3214,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032761</v>
+        <v>129011222</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3247,10 +3249,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410889</v>
+        <v>411303</v>
       </c>
       <c r="R27" t="n">
-        <v>6781774</v>
+        <v>6781896</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3280,9 +3282,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3297,68 +3309,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032787</v>
+        <v>129032754</v>
       </c>
       <c r="B28" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410912</v>
+        <v>410774</v>
       </c>
       <c r="R28" t="n">
-        <v>6781662</v>
+        <v>6781776</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,7 +3400,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032762</v>
+        <v>129032771</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410890</v>
+        <v>411508</v>
       </c>
       <c r="R29" t="n">
-        <v>6781771</v>
+        <v>6781794</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032771</v>
+        <v>129032762</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411508</v>
+        <v>410890</v>
       </c>
       <c r="R30" t="n">
-        <v>6781794</v>
+        <v>6781771</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032180</v>
+        <v>129032201</v>
       </c>
       <c r="B32" t="n">
         <v>79663</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411312</v>
+        <v>411198</v>
       </c>
       <c r="R32" t="n">
-        <v>6781871</v>
+        <v>6781834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032201</v>
+        <v>129032180</v>
       </c>
       <c r="B33" t="n">
         <v>79663</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411198</v>
+        <v>411312</v>
       </c>
       <c r="R33" t="n">
-        <v>6781834</v>
+        <v>6781871</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3903,10 +3903,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011216</v>
+        <v>129011197</v>
       </c>
       <c r="B34" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3914,21 +3914,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +3938,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411316</v>
+        <v>411531</v>
       </c>
       <c r="R34" t="n">
-        <v>6781674</v>
+        <v>6781805</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +3973,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +3983,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011229</v>
+        <v>129032739</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>412001</v>
+        <v>410877</v>
       </c>
       <c r="R35" t="n">
-        <v>6781693</v>
+        <v>6781741</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,19 +4078,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4105,19 +4095,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032187</v>
+        <v>129011229</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4152,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411321</v>
+        <v>412001</v>
       </c>
       <c r="R36" t="n">
-        <v>6781689</v>
+        <v>6781693</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4185,9 +4175,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:14</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4202,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032764</v>
+        <v>129032187</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4249,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410852</v>
+        <v>411321</v>
       </c>
       <c r="R37" t="n">
-        <v>6781859</v>
+        <v>6781689</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4299,19 +4299,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129032774</v>
+        <v>129011216</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411548</v>
+        <v>411316</v>
       </c>
       <c r="R38" t="n">
-        <v>6781798</v>
+        <v>6781674</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4379,9 +4379,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4396,22 +4406,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129011197</v>
+        <v>129032774</v>
       </c>
       <c r="B39" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4419,21 +4429,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4443,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411531</v>
+        <v>411548</v>
       </c>
       <c r="R39" t="n">
-        <v>6781805</v>
+        <v>6781798</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4476,19 +4486,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>13:39</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>13:39</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4503,22 +4503,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032739</v>
+        <v>129032764</v>
       </c>
       <c r="B40" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4526,21 +4526,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410877</v>
+        <v>410852</v>
       </c>
       <c r="R40" t="n">
-        <v>6781741</v>
+        <v>6781859</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011215</v>
+        <v>129011221</v>
       </c>
       <c r="B42" t="n">
         <v>79044</v>
@@ -4754,10 +4754,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411330</v>
+        <v>411310</v>
       </c>
       <c r="R42" t="n">
-        <v>6781666</v>
+        <v>6781709</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -4799,7 +4799,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:41</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011221</v>
+        <v>129032183</v>
       </c>
       <c r="B43" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411310</v>
+        <v>412070</v>
       </c>
       <c r="R43" t="n">
-        <v>6781709</v>
+        <v>6781682</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,19 +4894,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4921,12 +4911,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5040,10 +5030,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032183</v>
+        <v>129011215</v>
       </c>
       <c r="B45" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412070</v>
+        <v>411330</v>
       </c>
       <c r="R45" t="n">
-        <v>6781682</v>
+        <v>6781666</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,9 +5098,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011224</v>
+        <v>129032769</v>
       </c>
       <c r="B48" t="n">
         <v>79044</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411539</v>
+        <v>411017</v>
       </c>
       <c r="R48" t="n">
-        <v>6781802</v>
+        <v>6781839</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,19 +5399,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5426,19 +5416,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032184</v>
+        <v>129011206</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5473,10 +5463,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411414</v>
+        <v>411166</v>
       </c>
       <c r="R49" t="n">
-        <v>6781817</v>
+        <v>6781615</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5506,9 +5496,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5523,19 +5523,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011206</v>
+        <v>129011224</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411166</v>
+        <v>411539</v>
       </c>
       <c r="R50" t="n">
-        <v>6781615</v>
+        <v>6781802</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032191</v>
+        <v>129032184</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411495</v>
+        <v>411414</v>
       </c>
       <c r="R51" t="n">
-        <v>6781803</v>
+        <v>6781817</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032769</v>
+        <v>129032191</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411017</v>
+        <v>411495</v>
       </c>
       <c r="R52" t="n">
-        <v>6781839</v>
+        <v>6781803</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011225</v>
+        <v>129032750</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411536</v>
+        <v>410717</v>
       </c>
       <c r="R54" t="n">
-        <v>6781806</v>
+        <v>6781843</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,19 +6001,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6028,19 +6018,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011227</v>
+        <v>129011213</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6075,10 +6065,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411730</v>
+        <v>411327</v>
       </c>
       <c r="R55" t="n">
-        <v>6781958</v>
+        <v>6781657</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6110,7 +6100,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6120,7 +6110,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6147,7 +6137,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011213</v>
+        <v>129011225</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6182,10 +6172,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411327</v>
+        <v>411536</v>
       </c>
       <c r="R56" t="n">
-        <v>6781657</v>
+        <v>6781806</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6217,7 +6207,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6227,7 +6217,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6254,7 +6244,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032192</v>
+        <v>129011227</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6289,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411504</v>
+        <v>411730</v>
       </c>
       <c r="R57" t="n">
-        <v>6781807</v>
+        <v>6781958</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6322,9 +6312,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032750</v>
+        <v>129032192</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410717</v>
+        <v>411504</v>
       </c>
       <c r="R58" t="n">
-        <v>6781843</v>
+        <v>6781807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6642,7 +6642,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -6677,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R61" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,19 +6710,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,19 +6727,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032770</v>
+        <v>129011218</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -6784,10 +6774,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411070</v>
+        <v>411322</v>
       </c>
       <c r="R62" t="n">
-        <v>6781879</v>
+        <v>6781695</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6817,9 +6807,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,22 +6834,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032740</v>
+        <v>129032765</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411020</v>
+        <v>410893</v>
       </c>
       <c r="R63" t="n">
-        <v>6781851</v>
+        <v>6781859</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7050,10 +7050,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032765</v>
+        <v>129032740</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7061,21 +7061,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>410893</v>
+        <v>411020</v>
       </c>
       <c r="R65" t="n">
-        <v>6781859</v>
+        <v>6781851</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7147,7 +7147,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032772</v>
+        <v>129032189</v>
       </c>
       <c r="B66" t="n">
         <v>79044</v>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411565</v>
+        <v>411250</v>
       </c>
       <c r="R66" t="n">
-        <v>6781780</v>
+        <v>6781886</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,19 +7232,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032746</v>
+        <v>129032772</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410697</v>
+        <v>411565</v>
       </c>
       <c r="R67" t="n">
-        <v>6781752</v>
+        <v>6781780</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032189</v>
+        <v>129032746</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411250</v>
+        <v>410697</v>
       </c>
       <c r="R68" t="n">
-        <v>6781886</v>
+        <v>6781752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,12 +7426,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7632,10 +7632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032783</v>
+        <v>129032741</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,34 +7643,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411996</v>
+        <v>410958</v>
       </c>
       <c r="R71" t="n">
-        <v>6781690</v>
+        <v>6781689</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7729,7 +7737,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032757</v>
+        <v>129032186</v>
       </c>
       <c r="B72" t="n">
         <v>79044</v>
@@ -7764,10 +7772,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410790</v>
+        <v>411332</v>
       </c>
       <c r="R72" t="n">
-        <v>6781786</v>
+        <v>6781694</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7814,19 +7822,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032186</v>
+        <v>129032783</v>
       </c>
       <c r="B73" t="n">
         <v>79044</v>
@@ -7861,10 +7869,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411332</v>
+        <v>411996</v>
       </c>
       <c r="R73" t="n">
-        <v>6781694</v>
+        <v>6781690</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,22 +7919,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032741</v>
+        <v>129032757</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7934,42 +7942,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410958</v>
+        <v>410790</v>
       </c>
       <c r="R74" t="n">
-        <v>6781689</v>
+        <v>6781786</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8125,7 +8125,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032768</v>
+        <v>129011230</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R76" t="n">
-        <v>6781857</v>
+        <v>6781667</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,9 +8193,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8210,22 +8220,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129011230</v>
+        <v>129032181</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8243,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8267,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>412017</v>
+        <v>411425</v>
       </c>
       <c r="R77" t="n">
-        <v>6781667</v>
+        <v>6781806</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8290,19 +8300,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8317,22 +8317,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032181</v>
+        <v>129032768</v>
       </c>
       <c r="B78" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8340,21 +8340,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8364,10 +8364,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R78" t="n">
-        <v>6781806</v>
+        <v>6781857</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -2814,56 +2814,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032787</v>
+        <v>129032761</v>
       </c>
       <c r="B23" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410912</v>
+        <v>410889</v>
       </c>
       <c r="R23" t="n">
-        <v>6781662</v>
+        <v>6781774</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2904,7 +2893,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2923,7 +2911,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032761</v>
+        <v>129032759</v>
       </c>
       <c r="B24" t="n">
         <v>79044</v>
@@ -2958,10 +2946,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410889</v>
+        <v>410870</v>
       </c>
       <c r="R24" t="n">
-        <v>6781774</v>
+        <v>6781738</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3020,7 +3008,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032759</v>
+        <v>129032755</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3055,10 +3043,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410870</v>
+        <v>410678</v>
       </c>
       <c r="R25" t="n">
-        <v>6781738</v>
+        <v>6781823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3117,7 +3105,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032755</v>
+        <v>129011222</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3152,10 +3140,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410678</v>
+        <v>411303</v>
       </c>
       <c r="R26" t="n">
-        <v>6781823</v>
+        <v>6781896</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3185,9 +3173,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3202,19 +3200,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129011222</v>
+        <v>129032754</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3249,10 +3247,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>411303</v>
+        <v>410774</v>
       </c>
       <c r="R27" t="n">
-        <v>6781896</v>
+        <v>6781776</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3282,19 +3280,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3309,57 +3297,68 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032754</v>
+        <v>129032787</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>92832</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410774</v>
+        <v>410912</v>
       </c>
       <c r="R28" t="n">
-        <v>6781776</v>
+        <v>6781662</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3400,6 +3399,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -6846,10 +6846,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032765</v>
+        <v>129032740</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>410893</v>
+        <v>411020</v>
       </c>
       <c r="R63" t="n">
-        <v>6781859</v>
+        <v>6781851</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6943,7 +6943,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129011220</v>
+        <v>129032765</v>
       </c>
       <c r="B64" t="n">
         <v>79044</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>411312</v>
+        <v>410893</v>
       </c>
       <c r="R64" t="n">
-        <v>6781706</v>
+        <v>6781859</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7011,19 +7011,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7038,22 +7028,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032740</v>
+        <v>129011220</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7061,21 +7051,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411020</v>
+        <v>411312</v>
       </c>
       <c r="R65" t="n">
-        <v>6781851</v>
+        <v>6781706</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7118,9 +7108,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7135,12 +7135,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -7632,10 +7632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032741</v>
+        <v>129032186</v>
       </c>
       <c r="B71" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,42 +7643,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410958</v>
+        <v>411332</v>
       </c>
       <c r="R71" t="n">
-        <v>6781689</v>
+        <v>6781694</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7725,19 +7717,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032186</v>
+        <v>129032783</v>
       </c>
       <c r="B72" t="n">
         <v>79044</v>
@@ -7772,10 +7764,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>411332</v>
+        <v>411996</v>
       </c>
       <c r="R72" t="n">
-        <v>6781694</v>
+        <v>6781690</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7822,19 +7814,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032783</v>
+        <v>129032757</v>
       </c>
       <c r="B73" t="n">
         <v>79044</v>
@@ -7869,10 +7861,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411996</v>
+        <v>410790</v>
       </c>
       <c r="R73" t="n">
-        <v>6781690</v>
+        <v>6781786</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7931,10 +7923,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032757</v>
+        <v>129032741</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7942,34 +7934,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410790</v>
+        <v>410958</v>
       </c>
       <c r="R74" t="n">
-        <v>6781786</v>
+        <v>6781689</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032756</v>
+        <v>129032781</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410745</v>
+        <v>411940</v>
       </c>
       <c r="R6" t="n">
-        <v>6781852</v>
+        <v>6781749</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032781</v>
+        <v>129032756</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411940</v>
+        <v>410745</v>
       </c>
       <c r="R8" t="n">
-        <v>6781749</v>
+        <v>6781852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011217</v>
+        <v>129011228</v>
       </c>
       <c r="B9" t="n">
         <v>79044</v>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411318</v>
+        <v>411779</v>
       </c>
       <c r="R9" t="n">
-        <v>6781689</v>
+        <v>6781900</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1471,7 +1471,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011228</v>
+        <v>129011217</v>
       </c>
       <c r="B10" t="n">
         <v>79044</v>
@@ -1506,10 +1506,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411779</v>
+        <v>411318</v>
       </c>
       <c r="R10" t="n">
-        <v>6781900</v>
+        <v>6781689</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1551,7 +1551,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1678,7 +1678,7 @@
         <v>129032786</v>
       </c>
       <c r="B12" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129032749</v>
+        <v>129011211</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>410719</v>
+        <v>411303</v>
       </c>
       <c r="R13" t="n">
-        <v>6781851</v>
+        <v>6781649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1852,9 +1852,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1869,19 +1879,19 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011212</v>
+        <v>129011208</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1916,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411313</v>
+        <v>411221</v>
       </c>
       <c r="R14" t="n">
-        <v>6781661</v>
+        <v>6781624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1951,7 +1961,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -1961,7 +1971,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2095,7 +2105,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011208</v>
+        <v>129011212</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2130,10 +2140,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411221</v>
+        <v>411313</v>
       </c>
       <c r="R16" t="n">
-        <v>6781624</v>
+        <v>6781661</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,7 +2175,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2175,7 +2185,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2202,7 +2212,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129011211</v>
+        <v>129032749</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2237,10 +2247,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411303</v>
+        <v>410719</v>
       </c>
       <c r="R17" t="n">
-        <v>6781649</v>
+        <v>6781851</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2270,19 +2280,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:45</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:45</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,19 +2297,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011207</v>
+        <v>129011219</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411175</v>
+        <v>411315</v>
       </c>
       <c r="R18" t="n">
-        <v>6781624</v>
+        <v>6781704</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2389,7 +2389,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2416,7 +2416,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032751</v>
+        <v>129011207</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2451,10 +2451,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>410727</v>
+        <v>411175</v>
       </c>
       <c r="R19" t="n">
-        <v>6781837</v>
+        <v>6781624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,9 +2484,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2501,19 +2511,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011219</v>
+        <v>129032758</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2548,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>411315</v>
+        <v>410842</v>
       </c>
       <c r="R20" t="n">
-        <v>6781704</v>
+        <v>6781713</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2581,19 +2591,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,19 +2608,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032780</v>
+        <v>129032751</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2655,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>411808</v>
+        <v>410727</v>
       </c>
       <c r="R21" t="n">
-        <v>6781897</v>
+        <v>6781837</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,7 +2717,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032758</v>
+        <v>129032780</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2752,10 +2752,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>410842</v>
+        <v>411808</v>
       </c>
       <c r="R22" t="n">
-        <v>6781713</v>
+        <v>6781897</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2911,45 +2911,56 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032759</v>
+        <v>129032787</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410870</v>
+        <v>410912</v>
       </c>
       <c r="R24" t="n">
-        <v>6781738</v>
+        <v>6781662</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,6 +3001,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3008,7 +3020,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032755</v>
+        <v>129011222</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3043,10 +3055,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410678</v>
+        <v>411303</v>
       </c>
       <c r="R25" t="n">
-        <v>6781823</v>
+        <v>6781896</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3076,9 +3088,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3093,19 +3115,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129011222</v>
+        <v>129032755</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3140,10 +3162,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>411303</v>
+        <v>410678</v>
       </c>
       <c r="R26" t="n">
-        <v>6781896</v>
+        <v>6781823</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3173,19 +3195,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3200,19 +3212,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032754</v>
+        <v>129032759</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3247,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410774</v>
+        <v>410870</v>
       </c>
       <c r="R27" t="n">
-        <v>6781776</v>
+        <v>6781738</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3309,56 +3321,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032787</v>
+        <v>129032754</v>
       </c>
       <c r="B28" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410912</v>
+        <v>410774</v>
       </c>
       <c r="R28" t="n">
-        <v>6781662</v>
+        <v>6781776</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3399,7 +3400,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3709,7 +3709,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032201</v>
+        <v>129032180</v>
       </c>
       <c r="B32" t="n">
         <v>79663</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411198</v>
+        <v>411312</v>
       </c>
       <c r="R32" t="n">
-        <v>6781834</v>
+        <v>6781871</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032180</v>
+        <v>129032201</v>
       </c>
       <c r="B33" t="n">
         <v>79663</v>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411312</v>
+        <v>411198</v>
       </c>
       <c r="R33" t="n">
-        <v>6781871</v>
+        <v>6781834</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4107,7 +4107,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129011229</v>
+        <v>129032764</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4142,10 +4142,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>412001</v>
+        <v>410852</v>
       </c>
       <c r="R36" t="n">
-        <v>6781693</v>
+        <v>6781859</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4175,19 +4175,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,19 +4192,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032187</v>
+        <v>129011216</v>
       </c>
       <c r="B37" t="n">
         <v>79044</v>
@@ -4249,10 +4239,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411321</v>
+        <v>411316</v>
       </c>
       <c r="R37" t="n">
-        <v>6781689</v>
+        <v>6781674</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,9 +4272,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,19 +4299,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011216</v>
+        <v>129011229</v>
       </c>
       <c r="B38" t="n">
         <v>79044</v>
@@ -4346,10 +4346,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>411316</v>
+        <v>412001</v>
       </c>
       <c r="R38" t="n">
-        <v>6781674</v>
+        <v>6781693</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4381,7 +4381,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4418,7 +4418,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032774</v>
+        <v>129032187</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411548</v>
+        <v>411321</v>
       </c>
       <c r="R39" t="n">
-        <v>6781798</v>
+        <v>6781689</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,19 +4503,19 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032764</v>
+        <v>129032774</v>
       </c>
       <c r="B40" t="n">
         <v>79044</v>
@@ -4550,10 +4550,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>410852</v>
+        <v>411548</v>
       </c>
       <c r="R40" t="n">
-        <v>6781859</v>
+        <v>6781798</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4612,10 +4612,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128978125</v>
+        <v>129011215</v>
       </c>
       <c r="B41" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4623,21 +4623,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4647,10 +4647,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411776</v>
+        <v>411330</v>
       </c>
       <c r="R41" t="n">
-        <v>6781941</v>
+        <v>6781666</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4682,7 +4682,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129032183</v>
+        <v>128978125</v>
       </c>
       <c r="B43" t="n">
-        <v>79663</v>
+        <v>79076</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>412070</v>
+        <v>411776</v>
       </c>
       <c r="R43" t="n">
-        <v>6781682</v>
+        <v>6781941</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,9 +4894,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4911,12 +4921,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5030,10 +5040,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129011215</v>
+        <v>129032183</v>
       </c>
       <c r="B45" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5041,21 +5051,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5075,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411330</v>
+        <v>412070</v>
       </c>
       <c r="R45" t="n">
-        <v>6781666</v>
+        <v>6781682</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,19 +5108,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032769</v>
+        <v>129011224</v>
       </c>
       <c r="B48" t="n">
         <v>79044</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411017</v>
+        <v>411539</v>
       </c>
       <c r="R48" t="n">
-        <v>6781839</v>
+        <v>6781802</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,9 +5399,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5416,19 +5426,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129011206</v>
+        <v>129032184</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5463,10 +5473,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411166</v>
+        <v>411414</v>
       </c>
       <c r="R49" t="n">
-        <v>6781615</v>
+        <v>6781817</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5496,19 +5506,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5523,19 +5523,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011224</v>
+        <v>129011206</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411539</v>
+        <v>411166</v>
       </c>
       <c r="R50" t="n">
-        <v>6781802</v>
+        <v>6781615</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5642,7 +5642,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032184</v>
+        <v>129032191</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5677,10 +5677,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411414</v>
+        <v>411495</v>
       </c>
       <c r="R51" t="n">
-        <v>6781817</v>
+        <v>6781803</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5739,7 +5739,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032191</v>
+        <v>129032769</v>
       </c>
       <c r="B52" t="n">
         <v>79044</v>
@@ -5774,10 +5774,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411495</v>
+        <v>411017</v>
       </c>
       <c r="R52" t="n">
-        <v>6781803</v>
+        <v>6781839</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5824,12 +5824,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129032750</v>
+        <v>129011225</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>410717</v>
+        <v>411536</v>
       </c>
       <c r="R54" t="n">
-        <v>6781843</v>
+        <v>6781806</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,9 +6001,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6018,19 +6028,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011213</v>
+        <v>129011227</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6065,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411327</v>
+        <v>411730</v>
       </c>
       <c r="R55" t="n">
-        <v>6781657</v>
+        <v>6781958</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6100,7 +6110,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6110,7 +6120,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6137,7 +6147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011225</v>
+        <v>129011213</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6172,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411536</v>
+        <v>411327</v>
       </c>
       <c r="R56" t="n">
-        <v>6781806</v>
+        <v>6781657</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6207,7 +6217,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6217,7 +6227,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6244,7 +6254,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011227</v>
+        <v>129032192</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6279,10 +6289,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411730</v>
+        <v>411504</v>
       </c>
       <c r="R57" t="n">
-        <v>6781958</v>
+        <v>6781807</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6312,19 +6322,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032192</v>
+        <v>129032750</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411504</v>
+        <v>410717</v>
       </c>
       <c r="R58" t="n">
-        <v>6781807</v>
+        <v>6781843</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032778</v>
+        <v>129011218</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411824</v>
+        <v>411322</v>
       </c>
       <c r="R60" t="n">
-        <v>6781940</v>
+        <v>6781695</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6613,9 +6613,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6630,19 +6640,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032770</v>
+        <v>129032778</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -6677,10 +6687,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411070</v>
+        <v>411824</v>
       </c>
       <c r="R61" t="n">
-        <v>6781879</v>
+        <v>6781940</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6739,7 +6749,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129011218</v>
+        <v>129032770</v>
       </c>
       <c r="B62" t="n">
         <v>79044</v>
@@ -6774,10 +6784,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411322</v>
+        <v>411070</v>
       </c>
       <c r="R62" t="n">
-        <v>6781695</v>
+        <v>6781879</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6807,19 +6817,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6834,22 +6834,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129032740</v>
+        <v>129011220</v>
       </c>
       <c r="B63" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6857,21 +6857,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411020</v>
+        <v>411312</v>
       </c>
       <c r="R63" t="n">
-        <v>6781851</v>
+        <v>6781706</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,9 +6914,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6931,12 +6941,12 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
@@ -7040,10 +7050,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129011220</v>
+        <v>129032740</v>
       </c>
       <c r="B65" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7051,21 +7061,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7075,10 +7085,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411312</v>
+        <v>411020</v>
       </c>
       <c r="R65" t="n">
-        <v>6781706</v>
+        <v>6781851</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7108,19 +7118,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7135,44 +7135,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032189</v>
+        <v>129032200</v>
       </c>
       <c r="B66" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411250</v>
+        <v>411326</v>
       </c>
       <c r="R66" t="n">
-        <v>6781886</v>
+        <v>6781874</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032772</v>
+        <v>129032746</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411565</v>
+        <v>410697</v>
       </c>
       <c r="R67" t="n">
-        <v>6781780</v>
+        <v>6781752</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032746</v>
+        <v>129032189</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410697</v>
+        <v>411250</v>
       </c>
       <c r="R68" t="n">
-        <v>6781752</v>
+        <v>6781886</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,19 +7426,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032760</v>
+        <v>129032772</v>
       </c>
       <c r="B69" t="n">
         <v>79044</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>410875</v>
+        <v>411565</v>
       </c>
       <c r="R69" t="n">
-        <v>6781746</v>
+        <v>6781780</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7535,32 +7535,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032200</v>
+        <v>129032760</v>
       </c>
       <c r="B70" t="n">
-        <v>92832</v>
+        <v>79044</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7570,10 +7570,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>411326</v>
+        <v>410875</v>
       </c>
       <c r="R70" t="n">
-        <v>6781874</v>
+        <v>6781746</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7620,22 +7620,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032186</v>
+        <v>129032741</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,34 +7643,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411332</v>
+        <v>410958</v>
       </c>
       <c r="R71" t="n">
-        <v>6781694</v>
+        <v>6781689</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7717,12 +7725,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7826,7 +7834,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032757</v>
+        <v>129032186</v>
       </c>
       <c r="B73" t="n">
         <v>79044</v>
@@ -7861,10 +7869,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>410790</v>
+        <v>411332</v>
       </c>
       <c r="R73" t="n">
-        <v>6781786</v>
+        <v>6781694</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,22 +7919,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032741</v>
+        <v>129032757</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7934,42 +7942,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410958</v>
+        <v>410790</v>
       </c>
       <c r="R74" t="n">
-        <v>6781689</v>
+        <v>6781786</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8125,7 +8125,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129011230</v>
+        <v>129032768</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8160,10 +8160,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>412017</v>
+        <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781667</v>
+        <v>6781857</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8193,19 +8193,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8220,12 +8210,12 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -8329,7 +8319,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129032768</v>
+        <v>129011230</v>
       </c>
       <c r="B78" t="n">
         <v>79044</v>
@@ -8364,10 +8354,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>410959</v>
+        <v>412017</v>
       </c>
       <c r="R78" t="n">
-        <v>6781857</v>
+        <v>6781667</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8397,9 +8387,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,12 +8414,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -976,7 +976,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032745</v>
+        <v>129032756</v>
       </c>
       <c r="B5" t="n">
         <v>79044</v>
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>411010</v>
+        <v>410745</v>
       </c>
       <c r="R5" t="n">
-        <v>6781686</v>
+        <v>6781852</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,7 +1073,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032781</v>
+        <v>129032745</v>
       </c>
       <c r="B6" t="n">
         <v>79044</v>
@@ -1108,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411940</v>
+        <v>411010</v>
       </c>
       <c r="R6" t="n">
-        <v>6781749</v>
+        <v>6781686</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1267,7 +1267,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032756</v>
+        <v>129032781</v>
       </c>
       <c r="B8" t="n">
         <v>79044</v>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>410745</v>
+        <v>411940</v>
       </c>
       <c r="R8" t="n">
-        <v>6781852</v>
+        <v>6781749</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1784,7 +1784,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011211</v>
+        <v>129011212</v>
       </c>
       <c r="B13" t="n">
         <v>79044</v>
@@ -1819,10 +1819,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411303</v>
+        <v>411313</v>
       </c>
       <c r="R13" t="n">
-        <v>6781649</v>
+        <v>6781661</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,7 +1891,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129011208</v>
+        <v>129032749</v>
       </c>
       <c r="B14" t="n">
         <v>79044</v>
@@ -1926,10 +1926,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>411221</v>
+        <v>410719</v>
       </c>
       <c r="R14" t="n">
-        <v>6781624</v>
+        <v>6781851</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,19 +1959,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>15:57</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>15:57</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1986,12 +1976,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2105,7 +2095,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011212</v>
+        <v>129011211</v>
       </c>
       <c r="B16" t="n">
         <v>79044</v>
@@ -2140,10 +2130,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411313</v>
+        <v>411303</v>
       </c>
       <c r="R16" t="n">
-        <v>6781661</v>
+        <v>6781649</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2175,7 +2165,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2185,7 +2175,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2212,7 +2202,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129032749</v>
+        <v>129011208</v>
       </c>
       <c r="B17" t="n">
         <v>79044</v>
@@ -2247,10 +2237,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>410719</v>
+        <v>411221</v>
       </c>
       <c r="R17" t="n">
-        <v>6781851</v>
+        <v>6781624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2280,9 +2270,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:57</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2297,19 +2297,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129011219</v>
+        <v>129032751</v>
       </c>
       <c r="B18" t="n">
         <v>79044</v>
@@ -2344,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>411315</v>
+        <v>410727</v>
       </c>
       <c r="R18" t="n">
-        <v>6781704</v>
+        <v>6781837</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,19 +2377,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2404,19 +2394,19 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129011207</v>
+        <v>129032780</v>
       </c>
       <c r="B19" t="n">
         <v>79044</v>
@@ -2451,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411175</v>
+        <v>411808</v>
       </c>
       <c r="R19" t="n">
-        <v>6781624</v>
+        <v>6781897</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2484,19 +2474,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>16:05</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>16:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2511,19 +2491,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129032758</v>
+        <v>129011207</v>
       </c>
       <c r="B20" t="n">
         <v>79044</v>
@@ -2558,10 +2538,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>410842</v>
+        <v>411175</v>
       </c>
       <c r="R20" t="n">
-        <v>6781713</v>
+        <v>6781624</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2591,9 +2571,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2608,19 +2598,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032751</v>
+        <v>129032758</v>
       </c>
       <c r="B21" t="n">
         <v>79044</v>
@@ -2655,10 +2645,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410727</v>
+        <v>410842</v>
       </c>
       <c r="R21" t="n">
-        <v>6781837</v>
+        <v>6781713</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2717,7 +2707,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129032780</v>
+        <v>129011219</v>
       </c>
       <c r="B22" t="n">
         <v>79044</v>
@@ -2752,10 +2742,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411808</v>
+        <v>411315</v>
       </c>
       <c r="R22" t="n">
-        <v>6781897</v>
+        <v>6781704</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2785,9 +2775,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2802,57 +2802,68 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032761</v>
+        <v>129032787</v>
       </c>
       <c r="B23" t="n">
-        <v>79044</v>
+        <v>92835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410889</v>
+        <v>410912</v>
       </c>
       <c r="R23" t="n">
-        <v>6781774</v>
+        <v>6781662</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,6 +2904,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2911,56 +2923,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129032787</v>
+        <v>129011222</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>79044</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>410912</v>
+        <v>411303</v>
       </c>
       <c r="R24" t="n">
-        <v>6781662</v>
+        <v>6781896</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2990,37 +2991,46 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129011222</v>
+        <v>129032755</v>
       </c>
       <c r="B25" t="n">
         <v>79044</v>
@@ -3055,10 +3065,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>411303</v>
+        <v>410678</v>
       </c>
       <c r="R25" t="n">
-        <v>6781896</v>
+        <v>6781823</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3088,19 +3098,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>14:57</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>14:57</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,19 +3115,19 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032755</v>
+        <v>129032759</v>
       </c>
       <c r="B26" t="n">
         <v>79044</v>
@@ -3162,10 +3162,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410678</v>
+        <v>410870</v>
       </c>
       <c r="R26" t="n">
-        <v>6781823</v>
+        <v>6781738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3224,7 +3224,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032759</v>
+        <v>129032761</v>
       </c>
       <c r="B27" t="n">
         <v>79044</v>
@@ -3259,10 +3259,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410870</v>
+        <v>410889</v>
       </c>
       <c r="R27" t="n">
-        <v>6781738</v>
+        <v>6781774</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032771</v>
+        <v>129032762</v>
       </c>
       <c r="B29" t="n">
         <v>79044</v>
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>411508</v>
+        <v>410890</v>
       </c>
       <c r="R29" t="n">
-        <v>6781794</v>
+        <v>6781771</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,7 +3515,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032762</v>
+        <v>129032771</v>
       </c>
       <c r="B30" t="n">
         <v>79044</v>
@@ -3550,10 +3550,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>410890</v>
+        <v>411508</v>
       </c>
       <c r="R30" t="n">
-        <v>6781771</v>
+        <v>6781794</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3612,10 +3612,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032779</v>
+        <v>129032180</v>
       </c>
       <c r="B31" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3623,21 +3623,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3647,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411808</v>
+        <v>411312</v>
       </c>
       <c r="R31" t="n">
-        <v>6781920</v>
+        <v>6781871</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3697,19 +3697,19 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032180</v>
+        <v>129032201</v>
       </c>
       <c r="B32" t="n">
         <v>79663</v>
@@ -3744,10 +3744,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411312</v>
+        <v>411198</v>
       </c>
       <c r="R32" t="n">
-        <v>6781871</v>
+        <v>6781834</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,10 +3806,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032201</v>
+        <v>129032779</v>
       </c>
       <c r="B33" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,21 +3817,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3841,10 +3841,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411198</v>
+        <v>411808</v>
       </c>
       <c r="R33" t="n">
-        <v>6781834</v>
+        <v>6781920</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3891,12 +3891,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4010,10 +4010,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129032739</v>
+        <v>129011216</v>
       </c>
       <c r="B35" t="n">
-        <v>79076</v>
+        <v>79044</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4021,21 +4021,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4045,10 +4045,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>410877</v>
+        <v>411316</v>
       </c>
       <c r="R35" t="n">
-        <v>6781741</v>
+        <v>6781674</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4078,9 +4078,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4095,19 +4105,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032764</v>
+        <v>129032187</v>
       </c>
       <c r="B36" t="n">
         <v>79044</v>
@@ -4142,10 +4152,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>410852</v>
+        <v>411321</v>
       </c>
       <c r="R36" t="n">
-        <v>6781859</v>
+        <v>6781689</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4192,22 +4202,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129011216</v>
+        <v>129032739</v>
       </c>
       <c r="B37" t="n">
-        <v>79044</v>
+        <v>79076</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4215,21 +4225,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4239,10 +4249,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>411316</v>
+        <v>410877</v>
       </c>
       <c r="R37" t="n">
-        <v>6781674</v>
+        <v>6781741</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4272,19 +4282,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,12 +4299,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4418,7 +4418,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032187</v>
+        <v>129032764</v>
       </c>
       <c r="B39" t="n">
         <v>79044</v>
@@ -4453,10 +4453,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>411321</v>
+        <v>410852</v>
       </c>
       <c r="R39" t="n">
-        <v>6781689</v>
+        <v>6781859</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,12 +4503,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4826,10 +4826,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128978125</v>
+        <v>129011202</v>
       </c>
       <c r="B43" t="n">
-        <v>79076</v>
+        <v>78801</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4837,21 +4837,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4861,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411776</v>
+        <v>411246</v>
       </c>
       <c r="R43" t="n">
-        <v>6781941</v>
+        <v>6781879</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4896,7 +4896,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:14</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4933,10 +4933,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129011202</v>
+        <v>129032183</v>
       </c>
       <c r="B44" t="n">
-        <v>78801</v>
+        <v>79663</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4944,21 +4944,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +4968,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>411246</v>
+        <v>412070</v>
       </c>
       <c r="R44" t="n">
-        <v>6781879</v>
+        <v>6781682</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5001,19 +5001,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5028,22 +5018,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>129032183</v>
+        <v>128978125</v>
       </c>
       <c r="B45" t="n">
-        <v>79663</v>
+        <v>79076</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5051,21 +5041,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6453</v>
+        <v>185</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5075,10 +5065,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>412070</v>
+        <v>411776</v>
       </c>
       <c r="R45" t="n">
-        <v>6781682</v>
+        <v>6781941</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5108,9 +5098,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,12 +5125,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5331,7 +5331,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129011224</v>
+        <v>129032184</v>
       </c>
       <c r="B48" t="n">
         <v>79044</v>
@@ -5366,10 +5366,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411539</v>
+        <v>411414</v>
       </c>
       <c r="R48" t="n">
-        <v>6781802</v>
+        <v>6781817</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5399,19 +5399,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5426,19 +5416,19 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032184</v>
+        <v>129032191</v>
       </c>
       <c r="B49" t="n">
         <v>79044</v>
@@ -5473,10 +5463,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411414</v>
+        <v>411495</v>
       </c>
       <c r="R49" t="n">
-        <v>6781817</v>
+        <v>6781803</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5535,7 +5525,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011206</v>
+        <v>129011224</v>
       </c>
       <c r="B50" t="n">
         <v>79044</v>
@@ -5570,10 +5560,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411166</v>
+        <v>411539</v>
       </c>
       <c r="R50" t="n">
-        <v>6781615</v>
+        <v>6781802</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5605,7 +5595,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -5615,7 +5605,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>16:06</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5642,7 +5632,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129032191</v>
+        <v>129011206</v>
       </c>
       <c r="B51" t="n">
         <v>79044</v>
@@ -5677,10 +5667,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411495</v>
+        <v>411166</v>
       </c>
       <c r="R51" t="n">
-        <v>6781803</v>
+        <v>6781615</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5710,9 +5700,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5727,12 +5727,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5933,7 +5933,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011225</v>
+        <v>129011227</v>
       </c>
       <c r="B54" t="n">
         <v>79044</v>
@@ -5968,10 +5968,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411536</v>
+        <v>411730</v>
       </c>
       <c r="R54" t="n">
-        <v>6781806</v>
+        <v>6781958</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6003,7 +6003,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6013,7 +6013,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6040,7 +6040,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011227</v>
+        <v>129011213</v>
       </c>
       <c r="B55" t="n">
         <v>79044</v>
@@ -6075,10 +6075,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411730</v>
+        <v>411327</v>
       </c>
       <c r="R55" t="n">
-        <v>6781958</v>
+        <v>6781657</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6147,7 +6147,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129011213</v>
+        <v>129032750</v>
       </c>
       <c r="B56" t="n">
         <v>79044</v>
@@ -6182,10 +6182,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>411327</v>
+        <v>410717</v>
       </c>
       <c r="R56" t="n">
-        <v>6781657</v>
+        <v>6781843</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6215,19 +6215,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6242,19 +6232,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129032192</v>
+        <v>129011225</v>
       </c>
       <c r="B57" t="n">
         <v>79044</v>
@@ -6289,10 +6279,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411504</v>
+        <v>411536</v>
       </c>
       <c r="R57" t="n">
-        <v>6781807</v>
+        <v>6781806</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6322,9 +6312,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,19 +6339,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032750</v>
+        <v>129032192</v>
       </c>
       <c r="B58" t="n">
         <v>79044</v>
@@ -6386,10 +6386,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>410717</v>
+        <v>411504</v>
       </c>
       <c r="R58" t="n">
-        <v>6781843</v>
+        <v>6781807</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,12 +6436,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129011218</v>
+        <v>129032778</v>
       </c>
       <c r="B60" t="n">
         <v>79044</v>
@@ -6580,10 +6580,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411322</v>
+        <v>411824</v>
       </c>
       <c r="R60" t="n">
-        <v>6781695</v>
+        <v>6781940</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6613,19 +6613,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6640,19 +6630,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129032778</v>
+        <v>129011218</v>
       </c>
       <c r="B61" t="n">
         <v>79044</v>
@@ -6687,10 +6677,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411824</v>
+        <v>411322</v>
       </c>
       <c r="R61" t="n">
-        <v>6781940</v>
+        <v>6781695</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6720,9 +6710,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,12 +6737,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -7244,7 +7244,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032746</v>
+        <v>129032772</v>
       </c>
       <c r="B67" t="n">
         <v>79044</v>
@@ -7279,10 +7279,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>410697</v>
+        <v>411565</v>
       </c>
       <c r="R67" t="n">
-        <v>6781752</v>
+        <v>6781780</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,7 +7341,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032189</v>
+        <v>129032746</v>
       </c>
       <c r="B68" t="n">
         <v>79044</v>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>411250</v>
+        <v>410697</v>
       </c>
       <c r="R68" t="n">
-        <v>6781886</v>
+        <v>6781752</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7426,19 +7426,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032772</v>
+        <v>129032189</v>
       </c>
       <c r="B69" t="n">
         <v>79044</v>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411565</v>
+        <v>411250</v>
       </c>
       <c r="R69" t="n">
-        <v>6781780</v>
+        <v>6781886</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,12 +7523,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7632,10 +7632,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032741</v>
+        <v>129032783</v>
       </c>
       <c r="B71" t="n">
-        <v>57724</v>
+        <v>79044</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7643,42 +7643,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>410958</v>
+        <v>411996</v>
       </c>
       <c r="R71" t="n">
-        <v>6781689</v>
+        <v>6781690</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,7 +7729,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032783</v>
+        <v>129032757</v>
       </c>
       <c r="B72" t="n">
         <v>79044</v>
@@ -7772,10 +7764,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>411996</v>
+        <v>410790</v>
       </c>
       <c r="R72" t="n">
-        <v>6781690</v>
+        <v>6781786</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7931,10 +7923,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032757</v>
+        <v>129032741</v>
       </c>
       <c r="B74" t="n">
-        <v>79044</v>
+        <v>57724</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7942,34 +7934,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410790</v>
+        <v>410958</v>
       </c>
       <c r="R74" t="n">
-        <v>6781786</v>
+        <v>6781689</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8028,10 +8028,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032767</v>
+        <v>129032181</v>
       </c>
       <c r="B75" t="n">
-        <v>79044</v>
+        <v>79663</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8039,21 +8039,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8063,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>410959</v>
+        <v>411425</v>
       </c>
       <c r="R75" t="n">
-        <v>6781848</v>
+        <v>6781806</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,19 +8113,19 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032768</v>
+        <v>129032767</v>
       </c>
       <c r="B76" t="n">
         <v>79044</v>
@@ -8163,7 +8163,7 @@
         <v>410959</v>
       </c>
       <c r="R76" t="n">
-        <v>6781857</v>
+        <v>6781848</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,10 +8222,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032181</v>
+        <v>129032768</v>
       </c>
       <c r="B77" t="n">
-        <v>79663</v>
+        <v>79044</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8233,21 +8233,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8257,10 +8257,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>411425</v>
+        <v>410959</v>
       </c>
       <c r="R77" t="n">
-        <v>6781806</v>
+        <v>6781857</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8307,12 +8307,12 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129032775</v>
+        <v>128978125</v>
       </c>
       <c r="B2" t="n">
-        <v>79044</v>
+        <v>79359</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>411542</v>
+        <v>411776</v>
       </c>
       <c r="R2" t="n">
-        <v>6781824</v>
+        <v>6781941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -743,9 +743,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13:14</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>13:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -760,22 +770,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129011223</v>
+        <v>129011197</v>
       </c>
       <c r="B3" t="n">
-        <v>79044</v>
+        <v>79359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>411437</v>
+        <v>411531</v>
       </c>
       <c r="R3" t="n">
-        <v>6781809</v>
+        <v>6781805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -842,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:22</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129032199</v>
+        <v>129011198</v>
       </c>
       <c r="B4" t="n">
-        <v>79044</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -890,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -914,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>412062</v>
+        <v>411534</v>
       </c>
       <c r="R4" t="n">
-        <v>6781678</v>
+        <v>6781828</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -947,9 +957,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,22 +984,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129032756</v>
+        <v>129032739</v>
       </c>
       <c r="B5" t="n">
-        <v>79044</v>
+        <v>79359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -987,21 +1007,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1011,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410745</v>
+        <v>410877</v>
       </c>
       <c r="R5" t="n">
-        <v>6781852</v>
+        <v>6781741</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1073,10 +1093,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129032745</v>
+        <v>129032740</v>
       </c>
       <c r="B6" t="n">
-        <v>79044</v>
+        <v>79359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1084,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1108,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>411010</v>
+        <v>411020</v>
       </c>
       <c r="R6" t="n">
-        <v>6781686</v>
+        <v>6781851</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1170,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129032188</v>
+        <v>131028944</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>79359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1181,34 +1201,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>185</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Piltsätern, Dlr</t>
+          <t>Mellantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>411295</v>
+        <v>410668</v>
       </c>
       <c r="R7" t="n">
-        <v>6781724</v>
+        <v>6781827</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1235,12 +1255,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1255,22 +1275,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129032781</v>
+        <v>131028938</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,34 +1298,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Piltsätern, Dlr</t>
+          <t>Mellantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>411940</v>
+        <v>410652</v>
       </c>
       <c r="R8" t="n">
-        <v>6781749</v>
+        <v>6781781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1332,12 +1352,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1352,22 +1372,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129011228</v>
+        <v>129032200</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1395,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1419,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>411779</v>
+        <v>411326</v>
       </c>
       <c r="R9" t="n">
-        <v>6781900</v>
+        <v>6781874</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1432,19 +1452,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:03</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1459,22 +1469,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129011217</v>
+        <v>129032786</v>
       </c>
       <c r="B10" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,34 +1492,45 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>411318</v>
+        <v>410970</v>
       </c>
       <c r="R10" t="n">
-        <v>6781689</v>
+        <v>6781684</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1539,49 +1560,40 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>15:38</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129032766</v>
+        <v>129032787</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,34 +1601,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>410949</v>
+        <v>410912</v>
       </c>
       <c r="R11" t="n">
-        <v>6781860</v>
+        <v>6781662</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1657,6 +1680,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1675,10 +1699,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129032786</v>
+        <v>131028939</v>
       </c>
       <c r="B12" t="n">
-        <v>92835</v>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,45 +1710,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Piltsätern, Dlr</t>
+          <t>Mellantjärnen, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>410970</v>
+        <v>410655</v>
       </c>
       <c r="R12" t="n">
-        <v>6781684</v>
+        <v>6781791</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,12 +1764,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-07-01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-08-30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1765,33 +1778,32 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Maria Hindemo</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129011212</v>
+        <v>129011205</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1819,10 +1831,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>411313</v>
+        <v>411162</v>
       </c>
       <c r="R13" t="n">
-        <v>6781661</v>
+        <v>6781612</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1854,7 +1866,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1864,7 +1876,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:43</t>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1891,14 +1903,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129032749</v>
+        <v>129011206</v>
       </c>
       <c r="B14" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1926,10 +1938,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>410719</v>
+        <v>411166</v>
       </c>
       <c r="R14" t="n">
-        <v>6781851</v>
+        <v>6781615</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1959,9 +1971,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>16:06</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>16:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1976,26 +1998,26 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129011209</v>
+        <v>129011207</v>
       </c>
       <c r="B15" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2023,10 +2045,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>411237</v>
+        <v>411175</v>
       </c>
       <c r="R15" t="n">
-        <v>6781635</v>
+        <v>6781624</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,7 +2080,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2068,7 +2090,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:55</t>
+          <t>16:05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2095,14 +2117,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129011211</v>
+        <v>129011208</v>
       </c>
       <c r="B16" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2130,10 +2152,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>411303</v>
+        <v>411221</v>
       </c>
       <c r="R16" t="n">
-        <v>6781649</v>
+        <v>6781624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2165,7 +2187,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2175,7 +2197,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:45</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2202,14 +2224,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129011208</v>
+        <v>129011209</v>
       </c>
       <c r="B17" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2237,10 +2259,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>411221</v>
+        <v>411237</v>
       </c>
       <c r="R17" t="n">
-        <v>6781624</v>
+        <v>6781635</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2272,7 +2294,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2282,7 +2304,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>15:55</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2309,14 +2331,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129032751</v>
+        <v>129011211</v>
       </c>
       <c r="B18" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2344,10 +2366,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>410727</v>
+        <v>411303</v>
       </c>
       <c r="R18" t="n">
-        <v>6781837</v>
+        <v>6781649</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2377,9 +2399,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:45</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2394,26 +2426,26 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129032780</v>
+        <v>129011212</v>
       </c>
       <c r="B19" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2441,10 +2473,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>411808</v>
+        <v>411313</v>
       </c>
       <c r="R19" t="n">
-        <v>6781897</v>
+        <v>6781661</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2474,9 +2506,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:43</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2491,26 +2533,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129011207</v>
+        <v>129011213</v>
       </c>
       <c r="B20" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2538,10 +2580,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>411175</v>
+        <v>411327</v>
       </c>
       <c r="R20" t="n">
-        <v>6781624</v>
+        <v>6781657</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2573,7 +2615,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2583,7 +2625,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>16:05</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2610,14 +2652,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129032758</v>
+        <v>129011215</v>
       </c>
       <c r="B21" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2645,10 +2687,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>410842</v>
+        <v>411330</v>
       </c>
       <c r="R21" t="n">
-        <v>6781713</v>
+        <v>6781666</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2678,9 +2720,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:41</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:41</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2695,26 +2747,26 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129011219</v>
+        <v>129011216</v>
       </c>
       <c r="B22" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2742,10 +2794,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>411315</v>
+        <v>411316</v>
       </c>
       <c r="R22" t="n">
-        <v>6781704</v>
+        <v>6781674</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2777,7 +2829,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2787,7 +2839,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2814,56 +2866,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129032787</v>
+        <v>129011217</v>
       </c>
       <c r="B23" t="n">
-        <v>92835</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>410912</v>
+        <v>411318</v>
       </c>
       <c r="R23" t="n">
-        <v>6781662</v>
+        <v>6781689</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2893,44 +2934,53 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129011222</v>
+        <v>129011218</v>
       </c>
       <c r="B24" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2958,10 +3008,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>411303</v>
+        <v>411322</v>
       </c>
       <c r="R24" t="n">
-        <v>6781896</v>
+        <v>6781695</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2993,7 +3043,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3003,7 +3053,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3030,14 +3080,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129032755</v>
+        <v>129011219</v>
       </c>
       <c r="B25" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3065,10 +3115,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>410678</v>
+        <v>411315</v>
       </c>
       <c r="R25" t="n">
-        <v>6781823</v>
+        <v>6781704</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3098,9 +3148,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3115,26 +3175,26 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129032759</v>
+        <v>129011220</v>
       </c>
       <c r="B26" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3162,10 +3222,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>410870</v>
+        <v>411312</v>
       </c>
       <c r="R26" t="n">
-        <v>6781738</v>
+        <v>6781706</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,9 +3255,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3212,26 +3282,26 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129032761</v>
+        <v>129011221</v>
       </c>
       <c r="B27" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3259,10 +3329,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>410889</v>
+        <v>411310</v>
       </c>
       <c r="R27" t="n">
-        <v>6781774</v>
+        <v>6781709</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3292,9 +3362,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3309,26 +3389,26 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129032754</v>
+        <v>129011222</v>
       </c>
       <c r="B28" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3356,10 +3436,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>410774</v>
+        <v>411303</v>
       </c>
       <c r="R28" t="n">
-        <v>6781776</v>
+        <v>6781896</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3389,9 +3469,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3406,26 +3496,26 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129032762</v>
+        <v>129011223</v>
       </c>
       <c r="B29" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3453,10 +3543,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>410890</v>
+        <v>411437</v>
       </c>
       <c r="R29" t="n">
-        <v>6781771</v>
+        <v>6781809</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3486,9 +3576,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>14:22</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>14:22</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3503,26 +3603,26 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129032771</v>
+        <v>129011224</v>
       </c>
       <c r="B30" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3550,10 +3650,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>411508</v>
+        <v>411539</v>
       </c>
       <c r="R30" t="n">
-        <v>6781794</v>
+        <v>6781802</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3583,9 +3683,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3600,44 +3710,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129032180</v>
+        <v>129011225</v>
       </c>
       <c r="B31" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3647,10 +3757,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>411312</v>
+        <v>411536</v>
       </c>
       <c r="R31" t="n">
-        <v>6781871</v>
+        <v>6781806</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3680,9 +3790,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3697,44 +3817,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129032201</v>
+        <v>129011226</v>
       </c>
       <c r="B32" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3744,10 +3864,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>411198</v>
+        <v>411549</v>
       </c>
       <c r="R32" t="n">
-        <v>6781834</v>
+        <v>6781840</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3777,9 +3897,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3794,26 +3924,26 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129032779</v>
+        <v>129011227</v>
       </c>
       <c r="B33" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -3841,10 +3971,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>411808</v>
+        <v>411730</v>
       </c>
       <c r="R33" t="n">
-        <v>6781920</v>
+        <v>6781958</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3874,9 +4004,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3891,44 +4031,44 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129011197</v>
+        <v>129011228</v>
       </c>
       <c r="B34" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3938,10 +4078,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>411531</v>
+        <v>411779</v>
       </c>
       <c r="R34" t="n">
-        <v>6781805</v>
+        <v>6781900</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3973,7 +4113,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -3983,7 +4123,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4010,14 +4150,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129011216</v>
+        <v>129011229</v>
       </c>
       <c r="B35" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4045,10 +4185,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>411316</v>
+        <v>412001</v>
       </c>
       <c r="R35" t="n">
-        <v>6781674</v>
+        <v>6781693</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4080,7 +4220,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4090,7 +4230,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>12:14</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4117,14 +4257,14 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129032187</v>
+        <v>129011230</v>
       </c>
       <c r="B36" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -4152,10 +4292,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>411321</v>
+        <v>412017</v>
       </c>
       <c r="R36" t="n">
-        <v>6781689</v>
+        <v>6781667</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4185,9 +4325,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4202,44 +4352,44 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129032739</v>
+        <v>129011231</v>
       </c>
       <c r="B37" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4249,10 +4399,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>410877</v>
+        <v>412081</v>
       </c>
       <c r="R37" t="n">
-        <v>6781741</v>
+        <v>6781660</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4282,9 +4432,19 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:48</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4299,26 +4459,26 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Anna-Britt Olsson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129011229</v>
+        <v>129032184</v>
       </c>
       <c r="B38" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -4346,10 +4506,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>412001</v>
+        <v>411414</v>
       </c>
       <c r="R38" t="n">
-        <v>6781693</v>
+        <v>6781817</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4379,19 +4539,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:14</t>
-        </is>
-      </c>
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:14</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4406,26 +4556,26 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129032764</v>
+        <v>129032185</v>
       </c>
       <c r="B39" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -4453,10 +4603,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>410852</v>
+        <v>411311</v>
       </c>
       <c r="R39" t="n">
-        <v>6781859</v>
+        <v>6781652</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4503,26 +4653,26 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129032774</v>
+        <v>129032186</v>
       </c>
       <c r="B40" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4550,10 +4700,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>411548</v>
+        <v>411332</v>
       </c>
       <c r="R40" t="n">
-        <v>6781798</v>
+        <v>6781694</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4600,26 +4750,26 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129011215</v>
+        <v>129032187</v>
       </c>
       <c r="B41" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -4647,10 +4797,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>411330</v>
+        <v>411321</v>
       </c>
       <c r="R41" t="n">
-        <v>6781666</v>
+        <v>6781689</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4680,19 +4830,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>15:41</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>15:41</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4707,26 +4847,26 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129011221</v>
+        <v>129032188</v>
       </c>
       <c r="B42" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -4754,10 +4894,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>411310</v>
+        <v>411295</v>
       </c>
       <c r="R42" t="n">
-        <v>6781709</v>
+        <v>6781724</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4787,19 +4927,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4814,44 +4944,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129011202</v>
+        <v>129032189</v>
       </c>
       <c r="B43" t="n">
-        <v>78801</v>
+        <v>79327</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4861,10 +4991,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>411246</v>
+        <v>411250</v>
       </c>
       <c r="R43" t="n">
-        <v>6781879</v>
+        <v>6781886</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4894,19 +5024,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>15:04</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -4921,44 +5041,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129032183</v>
+        <v>129032190</v>
       </c>
       <c r="B44" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4968,10 +5088,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>412070</v>
+        <v>411280</v>
       </c>
       <c r="R44" t="n">
-        <v>6781682</v>
+        <v>6781880</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5030,32 +5150,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128978125</v>
+        <v>129032191</v>
       </c>
       <c r="B45" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5065,10 +5185,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>411776</v>
+        <v>411495</v>
       </c>
       <c r="R45" t="n">
-        <v>6781941</v>
+        <v>6781803</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5098,19 +5218,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>13:14</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>13:14</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5125,26 +5235,26 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>129032748</v>
+        <v>129032192</v>
       </c>
       <c r="B46" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -5172,10 +5282,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>410685</v>
+        <v>411504</v>
       </c>
       <c r="R46" t="n">
-        <v>6781838</v>
+        <v>6781807</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5222,26 +5332,26 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129032752</v>
+        <v>129032195</v>
       </c>
       <c r="B47" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
@@ -5269,10 +5379,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>410787</v>
+        <v>411559</v>
       </c>
       <c r="R47" t="n">
-        <v>6781835</v>
+        <v>6781843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5319,26 +5429,26 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>129032184</v>
+        <v>129032196</v>
       </c>
       <c r="B48" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -5366,10 +5476,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>411414</v>
+        <v>411759</v>
       </c>
       <c r="R48" t="n">
-        <v>6781817</v>
+        <v>6781897</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5428,14 +5538,14 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>129032191</v>
+        <v>129032197</v>
       </c>
       <c r="B49" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -5463,10 +5573,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>411495</v>
+        <v>412070</v>
       </c>
       <c r="R49" t="n">
-        <v>6781803</v>
+        <v>6781649</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5525,14 +5635,14 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>129011224</v>
+        <v>129032198</v>
       </c>
       <c r="B50" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -5560,10 +5670,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>411539</v>
+        <v>412087</v>
       </c>
       <c r="R50" t="n">
-        <v>6781802</v>
+        <v>6781647</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5593,19 +5703,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>13:37</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>13:37</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5620,26 +5720,26 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>129011206</v>
+        <v>129032199</v>
       </c>
       <c r="B51" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -5667,10 +5767,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>411166</v>
+        <v>412062</v>
       </c>
       <c r="R51" t="n">
-        <v>6781615</v>
+        <v>6781678</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5700,19 +5800,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:06</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:06</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5727,26 +5817,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>129032769</v>
+        <v>129032745</v>
       </c>
       <c r="B52" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -5774,10 +5864,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>411017</v>
+        <v>411010</v>
       </c>
       <c r="R52" t="n">
-        <v>6781839</v>
+        <v>6781686</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5836,14 +5926,14 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>129032196</v>
+        <v>129032746</v>
       </c>
       <c r="B53" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -5871,10 +5961,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>411759</v>
+        <v>410697</v>
       </c>
       <c r="R53" t="n">
-        <v>6781897</v>
+        <v>6781752</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5921,26 +6011,26 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>129011227</v>
+        <v>129032748</v>
       </c>
       <c r="B54" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -5968,10 +6058,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>411730</v>
+        <v>410685</v>
       </c>
       <c r="R54" t="n">
-        <v>6781958</v>
+        <v>6781838</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6001,19 +6091,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>13:20</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>13:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6028,26 +6108,26 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>129011213</v>
+        <v>129032749</v>
       </c>
       <c r="B55" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -6075,10 +6155,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>411327</v>
+        <v>410719</v>
       </c>
       <c r="R55" t="n">
-        <v>6781657</v>
+        <v>6781851</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6108,19 +6188,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:42</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:42</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6135,12 +6205,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6150,11 +6220,11 @@
         <v>129032750</v>
       </c>
       <c r="B56" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -6244,14 +6314,14 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>129011225</v>
+        <v>129032751</v>
       </c>
       <c r="B57" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -6279,10 +6349,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>411536</v>
+        <v>410727</v>
       </c>
       <c r="R57" t="n">
-        <v>6781806</v>
+        <v>6781837</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6312,19 +6382,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>13:36</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6339,26 +6399,26 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>129032192</v>
+        <v>129032752</v>
       </c>
       <c r="B58" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -6386,10 +6446,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>411504</v>
+        <v>410787</v>
       </c>
       <c r="R58" t="n">
-        <v>6781807</v>
+        <v>6781835</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6436,26 +6496,26 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>129032185</v>
+        <v>129032754</v>
       </c>
       <c r="B59" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -6483,10 +6543,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>411311</v>
+        <v>410774</v>
       </c>
       <c r="R59" t="n">
-        <v>6781652</v>
+        <v>6781776</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6533,26 +6593,26 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>129032778</v>
+        <v>129032755</v>
       </c>
       <c r="B60" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -6580,10 +6640,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>411824</v>
+        <v>410678</v>
       </c>
       <c r="R60" t="n">
-        <v>6781940</v>
+        <v>6781823</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6642,14 +6702,14 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>129011218</v>
+        <v>129032756</v>
       </c>
       <c r="B61" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
@@ -6677,10 +6737,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>411322</v>
+        <v>410745</v>
       </c>
       <c r="R61" t="n">
-        <v>6781695</v>
+        <v>6781852</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6710,19 +6770,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:35</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:35</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6737,26 +6787,26 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>129032770</v>
+        <v>129032757</v>
       </c>
       <c r="B62" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -6784,10 +6834,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>411070</v>
+        <v>410790</v>
       </c>
       <c r="R62" t="n">
-        <v>6781879</v>
+        <v>6781786</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6846,14 +6896,14 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129011220</v>
+        <v>129032758</v>
       </c>
       <c r="B63" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -6881,10 +6931,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>411312</v>
+        <v>410842</v>
       </c>
       <c r="R63" t="n">
-        <v>6781706</v>
+        <v>6781713</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,19 +6964,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:33</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:33</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6941,26 +6981,26 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Anna-Britt Olsson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129032765</v>
+        <v>129032759</v>
       </c>
       <c r="B64" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
@@ -6988,10 +7028,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>410893</v>
+        <v>410870</v>
       </c>
       <c r="R64" t="n">
-        <v>6781859</v>
+        <v>6781738</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7050,32 +7090,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129032740</v>
+        <v>129032760</v>
       </c>
       <c r="B65" t="n">
-        <v>79076</v>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>185</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7085,10 +7125,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>411020</v>
+        <v>410875</v>
       </c>
       <c r="R65" t="n">
-        <v>6781851</v>
+        <v>6781746</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7147,32 +7187,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129032200</v>
+        <v>129032761</v>
       </c>
       <c r="B66" t="n">
-        <v>92835</v>
+        <v>79327</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7182,10 +7222,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>411326</v>
+        <v>410889</v>
       </c>
       <c r="R66" t="n">
-        <v>6781874</v>
+        <v>6781774</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7232,26 +7272,26 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129032772</v>
+        <v>129032762</v>
       </c>
       <c r="B67" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -7279,10 +7319,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>411565</v>
+        <v>410890</v>
       </c>
       <c r="R67" t="n">
-        <v>6781780</v>
+        <v>6781771</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7341,14 +7381,14 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129032746</v>
+        <v>129032763</v>
       </c>
       <c r="B68" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
@@ -7376,10 +7416,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>410697</v>
+        <v>410880</v>
       </c>
       <c r="R68" t="n">
-        <v>6781752</v>
+        <v>6781797</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7438,14 +7478,14 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129032189</v>
+        <v>129032764</v>
       </c>
       <c r="B69" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -7473,10 +7513,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>411250</v>
+        <v>410852</v>
       </c>
       <c r="R69" t="n">
-        <v>6781886</v>
+        <v>6781859</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7523,26 +7563,26 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>129032760</v>
+        <v>129032765</v>
       </c>
       <c r="B70" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -7570,10 +7610,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>410875</v>
+        <v>410893</v>
       </c>
       <c r="R70" t="n">
-        <v>6781746</v>
+        <v>6781859</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7632,14 +7672,14 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>129032783</v>
+        <v>129032766</v>
       </c>
       <c r="B71" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -7667,10 +7707,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>411996</v>
+        <v>410949</v>
       </c>
       <c r="R71" t="n">
-        <v>6781690</v>
+        <v>6781860</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7729,14 +7769,14 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129032757</v>
+        <v>129032767</v>
       </c>
       <c r="B72" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -7764,10 +7804,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>410790</v>
+        <v>410959</v>
       </c>
       <c r="R72" t="n">
-        <v>6781786</v>
+        <v>6781848</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7826,14 +7866,14 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>129032186</v>
+        <v>129032768</v>
       </c>
       <c r="B73" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -7861,10 +7901,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>411332</v>
+        <v>410959</v>
       </c>
       <c r="R73" t="n">
-        <v>6781694</v>
+        <v>6781857</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7911,65 +7951,57 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129032741</v>
+        <v>129032769</v>
       </c>
       <c r="B74" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Piltsätern, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>410958</v>
+        <v>411017</v>
       </c>
       <c r="R74" t="n">
-        <v>6781689</v>
+        <v>6781839</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8028,32 +8060,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129032181</v>
+        <v>129032770</v>
       </c>
       <c r="B75" t="n">
-        <v>79663</v>
+        <v>79327</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8063,10 +8095,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>411425</v>
+        <v>411070</v>
       </c>
       <c r="R75" t="n">
-        <v>6781806</v>
+        <v>6781879</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8113,26 +8145,26 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129032767</v>
+        <v>129032771</v>
       </c>
       <c r="B76" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
@@ -8160,10 +8192,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>410959</v>
+        <v>411508</v>
       </c>
       <c r="R76" t="n">
-        <v>6781848</v>
+        <v>6781794</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8222,14 +8254,14 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129032768</v>
+        <v>129032772</v>
       </c>
       <c r="B77" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -8257,10 +8289,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>410959</v>
+        <v>411565</v>
       </c>
       <c r="R77" t="n">
-        <v>6781857</v>
+        <v>6781780</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8319,14 +8351,14 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129011230</v>
+        <v>129032774</v>
       </c>
       <c r="B78" t="n">
-        <v>79044</v>
+        <v>79327</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -8354,10 +8386,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>412017</v>
+        <v>411548</v>
       </c>
       <c r="R78" t="n">
-        <v>6781667</v>
+        <v>6781798</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8387,19 +8419,9 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>12:01</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>12:01</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8414,15 +8436,2080 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129032775</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>411542</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6781824</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129032776</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>411544</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6781849</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129032777</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>411599</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6781743</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129032778</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>411824</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6781940</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129032779</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>411808</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6781920</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129032780</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>411808</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6781897</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129032781</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>411940</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6781749</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129032782</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>411976</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6781662</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129032783</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>411996</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6781690</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129032784</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>412173</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6781673</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129032785</v>
+      </c>
+      <c r="B89" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>412203</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6781678</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>131028943</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Mellantjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>410668</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6781827</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>131028942</v>
+      </c>
+      <c r="B91" t="n">
+        <v>83307</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Mellantjärnen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>410652</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6781816</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-07-01</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-30</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Maria Hindemo</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129011202</v>
+      </c>
+      <c r="B92" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>411246</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6781879</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
           <t>Anna-Britt Olsson</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
+      <c r="AX92" t="inlineStr">
         <is>
           <t>Anna-Britt Olsson</t>
         </is>
       </c>
-      <c r="AY78" t="inlineStr"/>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129032180</v>
+      </c>
+      <c r="B93" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>411312</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6781871</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129032181</v>
+      </c>
+      <c r="B94" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>411425</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6781806</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129032182</v>
+      </c>
+      <c r="B95" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>411549</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6781849</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129032183</v>
+      </c>
+      <c r="B96" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>412070</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6781682</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129032201</v>
+      </c>
+      <c r="B97" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>411198</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6781834</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Lisa Olson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129032741</v>
+      </c>
+      <c r="B98" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>410958</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6781689</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Göran Ehn</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129011200</v>
+      </c>
+      <c r="B99" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Piltsätern, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>411994</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6781699</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Malung-Sälen</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Transtrand</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 40704-2025 artfynd.xlsx
+++ b/artfynd/A 40704-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY99"/>
+  <dimension ref="A1:AZ99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131028944</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131028938</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131028939</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032746</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032748</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032749</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032750</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032751</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032755</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032756</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131028943</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131028942</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1943,6 +2008,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128978125</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2050,6 +2120,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011197</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2157,6 +2232,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011198</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2254,6 +2334,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032739</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2351,6 +2436,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032740</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2448,6 +2538,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032200</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2557,6 +2652,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032786</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2666,6 +2766,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032787</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2773,6 +2878,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011205</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2880,6 +2990,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011206</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2987,6 +3102,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011207</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3094,6 +3214,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011208</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3201,6 +3326,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011209</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3308,6 +3438,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011211</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3415,6 +3550,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011212</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3522,6 +3662,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011213</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3629,6 +3774,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011215</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3736,6 +3886,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011216</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3843,6 +3998,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011217</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3950,6 +4110,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011218</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4057,6 +4222,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011219</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4164,6 +4334,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011220</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4271,6 +4446,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011221</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4378,6 +4558,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011222</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4485,6 +4670,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011223</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4592,6 +4782,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011224</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4699,6 +4894,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011225</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4806,6 +5006,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011226</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4913,6 +5118,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011227</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5020,6 +5230,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011228</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5127,6 +5342,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011229</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5234,6 +5454,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011230</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5341,6 +5566,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011231</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5438,6 +5668,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032184</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5535,6 +5770,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032185</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5632,6 +5872,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032186</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5729,6 +5974,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032187</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5826,6 +6076,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032188</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5923,6 +6178,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032189</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6020,6 +6280,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032190</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6117,6 +6382,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032191</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6214,6 +6484,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032192</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6311,6 +6586,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032195</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6408,6 +6688,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032196</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6505,6 +6790,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032197</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6602,6 +6892,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032198</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6699,6 +6994,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032199</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6796,6 +7096,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032745</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6893,6 +7198,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032752</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6990,6 +7300,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032754</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7087,6 +7402,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032757</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7184,6 +7504,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032758</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7281,6 +7606,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032759</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7378,6 +7708,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032760</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7475,6 +7810,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032761</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7572,6 +7912,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032762</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7669,6 +8014,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032763</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7766,6 +8116,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032764</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7863,6 +8218,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032765</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7960,6 +8320,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032766</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8057,6 +8422,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032767</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8154,6 +8524,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032768</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8251,6 +8626,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032769</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8348,6 +8728,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032770</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8445,6 +8830,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032771</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8542,6 +8932,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032772</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8639,6 +9034,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032774</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8736,6 +9136,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032775</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8833,6 +9238,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032776</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8930,6 +9340,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032777</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9027,6 +9442,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032778</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9124,6 +9544,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032779</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9221,6 +9646,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032780</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9318,6 +9748,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032781</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9415,6 +9850,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032782</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9512,6 +9952,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032783</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9609,6 +10054,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032784</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9706,6 +10156,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032785</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9813,6 +10268,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011202</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9910,6 +10370,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032180</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10007,6 +10472,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032181</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10104,6 +10574,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032182</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10201,6 +10676,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032183</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10298,6 +10778,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032201</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10403,6 +10888,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129032741</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10510,8 +11000,113 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129011200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>